--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF4926B-A931-4649-93A3-C3D3DD52DF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0357B34-1BB7-47E8-BF01-A12A56D07FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5295,7 +5295,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
         <v>73</v>
       </c>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K2" s="10"/>
     </row>
-    <row r="3" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
         <v>74</v>
       </c>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0357B34-1BB7-47E8-BF01-A12A56D07FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678388A6-2A6E-406A-8468-8E7BD8F8DA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1603,60 +1603,9 @@
     <t>Vanellus chilensis</t>
   </si>
   <si>
-    <t>Benteveo.jpg</t>
-  </si>
-  <si>
-    <t>Calandria.jpg</t>
-  </si>
-  <si>
-    <t>Carancho.jpg</t>
-  </si>
-  <si>
-    <t>Chimango.jpg</t>
-  </si>
-  <si>
-    <t>Chingolo.jpg</t>
-  </si>
-  <si>
-    <t>Zorzalcolorado.jpg</t>
-  </si>
-  <si>
-    <t>CarpinterosCampestres.jpg</t>
-  </si>
-  <si>
-    <t>LechucitaVizcachera.jpg</t>
-  </si>
-  <si>
-    <t>Tordorenegrido.jpg</t>
-  </si>
-  <si>
-    <t>TyrannusSavana.jpg</t>
-  </si>
-  <si>
-    <t>GavilanMixto.jpg</t>
-  </si>
-  <si>
     <t>Fuente.jpg</t>
   </si>
   <si>
-    <t>Hornero.jpg</t>
-  </si>
-  <si>
-    <t>Gorrion.jpg</t>
-  </si>
-  <si>
-    <t>PechoAmarillo.jpg</t>
-  </si>
-  <si>
-    <t>Pirincho.jpg</t>
-  </si>
-  <si>
-    <t>Suiriríreal.jpg</t>
-  </si>
-  <si>
-    <t>Tero.jpg</t>
-  </si>
-  <si>
     <t>destacado</t>
   </si>
   <si>
@@ -1669,10 +1618,61 @@
     <t>Cabecita negra</t>
   </si>
   <si>
-    <t>Torcaza.jpg</t>
-  </si>
-  <si>
-    <t>Picazuro.jpg</t>
+    <t>benteveo.jpg</t>
+  </si>
+  <si>
+    <t>zorzalcolorado.jpg</t>
+  </si>
+  <si>
+    <t>calandria.jpg</t>
+  </si>
+  <si>
+    <t>carancho.jpg</t>
+  </si>
+  <si>
+    <t>carpinteroscampestres.jpg</t>
+  </si>
+  <si>
+    <t>chimango.jpg</t>
+  </si>
+  <si>
+    <t>chingolo.jpg</t>
+  </si>
+  <si>
+    <t>gavilanmixto.jpg</t>
+  </si>
+  <si>
+    <t>gorrion.jpg</t>
+  </si>
+  <si>
+    <t>hornero.jpg</t>
+  </si>
+  <si>
+    <t>lechucitavizcachera.jpg</t>
+  </si>
+  <si>
+    <t>pechoamarillo.jpg</t>
+  </si>
+  <si>
+    <t>picazuro.jpg</t>
+  </si>
+  <si>
+    <t>pirincho.jpg</t>
+  </si>
+  <si>
+    <t>suiriríreal.jpg</t>
+  </si>
+  <si>
+    <t>tero.jpg</t>
+  </si>
+  <si>
+    <t>tyrannussavana.jpg</t>
+  </si>
+  <si>
+    <t>torcaza.jpg</t>
+  </si>
+  <si>
+    <t>tordorenegrido.jpg</t>
   </si>
 </sst>
 </file>
@@ -2147,10 +2147,10 @@
         <v>76</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
@@ -5318,7 +5318,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="K2" s="10"/>
     </row>
@@ -5345,7 +5345,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K3" s="10"/>
     </row>
@@ -5373,7 +5373,7 @@
         <v>392</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>478</v>
@@ -5404,7 +5404,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K6" s="10"/>
     </row>
@@ -5425,7 +5425,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="K7" s="10"/>
     </row>
@@ -5450,7 +5450,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -5494,7 +5494,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="K10" s="10"/>
     </row>
@@ -5519,7 +5519,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -5637,7 +5637,7 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
         <v>417</v>
       </c>
@@ -5658,7 +5658,7 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="10" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K18" s="10"/>
     </row>
@@ -5803,7 +5803,7 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K25" s="10"/>
     </row>
@@ -5847,7 +5847,7 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="K27" s="10"/>
     </row>
@@ -5948,7 +5948,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="10" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K32" s="10"/>
     </row>
@@ -5988,7 +5988,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
       <c r="J34" s="10" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="K34" s="10"/>
     </row>
@@ -6032,7 +6032,7 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="10" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K36" s="10"/>
     </row>
@@ -6076,7 +6076,7 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K38" s="10"/>
     </row>
@@ -6139,7 +6139,7 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="10" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K41" s="10"/>
     </row>
@@ -6164,7 +6164,7 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="10" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="K42" s="10"/>
     </row>
@@ -6227,7 +6227,7 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
     </row>
-    <row r="46" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
         <v>473</v>
       </c>
@@ -6248,7 +6248,7 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="10" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="K46" s="10"/>
     </row>
@@ -6482,7 +6482,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>48</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678388A6-2A6E-406A-8468-8E7BD8F8DA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9567B2-687A-45D1-8B0C-79BAC26718DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1618,27 +1618,6 @@
     <t>Cabecita negra</t>
   </si>
   <si>
-    <t>benteveo.jpg</t>
-  </si>
-  <si>
-    <t>zorzalcolorado.jpg</t>
-  </si>
-  <si>
-    <t>calandria.jpg</t>
-  </si>
-  <si>
-    <t>carancho.jpg</t>
-  </si>
-  <si>
-    <t>carpinteroscampestres.jpg</t>
-  </si>
-  <si>
-    <t>chimango.jpg</t>
-  </si>
-  <si>
-    <t>chingolo.jpg</t>
-  </si>
-  <si>
     <t>gavilanmixto.jpg</t>
   </si>
   <si>
@@ -1672,7 +1651,28 @@
     <t>torcaza.jpg</t>
   </si>
   <si>
-    <t>tordorenegrido.jpg</t>
+    <t xml:space="preserve">benteveo.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">zorzalcolorado.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">carancho.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">calandria.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">carpinteroscampestres.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chingolo.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chimango.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tordorenegrido.jpg </t>
   </si>
 </sst>
 </file>
@@ -5318,7 +5318,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="K2" s="10"/>
     </row>
@@ -5345,7 +5345,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="K3" s="10"/>
     </row>
@@ -5404,7 +5404,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="K6" s="10"/>
     </row>
@@ -5425,7 +5425,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="K7" s="10"/>
     </row>
@@ -5450,7 +5450,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -5494,7 +5494,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="K10" s="10"/>
     </row>
@@ -5519,7 +5519,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -5658,7 +5658,7 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="10" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="K18" s="10"/>
     </row>
@@ -5740,7 +5740,7 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
       <c r="J22" s="10" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="K22" s="10"/>
     </row>
@@ -5803,7 +5803,7 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="10" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="K25" s="10"/>
     </row>
@@ -5847,7 +5847,7 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="K27" s="10"/>
     </row>
@@ -5948,7 +5948,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="10" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="K32" s="10"/>
     </row>
@@ -5988,7 +5988,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
       <c r="J34" s="10" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="K34" s="10"/>
     </row>
@@ -6032,7 +6032,7 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="10" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="K36" s="10"/>
     </row>
@@ -6076,7 +6076,7 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="K38" s="10"/>
     </row>
@@ -6139,7 +6139,7 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="10" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="K41" s="10"/>
     </row>
@@ -6164,7 +6164,7 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="10" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="K42" s="10"/>
     </row>
@@ -6204,7 +6204,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
       <c r="J44" s="10" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="K44" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9567B2-687A-45D1-8B0C-79BAC26718DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9B96E5-25D4-45C0-B78E-80C0BC4866DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9B96E5-25D4-45C0-B78E-80C0BC4866DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8648B2D3-FBE5-4097-8215-4D4278CA0546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8648B2D3-FBE5-4097-8215-4D4278CA0546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641BC52B-E62B-43CF-9917-ABC7DAD20BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641BC52B-E62B-43CF-9917-ABC7DAD20BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D968D1C7-35EE-41BF-9757-A1AAF28F6769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5288,7 +5288,7 @@
       <c r="I1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="9" t="s">
@@ -5317,7 +5317,7 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="5" t="s">
         <v>536</v>
       </c>
       <c r="K2" s="10"/>
@@ -5344,12 +5344,12 @@
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="5" t="s">
         <v>537</v>
       </c>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
         <v>390</v>
       </c>
@@ -5365,7 +5365,7 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
+      <c r="J4" s="5"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5384,7 +5384,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5403,7 +5403,7 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="5" t="s">
         <v>539</v>
       </c>
       <c r="K6" s="10"/>
@@ -5424,12 +5424,12 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="5" t="s">
         <v>538</v>
       </c>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
         <v>397</v>
       </c>
@@ -5449,7 +5449,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="5" t="s">
         <v>540</v>
       </c>
       <c r="K8" s="10"/>
@@ -5470,7 +5470,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
+      <c r="J9" s="5"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5493,7 +5493,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="5" t="s">
         <v>542</v>
       </c>
       <c r="K10" s="10"/>
@@ -5518,7 +5518,7 @@
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="5" t="s">
         <v>541</v>
       </c>
       <c r="K11" s="10"/>
@@ -5657,7 +5657,7 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="5" t="s">
         <v>525</v>
       </c>
       <c r="K18" s="10"/>
@@ -5678,7 +5678,7 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
+      <c r="J19" s="5"/>
       <c r="K19" s="10"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5697,7 +5697,7 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
+      <c r="J20" s="5"/>
       <c r="K20" s="10"/>
     </row>
     <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5716,7 +5716,7 @@
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
+      <c r="J21" s="5"/>
       <c r="K21" s="10"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5739,7 +5739,7 @@
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="5" t="s">
         <v>526</v>
       </c>
       <c r="K22" s="10"/>
@@ -5760,7 +5760,7 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="J23" s="5"/>
       <c r="K23" s="10"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5779,7 +5779,7 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
+      <c r="J24" s="5"/>
       <c r="K24" s="10"/>
     </row>
     <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5802,7 +5802,7 @@
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="5" t="s">
         <v>527</v>
       </c>
       <c r="K25" s="10"/>
@@ -5823,7 +5823,7 @@
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
+      <c r="J26" s="5"/>
       <c r="K26" s="10"/>
     </row>
     <row r="27" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -5846,7 +5846,7 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="5" t="s">
         <v>528</v>
       </c>
       <c r="K27" s="10"/>
@@ -5867,7 +5867,7 @@
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
+      <c r="J28" s="5"/>
       <c r="K28" s="10"/>
     </row>
     <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5886,7 +5886,7 @@
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
+      <c r="J29" s="5"/>
       <c r="K29" s="10"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5905,7 +5905,7 @@
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
+      <c r="J30" s="5"/>
       <c r="K30" s="10"/>
     </row>
     <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5924,7 +5924,7 @@
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
+      <c r="J31" s="5"/>
       <c r="K31" s="10"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5947,7 +5947,7 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="5" t="s">
         <v>529</v>
       </c>
       <c r="K32" s="10"/>
@@ -5968,7 +5968,7 @@
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
+      <c r="J33" s="5"/>
       <c r="K33" s="10"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5987,7 +5987,7 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="5" t="s">
         <v>530</v>
       </c>
       <c r="K34" s="10"/>
@@ -6008,7 +6008,7 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
+      <c r="J35" s="5"/>
       <c r="K35" s="10"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6031,7 +6031,7 @@
       <c r="G36" s="10"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="5" t="s">
         <v>531</v>
       </c>
       <c r="K36" s="10"/>
@@ -6052,7 +6052,7 @@
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
+      <c r="J37" s="5"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6075,7 +6075,7 @@
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="5" t="s">
         <v>532</v>
       </c>
       <c r="K38" s="10"/>
@@ -6096,7 +6096,7 @@
       <c r="G39" s="10"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
+      <c r="J39" s="5"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6115,7 +6115,7 @@
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
+      <c r="J40" s="5"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6138,7 +6138,7 @@
       <c r="G41" s="10"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="5" t="s">
         <v>533</v>
       </c>
       <c r="K41" s="10"/>
@@ -6163,7 +6163,7 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="5" t="s">
         <v>534</v>
       </c>
       <c r="K42" s="10"/>
@@ -6184,7 +6184,7 @@
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
+      <c r="J43" s="5"/>
       <c r="K43" s="10"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6203,7 +6203,7 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
-      <c r="J44" s="10" t="s">
+      <c r="J44" s="5" t="s">
         <v>535</v>
       </c>
       <c r="K44" s="10"/>
@@ -6224,7 +6224,7 @@
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
+      <c r="J45" s="5"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6247,7 +6247,7 @@
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="5" t="s">
         <v>543</v>
       </c>
       <c r="K46" s="10"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D968D1C7-35EE-41BF-9757-A1AAF28F6769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230FC655-8D8B-47FF-A0EE-0F08479FDA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1642,9 +1642,6 @@
     <t>suiriríreal.jpg</t>
   </si>
   <si>
-    <t>tero.jpg</t>
-  </si>
-  <si>
     <t>tyrannussavana.jpg</t>
   </si>
   <si>
@@ -1673,6 +1670,9 @@
   </si>
   <si>
     <t xml:space="preserve">tordorenegrido.jpg </t>
+  </si>
+  <si>
+    <t>tero.JPG</t>
   </si>
 </sst>
 </file>
@@ -5318,7 +5318,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K2" s="10"/>
     </row>
@@ -5345,7 +5345,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K3" s="10"/>
     </row>
@@ -5404,7 +5404,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K6" s="10"/>
     </row>
@@ -5425,7 +5425,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K7" s="10"/>
     </row>
@@ -5450,7 +5450,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -5494,7 +5494,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K10" s="10"/>
     </row>
@@ -5519,7 +5519,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -6139,7 +6139,7 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="5" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="K41" s="10"/>
     </row>
@@ -6164,7 +6164,7 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K42" s="10"/>
     </row>
@@ -6204,7 +6204,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
       <c r="J44" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K44" s="10"/>
     </row>
@@ -6248,7 +6248,7 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230FC655-8D8B-47FF-A0EE-0F08479FDA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4547E476-8BA0-4360-A784-247F3956F3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="542">
   <si>
     <t>id</t>
   </si>
@@ -1207,9 +1207,6 @@
     <t>Sabina.jpg</t>
   </si>
   <si>
-    <t>Pino.jpg</t>
-  </si>
-  <si>
     <t>fuente</t>
   </si>
   <si>
@@ -1646,9 +1643,6 @@
   </si>
   <si>
     <t>torcaza.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">benteveo.jpg </t>
   </si>
   <si>
     <t xml:space="preserve">zorzalcolorado.jpg </t>
@@ -2147,10 +2141,10 @@
         <v>76</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2196,10 +2190,10 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -2218,7 +2212,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>83</v>
@@ -2258,7 +2252,9 @@
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>88</v>
       </c>
@@ -2276,7 +2272,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -2294,7 +2290,9 @@
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
         <v>89</v>
@@ -2313,7 +2311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -2331,7 +2329,9 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -2367,7 +2367,9 @@
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I7" s="5" t="s">
         <v>102</v>
       </c>
@@ -2385,7 +2387,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -2403,7 +2405,9 @@
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I8" s="5" t="s">
         <v>108</v>
       </c>
@@ -2421,7 +2425,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>111</v>
       </c>
@@ -2439,7 +2443,9 @@
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I9" s="5" t="s">
         <v>79</v>
       </c>
@@ -2457,7 +2463,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>115</v>
       </c>
@@ -2475,7 +2481,9 @@
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
       </c>
@@ -2511,7 +2519,9 @@
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I11" s="5" t="s">
         <v>121</v>
       </c>
@@ -2529,7 +2539,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>123</v>
       </c>
@@ -2545,7 +2555,9 @@
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I12" s="5" t="s">
         <v>121</v>
       </c>
@@ -2581,7 +2593,9 @@
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="H13" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I13" s="5" t="s">
         <v>79</v>
       </c>
@@ -2599,7 +2613,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -2617,7 +2631,9 @@
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I14" s="5" t="s">
         <v>88</v>
       </c>
@@ -2635,7 +2651,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>134</v>
       </c>
@@ -2653,7 +2669,9 @@
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I15" s="5" t="s">
         <v>83</v>
       </c>
@@ -2674,7 +2692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>138</v>
       </c>
@@ -2690,7 +2708,9 @@
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
       </c>
@@ -2708,7 +2728,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>141</v>
       </c>
@@ -2726,7 +2746,9 @@
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I17" s="5" t="s">
         <v>121</v>
       </c>
@@ -2747,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>145</v>
       </c>
@@ -2765,7 +2787,9 @@
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I18" s="5" t="s">
         <v>148</v>
       </c>
@@ -2799,7 +2823,9 @@
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I19" s="5" t="s">
         <v>152</v>
       </c>
@@ -2817,7 +2843,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>154</v>
       </c>
@@ -2835,7 +2861,9 @@
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I20" s="5" t="s">
         <v>157</v>
       </c>
@@ -2853,7 +2881,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -2871,7 +2899,9 @@
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I21" s="5" t="s">
         <v>162</v>
       </c>
@@ -2907,7 +2937,9 @@
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I22" s="5" t="s">
         <v>167</v>
       </c>
@@ -2925,7 +2957,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>169</v>
       </c>
@@ -2943,7 +2975,9 @@
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I23" s="5" t="s">
         <v>172</v>
       </c>
@@ -2961,7 +2995,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="87" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>174</v>
       </c>
@@ -2977,7 +3011,9 @@
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I24" s="5" t="s">
         <v>79</v>
       </c>
@@ -3011,7 +3047,9 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I25" s="5" t="s">
         <v>79</v>
       </c>
@@ -3029,7 +3067,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>179</v>
       </c>
@@ -3047,7 +3085,9 @@
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="H26" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I26" s="5" t="s">
         <v>102</v>
       </c>
@@ -3065,7 +3105,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>181</v>
       </c>
@@ -3083,7 +3123,9 @@
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="H27" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I27" s="5" t="s">
         <v>88</v>
       </c>
@@ -3101,7 +3143,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -3119,7 +3161,9 @@
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="H28" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I28" s="5" t="s">
         <v>83</v>
       </c>
@@ -3137,7 +3181,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -3155,7 +3199,9 @@
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="H29" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I29" s="5" t="s">
         <v>172</v>
       </c>
@@ -3191,7 +3237,9 @@
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
+      <c r="H30" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I30" s="5" t="s">
         <v>195</v>
       </c>
@@ -3209,7 +3257,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -3227,7 +3275,9 @@
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="H31" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I31" s="5" t="s">
         <v>200</v>
       </c>
@@ -3245,7 +3295,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>202</v>
       </c>
@@ -3263,7 +3313,9 @@
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
+      <c r="H32" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I32" s="5" t="s">
         <v>205</v>
       </c>
@@ -3281,7 +3333,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>207</v>
       </c>
@@ -3299,7 +3351,9 @@
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="H33" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I33" s="5" t="s">
         <v>79</v>
       </c>
@@ -3335,7 +3389,9 @@
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
+      <c r="H34" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="I34" s="5" t="s">
         <v>214</v>
       </c>
@@ -5246,7 +5302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A580122F-82B9-4D2E-B07E-0D8C98A0F809}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
@@ -5256,7 +5312,6 @@
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
     <col min="7" max="7" width="12.08984375" customWidth="1"/>
     <col min="9" max="9" width="16.08984375" customWidth="1"/>
-    <col min="10" max="10" width="21.26953125" customWidth="1"/>
     <col min="11" max="11" width="19.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5292,10 +5347,10 @@
         <v>7</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
         <v>73</v>
       </c>
@@ -5318,11 +5373,11 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="5" t="s">
-        <v>535</v>
+        <v>387</v>
       </c>
       <c r="K2" s="10"/>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
         <v>74</v>
       </c>
@@ -5345,19 +5400,19 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K3" s="10"/>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>391</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -5370,13 +5425,13 @@
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -5387,15 +5442,15 @@
       <c r="J5" s="5"/>
       <c r="K5" s="10"/>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>394</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -5404,19 +5459,19 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>396</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -5425,19 +5480,19 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>398</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D8" s="10">
         <v>-57.680219000000001</v>
@@ -5450,19 +5505,19 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>400</v>
-      </c>
       <c r="C9" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -5473,15 +5528,15 @@
       <c r="J9" s="5"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>402</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D10" s="10">
         <v>-57.679960999999999</v>
@@ -5494,19 +5549,19 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>404</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D11" s="10">
         <v>-57.681131000000001</v>
@@ -5519,19 +5574,19 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>406</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -5539,18 +5594,18 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
+      <c r="J12" s="5"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>408</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -5558,18 +5613,18 @@
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
+      <c r="J13" s="5"/>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>410</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -5577,18 +5632,18 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
+      <c r="J14" s="5"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>412</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -5596,18 +5651,18 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
+      <c r="J15" s="5"/>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>414</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -5615,18 +5670,18 @@
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
+      <c r="J16" s="5"/>
       <c r="K16" s="10"/>
     </row>
     <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>416</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -5634,18 +5689,18 @@
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>418</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D18" s="10">
         <v>-57.683276999999997</v>
@@ -5658,19 +5713,19 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K18" s="10"/>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>420</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -5683,13 +5738,13 @@
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>422</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -5702,13 +5757,13 @@
     </row>
     <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>424</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -5719,15 +5774,15 @@
       <c r="J21" s="5"/>
       <c r="K21" s="10"/>
     </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>426</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D22" s="10">
         <v>-57.682054000000001</v>
@@ -5740,19 +5795,19 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
       <c r="J22" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K22" s="10"/>
     </row>
     <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>428</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -5765,13 +5820,13 @@
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>430</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -5782,15 +5837,15 @@
       <c r="J24" s="5"/>
       <c r="K24" s="10"/>
     </row>
-    <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>432</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D25" s="10">
         <v>-57.679361</v>
@@ -5803,19 +5858,19 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K25" s="10"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>434</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -5826,15 +5881,15 @@
       <c r="J26" s="5"/>
       <c r="K26" s="10"/>
     </row>
-    <row r="27" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>436</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D27" s="10">
         <v>-57.684317</v>
@@ -5847,19 +5902,19 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K27" s="10"/>
     </row>
     <row r="28" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>438</v>
-      </c>
       <c r="C28" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -5872,13 +5927,13 @@
     </row>
     <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>440</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -5891,13 +5946,13 @@
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>442</v>
-      </c>
       <c r="C30" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
@@ -5910,13 +5965,13 @@
     </row>
     <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>444</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
@@ -5927,15 +5982,15 @@
       <c r="J31" s="5"/>
       <c r="K31" s="10"/>
     </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>446</v>
-      </c>
       <c r="C32" s="11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D32" s="10">
         <v>-57.682547</v>
@@ -5948,19 +6003,19 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K32" s="10"/>
     </row>
     <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>448</v>
-      </c>
       <c r="C33" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -5971,15 +6026,15 @@
       <c r="J33" s="5"/>
       <c r="K33" s="10"/>
     </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>450</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -5988,19 +6043,19 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
       <c r="J34" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K34" s="10"/>
     </row>
     <row r="35" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>452</v>
-      </c>
       <c r="C35" s="11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
@@ -6011,15 +6066,15 @@
       <c r="J35" s="5"/>
       <c r="K35" s="10"/>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>454</v>
-      </c>
       <c r="C36" s="11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D36" s="10">
         <v>-57.682281000000003</v>
@@ -6032,19 +6087,19 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>456</v>
-      </c>
       <c r="C37" s="11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -6055,15 +6110,15 @@
       <c r="J37" s="5"/>
       <c r="K37" s="10"/>
     </row>
-    <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>458</v>
-      </c>
       <c r="C38" s="11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D38" s="10">
         <v>-57.685510999999998</v>
@@ -6076,19 +6131,19 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B39" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>460</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -6101,13 +6156,13 @@
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>462</v>
-      </c>
       <c r="C40" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -6120,13 +6175,13 @@
     </row>
     <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>464</v>
-      </c>
       <c r="C41" s="11" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D41" s="10">
         <v>-57.681240000000003</v>
@@ -6139,19 +6194,19 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K41" s="10"/>
     </row>
-    <row r="42" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>466</v>
-      </c>
       <c r="C42" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D42" s="10">
         <v>-57.683684</v>
@@ -6164,19 +6219,19 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>468</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -6187,15 +6242,15 @@
       <c r="J43" s="5"/>
       <c r="K43" s="10"/>
     </row>
-    <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>470</v>
-      </c>
       <c r="C44" s="11" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
@@ -6204,19 +6259,19 @@
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
       <c r="J44" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K44" s="10"/>
     </row>
     <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>472</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
@@ -6227,15 +6282,15 @@
       <c r="J45" s="5"/>
       <c r="K45" s="10"/>
     </row>
-    <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B46" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>474</v>
-      </c>
       <c r="C46" s="11" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D46" s="10">
         <v>-57.682558</v>
@@ -6248,19 +6303,19 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K46" s="10"/>
     </row>
     <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>476</v>
-      </c>
       <c r="C47" s="11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
@@ -6268,8 +6323,143 @@
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="J47" s="5"/>
       <c r="K47" s="10"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J50" s="5"/>
+    </row>
+    <row r="51" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J52" s="5"/>
+    </row>
+    <row r="53" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J54" s="5"/>
+    </row>
+    <row r="55" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J56" s="5"/>
+    </row>
+    <row r="57" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J58" s="5"/>
+    </row>
+    <row r="59" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J59" s="5"/>
+    </row>
+    <row r="60" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J60" s="5"/>
+    </row>
+    <row r="61" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J61" s="5"/>
+    </row>
+    <row r="62" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J62" s="5"/>
+    </row>
+    <row r="63" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J63" s="5"/>
+    </row>
+    <row r="64" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J64" s="5"/>
+    </row>
+    <row r="65" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J65" s="5"/>
+    </row>
+    <row r="66" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J66" s="5"/>
+    </row>
+    <row r="67" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J67" s="5"/>
+    </row>
+    <row r="68" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J68" s="5"/>
+    </row>
+    <row r="69" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J69" s="5"/>
+    </row>
+    <row r="70" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J70" s="5"/>
+    </row>
+    <row r="71" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J71" s="5"/>
+    </row>
+    <row r="72" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J72" s="5"/>
+    </row>
+    <row r="73" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J73" s="5"/>
+    </row>
+    <row r="74" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J74" s="5"/>
+    </row>
+    <row r="75" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J76" s="5"/>
+    </row>
+    <row r="77" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J77" s="5"/>
+    </row>
+    <row r="78" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J78" s="5"/>
+    </row>
+    <row r="79" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J79" s="5"/>
+    </row>
+    <row r="80" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J81" s="5"/>
+    </row>
+    <row r="82" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J82" s="5"/>
+    </row>
+    <row r="83" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J83" s="5"/>
+    </row>
+    <row r="84" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J84" s="5"/>
+    </row>
+    <row r="85" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J85" s="5"/>
+    </row>
+    <row r="86" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J86" s="5"/>
+    </row>
+    <row r="87" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J87" s="5"/>
+    </row>
+    <row r="88" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J88" s="5"/>
+    </row>
+    <row r="89" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J89" s="5"/>
+    </row>
+    <row r="90" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J90" s="5"/>
+    </row>
+    <row r="91" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J91" s="5"/>
+    </row>
+    <row r="92" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J92" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -6482,7 +6672,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>48</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4547E476-8BA0-4360-A784-247F3956F3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C5C06B-A240-47DA-93EA-BB72124D8C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -2193,7 +2193,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -2212,7 +2212,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>387</v>
+        <v>534</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>83</v>
@@ -2253,7 +2253,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>387</v>
+        <v>536</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>88</v>
@@ -2291,7 +2291,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>387</v>
+        <v>535</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>387</v>
+        <v>537</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
@@ -2368,7 +2368,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>387</v>
+        <v>539</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>102</v>
@@ -2406,7 +2406,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>387</v>
+        <v>538</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>108</v>
@@ -2444,7 +2444,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>387</v>
+        <v>524</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>79</v>
@@ -2482,7 +2482,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>387</v>
+        <v>525</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
@@ -2520,7 +2520,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>387</v>
+        <v>526</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>121</v>
@@ -2539,7 +2539,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>123</v>
       </c>
@@ -2556,7 +2556,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>387</v>
+        <v>527</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>121</v>
@@ -2594,7 +2594,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>387</v>
+        <v>528</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>79</v>
@@ -2632,7 +2632,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>387</v>
+        <v>529</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>88</v>
@@ -2670,7 +2670,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>387</v>
+        <v>530</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>83</v>
@@ -2709,7 +2709,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>387</v>
+        <v>531</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
@@ -2728,7 +2728,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>141</v>
       </c>
@@ -2747,7 +2747,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>387</v>
+        <v>541</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>121</v>
@@ -2769,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>145</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>387</v>
+        <v>532</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>148</v>
@@ -2824,7 +2824,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>387</v>
+        <v>533</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>152</v>
@@ -2843,7 +2843,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>154</v>
       </c>
@@ -2862,7 +2862,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>387</v>
+        <v>540</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>157</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C5C06B-A240-47DA-93EA-BB72124D8C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACB4B64-28CE-4ED6-B399-B1D8166EA5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="544">
   <si>
     <t>id</t>
   </si>
@@ -1600,6 +1600,9 @@
     <t>Vanellus chilensis</t>
   </si>
   <si>
+    <t>Benteveo.jpg</t>
+  </si>
+  <si>
     <t>Fuente.jpg</t>
   </si>
   <si>
@@ -1667,6 +1670,9 @@
   </si>
   <si>
     <t>tero.JPG</t>
+  </si>
+  <si>
+    <t>foto1</t>
   </si>
 </sst>
 </file>
@@ -1762,7 +1768,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1794,6 +1800,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2141,10 +2153,10 @@
         <v>76</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2190,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2212,7 +2224,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>83</v>
@@ -2253,7 +2265,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>88</v>
@@ -2291,7 +2303,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2330,7 +2342,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
@@ -2368,7 +2380,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>102</v>
@@ -2406,7 +2418,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>108</v>
@@ -2444,7 +2456,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>79</v>
@@ -2482,7 +2494,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
@@ -2520,7 +2532,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>121</v>
@@ -2556,7 +2568,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>121</v>
@@ -2594,7 +2606,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>79</v>
@@ -2632,7 +2644,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>88</v>
@@ -2670,7 +2682,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>83</v>
@@ -2709,7 +2721,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
@@ -2747,7 +2759,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>121</v>
@@ -2788,7 +2800,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>148</v>
@@ -2824,7 +2836,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>152</v>
@@ -2862,7 +2874,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>157</v>
@@ -3409,7 +3421,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>216</v>
       </c>
@@ -3437,7 +3449,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -3465,7 +3477,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>222</v>
       </c>
@@ -3493,7 +3505,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>225</v>
       </c>
@@ -3521,7 +3533,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>228</v>
       </c>
@@ -3549,7 +3561,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>232</v>
       </c>
@@ -3577,7 +3589,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>236</v>
       </c>
@@ -3605,7 +3617,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>240</v>
       </c>
@@ -3633,7 +3645,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>243</v>
       </c>
@@ -3661,7 +3673,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>246</v>
       </c>
@@ -3695,7 +3707,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>248</v>
       </c>
@@ -3729,7 +3741,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>251</v>
       </c>
@@ -3763,7 +3775,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>255</v>
       </c>
@@ -3797,7 +3809,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>258</v>
       </c>
@@ -3831,7 +3843,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>261</v>
       </c>
@@ -3865,7 +3877,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>263</v>
       </c>
@@ -3895,7 +3907,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>266</v>
       </c>
@@ -3963,7 +3975,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>272</v>
       </c>
@@ -3997,7 +4009,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>275</v>
       </c>
@@ -4031,7 +4043,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>277</v>
       </c>
@@ -4065,7 +4077,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>281</v>
       </c>
@@ -4095,7 +4107,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>284</v>
       </c>
@@ -4193,7 +4205,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>294</v>
       </c>
@@ -4227,7 +4239,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>296</v>
       </c>
@@ -4261,7 +4273,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>298</v>
       </c>
@@ -4295,7 +4307,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>300</v>
       </c>
@@ -4329,7 +4341,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>303</v>
       </c>
@@ -4363,7 +4375,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>305</v>
       </c>
@@ -4393,7 +4405,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>307</v>
       </c>
@@ -4427,7 +4439,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>311</v>
       </c>
@@ -4461,7 +4473,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>313</v>
       </c>
@@ -4525,7 +4537,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>317</v>
       </c>
@@ -4559,7 +4571,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>320</v>
       </c>
@@ -4625,7 +4637,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>326</v>
       </c>
@@ -4659,7 +4671,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>331</v>
       </c>
@@ -4693,7 +4705,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>334</v>
       </c>
@@ -4727,7 +4739,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>337</v>
       </c>
@@ -4757,7 +4769,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>339</v>
       </c>
@@ -4791,7 +4803,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>342</v>
       </c>
@@ -4825,7 +4837,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>344</v>
       </c>
@@ -4859,7 +4871,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>347</v>
       </c>
@@ -4893,7 +4905,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>351</v>
       </c>
@@ -4961,7 +4973,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>356</v>
       </c>
@@ -5025,7 +5037,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>361</v>
       </c>
@@ -5127,7 +5139,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>369</v>
       </c>
@@ -5161,7 +5173,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>371</v>
       </c>
@@ -5195,7 +5207,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>373</v>
       </c>
@@ -5229,7 +5241,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>375</v>
       </c>
@@ -5263,7 +5275,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>378</v>
       </c>
@@ -5302,7 +5314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A580122F-82B9-4D2E-B07E-0D8C98A0F809}">
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
@@ -5311,11 +5323,11 @@
     <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
     <col min="7" max="7" width="12.08984375" customWidth="1"/>
-    <col min="9" max="9" width="16.08984375" customWidth="1"/>
-    <col min="11" max="11" width="19.36328125" customWidth="1"/>
+    <col min="9" max="10" width="16.08984375" customWidth="1"/>
+    <col min="12" max="12" width="19.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -5343,14 +5355,17 @@
       <c r="I1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="L1" s="9" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
         <v>73</v>
       </c>
@@ -5375,9 +5390,12 @@
       <c r="J2" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="K2" s="10"/>
-    </row>
-    <row r="3" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K2" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
         <v>74</v>
       </c>
@@ -5400,11 +5418,14 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
         <v>389</v>
       </c>
@@ -5420,15 +5441,16 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J4" s="14"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
         <v>391</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>477</v>
@@ -5439,10 +5461,11 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J5" s="14"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
         <v>392</v>
       </c>
@@ -5458,12 +5481,13 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J6" s="14"/>
+      <c r="K6" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
         <v>394</v>
       </c>
@@ -5479,12 +5503,13 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
-      <c r="J7" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J7" s="14"/>
+      <c r="K7" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
         <v>396</v>
       </c>
@@ -5505,11 +5530,14 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
         <v>398</v>
       </c>
@@ -5526,9 +5554,10 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K9" s="5"/>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
         <v>400</v>
       </c>
@@ -5549,11 +5578,14 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
         <v>402</v>
       </c>
@@ -5574,11 +5606,14 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="K11" s="10"/>
-    </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="L11" s="10"/>
+    </row>
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
         <v>404</v>
       </c>
@@ -5595,9 +5630,10 @@
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
       <c r="J12" s="5"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K12" s="5"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
         <v>406</v>
       </c>
@@ -5614,9 +5650,10 @@
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K13" s="5"/>
+      <c r="L13" s="10"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
         <v>408</v>
       </c>
@@ -5633,9 +5670,10 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
       <c r="J14" s="5"/>
-      <c r="K14" s="10"/>
-    </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K14" s="5"/>
+      <c r="L14" s="10"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
         <v>410</v>
       </c>
@@ -5652,9 +5690,10 @@
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
       <c r="J15" s="5"/>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K15" s="5"/>
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
         <v>412</v>
       </c>
@@ -5671,9 +5710,10 @@
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="5"/>
-      <c r="K16" s="10"/>
-    </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K16" s="5"/>
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
         <v>414</v>
       </c>
@@ -5690,9 +5730,10 @@
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
       <c r="J17" s="5"/>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K17" s="5"/>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
         <v>416</v>
       </c>
@@ -5713,11 +5754,14 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="K18" s="10"/>
-    </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>418</v>
       </c>
@@ -5734,9 +5778,10 @@
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
       <c r="J19" s="5"/>
-      <c r="K19" s="10"/>
-    </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K19" s="5"/>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>420</v>
       </c>
@@ -5753,9 +5798,10 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
       <c r="J20" s="5"/>
-      <c r="K20" s="10"/>
-    </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K20" s="5"/>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
         <v>422</v>
       </c>
@@ -5772,9 +5818,10 @@
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
       <c r="J21" s="5"/>
-      <c r="K21" s="10"/>
-    </row>
-    <row r="22" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K21" s="5"/>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
         <v>424</v>
       </c>
@@ -5795,11 +5842,14 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
       <c r="J22" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="K22" s="10"/>
-    </row>
-    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
         <v>426</v>
       </c>
@@ -5816,9 +5866,10 @@
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
       <c r="J23" s="5"/>
-      <c r="K23" s="10"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K23" s="5"/>
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>428</v>
       </c>
@@ -5835,9 +5886,10 @@
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="10"/>
-    </row>
-    <row r="25" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K24" s="5"/>
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>430</v>
       </c>
@@ -5858,11 +5910,14 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="K25" s="10"/>
-    </row>
-    <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="L25" s="10"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>432</v>
       </c>
@@ -5879,9 +5934,10 @@
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
       <c r="J26" s="5"/>
-      <c r="K26" s="10"/>
-    </row>
-    <row r="27" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K26" s="5"/>
+      <c r="L26" s="10"/>
+    </row>
+    <row r="27" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
         <v>434</v>
       </c>
@@ -5902,11 +5958,14 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="K27" s="10"/>
-    </row>
-    <row r="28" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="L27" s="10"/>
+    </row>
+    <row r="28" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="10" t="s">
         <v>436</v>
       </c>
@@ -5923,9 +5982,10 @@
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
       <c r="J28" s="5"/>
-      <c r="K28" s="10"/>
-    </row>
-    <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K28" s="5"/>
+      <c r="L28" s="10"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
         <v>438</v>
       </c>
@@ -5942,9 +6002,10 @@
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
       <c r="J29" s="5"/>
-      <c r="K29" s="10"/>
-    </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K29" s="5"/>
+      <c r="L29" s="10"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
         <v>440</v>
       </c>
@@ -5961,9 +6022,10 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
       <c r="J30" s="5"/>
-      <c r="K30" s="10"/>
-    </row>
-    <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K30" s="5"/>
+      <c r="L30" s="10"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="10" t="s">
         <v>442</v>
       </c>
@@ -5980,9 +6042,10 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="10"/>
-    </row>
-    <row r="32" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K31" s="5"/>
+      <c r="L31" s="10"/>
+    </row>
+    <row r="32" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="10" t="s">
         <v>444</v>
       </c>
@@ -6003,11 +6066,14 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="K32" s="10"/>
-    </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="L32" s="10"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="10" t="s">
         <v>446</v>
       </c>
@@ -6024,9 +6090,10 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="10"/>
-    </row>
-    <row r="34" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K33" s="5"/>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
         <v>448</v>
       </c>
@@ -6042,12 +6109,13 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
-      <c r="J34" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="K34" s="10"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J34" s="5"/>
+      <c r="K34" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="10" t="s">
         <v>450</v>
       </c>
@@ -6064,9 +6132,10 @@
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="10"/>
-    </row>
-    <row r="36" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K35" s="5"/>
+      <c r="L35" s="10"/>
+    </row>
+    <row r="36" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
         <v>452</v>
       </c>
@@ -6087,11 +6156,14 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="K36" s="10"/>
-    </row>
-    <row r="37" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="L36" s="10"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="10" t="s">
         <v>454</v>
       </c>
@@ -6108,9 +6180,10 @@
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="10"/>
-    </row>
-    <row r="38" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K37" s="5"/>
+      <c r="L37" s="10"/>
+    </row>
+    <row r="38" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
         <v>456</v>
       </c>
@@ -6131,11 +6204,14 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="K38" s="10"/>
-    </row>
-    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="L38" s="10"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="10" t="s">
         <v>458</v>
       </c>
@@ -6152,9 +6228,10 @@
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="10"/>
-    </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K39" s="5"/>
+      <c r="L39" s="10"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="10" t="s">
         <v>460</v>
       </c>
@@ -6171,9 +6248,10 @@
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="10"/>
-    </row>
-    <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K40" s="5"/>
+      <c r="L40" s="10"/>
+    </row>
+    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
         <v>462</v>
       </c>
@@ -6194,11 +6272,14 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="K41" s="10"/>
-    </row>
-    <row r="42" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="L41" s="10"/>
+    </row>
+    <row r="42" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
         <v>464</v>
       </c>
@@ -6219,11 +6300,14 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="K42" s="10"/>
-    </row>
-    <row r="43" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="L42" s="10"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
         <v>466</v>
       </c>
@@ -6240,9 +6324,10 @@
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="10"/>
-    </row>
-    <row r="44" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K43" s="5"/>
+      <c r="L43" s="10"/>
+    </row>
+    <row r="44" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="10" t="s">
         <v>468</v>
       </c>
@@ -6258,12 +6343,13 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
-      <c r="J44" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="K44" s="10"/>
-    </row>
-    <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J44" s="5"/>
+      <c r="K44" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="L44" s="10"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="10" t="s">
         <v>470</v>
       </c>
@@ -6280,9 +6366,10 @@
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="10"/>
-    </row>
-    <row r="46" spans="1:11" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K45" s="5"/>
+      <c r="L45" s="10"/>
+    </row>
+    <row r="46" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
         <v>472</v>
       </c>
@@ -6303,11 +6390,14 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="K46" s="10"/>
-    </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="L46" s="10"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
         <v>474</v>
       </c>
@@ -6323,143 +6413,144 @@
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="10"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J48" s="5"/>
-    </row>
-    <row r="49" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J49" s="5"/>
-    </row>
-    <row r="50" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J50" s="5"/>
-    </row>
-    <row r="51" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J51" s="5"/>
-    </row>
-    <row r="52" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J52" s="5"/>
-    </row>
-    <row r="53" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J53" s="5"/>
-    </row>
-    <row r="54" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J54" s="5"/>
-    </row>
-    <row r="55" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J55" s="5"/>
-    </row>
-    <row r="56" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J56" s="5"/>
-    </row>
-    <row r="57" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J57" s="5"/>
-    </row>
-    <row r="58" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J58" s="5"/>
-    </row>
-    <row r="59" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J59" s="5"/>
-    </row>
-    <row r="60" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J60" s="5"/>
-    </row>
-    <row r="61" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J61" s="5"/>
-    </row>
-    <row r="62" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J62" s="5"/>
-    </row>
-    <row r="63" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J63" s="5"/>
-    </row>
-    <row r="64" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J64" s="5"/>
-    </row>
-    <row r="65" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J65" s="5"/>
-    </row>
-    <row r="66" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J66" s="5"/>
-    </row>
-    <row r="67" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J67" s="5"/>
-    </row>
-    <row r="68" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J68" s="5"/>
-    </row>
-    <row r="69" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J69" s="5"/>
-    </row>
-    <row r="70" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J70" s="5"/>
-    </row>
-    <row r="71" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J71" s="5"/>
-    </row>
-    <row r="72" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J72" s="5"/>
-    </row>
-    <row r="73" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J73" s="5"/>
-    </row>
-    <row r="74" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J74" s="5"/>
-    </row>
-    <row r="75" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J75" s="5"/>
-    </row>
-    <row r="76" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J76" s="5"/>
-    </row>
-    <row r="77" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J77" s="5"/>
-    </row>
-    <row r="78" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J78" s="5"/>
-    </row>
-    <row r="79" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J79" s="5"/>
-    </row>
-    <row r="80" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J80" s="5"/>
-    </row>
-    <row r="81" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J81" s="5"/>
-    </row>
-    <row r="82" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J82" s="5"/>
-    </row>
-    <row r="83" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J83" s="5"/>
-    </row>
-    <row r="84" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J84" s="5"/>
-    </row>
-    <row r="85" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J85" s="5"/>
-    </row>
-    <row r="86" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J86" s="5"/>
-    </row>
-    <row r="87" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J87" s="5"/>
-    </row>
-    <row r="88" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J88" s="5"/>
-    </row>
-    <row r="89" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J89" s="5"/>
-    </row>
-    <row r="90" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J90" s="5"/>
-    </row>
-    <row r="91" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J91" s="5"/>
-    </row>
-    <row r="92" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J92" s="5"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="10"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K48" s="5"/>
+    </row>
+    <row r="49" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K49" s="5"/>
+    </row>
+    <row r="50" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K50" s="5"/>
+    </row>
+    <row r="51" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K51" s="5"/>
+    </row>
+    <row r="52" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K53" s="5"/>
+    </row>
+    <row r="54" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K54" s="5"/>
+    </row>
+    <row r="55" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K55" s="5"/>
+    </row>
+    <row r="56" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K56" s="5"/>
+    </row>
+    <row r="57" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K57" s="5"/>
+    </row>
+    <row r="58" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K58" s="5"/>
+    </row>
+    <row r="59" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K59" s="5"/>
+    </row>
+    <row r="60" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K60" s="5"/>
+    </row>
+    <row r="61" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K62" s="5"/>
+    </row>
+    <row r="63" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K63" s="5"/>
+    </row>
+    <row r="64" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K64" s="5"/>
+    </row>
+    <row r="65" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K65" s="5"/>
+    </row>
+    <row r="66" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K66" s="5"/>
+    </row>
+    <row r="67" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K67" s="5"/>
+    </row>
+    <row r="68" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K68" s="5"/>
+    </row>
+    <row r="69" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K69" s="5"/>
+    </row>
+    <row r="70" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K70" s="5"/>
+    </row>
+    <row r="71" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K71" s="5"/>
+    </row>
+    <row r="72" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K72" s="5"/>
+    </row>
+    <row r="73" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K73" s="5"/>
+    </row>
+    <row r="74" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K75" s="5"/>
+    </row>
+    <row r="76" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K76" s="5"/>
+    </row>
+    <row r="77" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K77" s="5"/>
+    </row>
+    <row r="78" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K78" s="5"/>
+    </row>
+    <row r="79" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K79" s="5"/>
+    </row>
+    <row r="80" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K80" s="5"/>
+    </row>
+    <row r="81" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K81" s="5"/>
+    </row>
+    <row r="82" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K82" s="5"/>
+    </row>
+    <row r="83" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K83" s="5"/>
+    </row>
+    <row r="84" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K84" s="5"/>
+    </row>
+    <row r="85" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K85" s="5"/>
+    </row>
+    <row r="86" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K87" s="5"/>
+    </row>
+    <row r="88" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K88" s="5"/>
+    </row>
+    <row r="89" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K89" s="5"/>
+    </row>
+    <row r="90" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K90" s="5"/>
+    </row>
+    <row r="91" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K91" s="5"/>
+    </row>
+    <row r="92" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K92" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -6672,7 +6763,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>48</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACB4B64-28CE-4ED6-B399-B1D8166EA5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D0DDEF-A269-4CAE-B28B-743460F664E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="560">
   <si>
     <t>id</t>
   </si>
@@ -1600,9 +1600,6 @@
     <t>Vanellus chilensis</t>
   </si>
   <si>
-    <t>Benteveo.jpg</t>
-  </si>
-  <si>
     <t>Fuente.jpg</t>
   </si>
   <si>
@@ -1673,6 +1670,57 @@
   </si>
   <si>
     <t>foto1</t>
+  </si>
+  <si>
+    <t>Benteveo.JPG</t>
+  </si>
+  <si>
+    <t>zorzalcolorado.JPG</t>
+  </si>
+  <si>
+    <t>calandria.JPG</t>
+  </si>
+  <si>
+    <t>carancho.JPG</t>
+  </si>
+  <si>
+    <t>chimango.JPG</t>
+  </si>
+  <si>
+    <t>chingolo.JPG</t>
+  </si>
+  <si>
+    <t>gavilanmixto.JPG</t>
+  </si>
+  <si>
+    <t>gorrion.JPG</t>
+  </si>
+  <si>
+    <t>hornero.JPG</t>
+  </si>
+  <si>
+    <t>lechucitavizcachera.JPG</t>
+  </si>
+  <si>
+    <t>pechoamarillo.JPG</t>
+  </si>
+  <si>
+    <t>picazuro.JPG</t>
+  </si>
+  <si>
+    <t>pirincho.JPG</t>
+  </si>
+  <si>
+    <t>suiriríreal.JPG</t>
+  </si>
+  <si>
+    <t>tyrannussavana.JPG</t>
+  </si>
+  <si>
+    <t>torcaza.JPG</t>
+  </si>
+  <si>
+    <t>tordorenegrido.JPG</t>
   </si>
 </sst>
 </file>
@@ -2153,10 +2201,10 @@
         <v>76</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2202,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2224,7 +2272,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>83</v>
@@ -2265,7 +2313,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>88</v>
@@ -2303,7 +2351,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2342,7 +2390,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
@@ -2380,7 +2428,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>102</v>
@@ -2418,7 +2466,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>108</v>
@@ -2456,7 +2504,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>79</v>
@@ -2494,7 +2542,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
@@ -2532,7 +2580,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>121</v>
@@ -2568,7 +2616,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>121</v>
@@ -2606,7 +2654,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>79</v>
@@ -2644,7 +2692,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>88</v>
@@ -2682,7 +2730,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>83</v>
@@ -2721,7 +2769,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
@@ -2759,7 +2807,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>121</v>
@@ -2800,7 +2848,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>148</v>
@@ -2836,7 +2884,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>152</v>
@@ -2874,7 +2922,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>157</v>
@@ -5356,10 +5404,10 @@
         <v>63</v>
       </c>
       <c r="J1" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>543</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>388</v>
@@ -5391,7 +5439,7 @@
         <v>387</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="L2" s="10"/>
     </row>
@@ -5421,7 +5469,7 @@
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5450,7 +5498,7 @@
         <v>391</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>477</v>
@@ -5483,7 +5531,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5505,11 +5553,11 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="L7" s="10"/>
     </row>
-    <row r="8" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
         <v>396</v>
       </c>
@@ -5532,9 +5580,7 @@
       <c r="J8" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>538</v>
-      </c>
+      <c r="K8" s="5"/>
       <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5581,7 +5627,7 @@
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -5609,7 +5655,7 @@
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -5757,7 +5803,7 @@
         <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5845,7 +5891,7 @@
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -5913,7 +5959,7 @@
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -5961,7 +6007,7 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6069,7 +6115,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6111,7 +6157,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6159,7 +6205,7 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6207,7 +6253,7 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6275,7 +6321,7 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6303,7 +6349,7 @@
         <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6345,7 +6391,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="L44" s="10"/>
     </row>
@@ -6393,7 +6439,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="L46" s="10"/>
     </row>
@@ -6763,7 +6809,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>48</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D0DDEF-A269-4CAE-B28B-743460F664E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10D845B-EE0B-41D7-809D-F27418820A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1696,9 +1696,6 @@
     <t>gorrion.JPG</t>
   </si>
   <si>
-    <t>hornero.JPG</t>
-  </si>
-  <si>
     <t>lechucitavizcachera.JPG</t>
   </si>
   <si>
@@ -1721,6 +1718,9 @@
   </si>
   <si>
     <t>tordorenegrido.JPG</t>
+  </si>
+  <si>
+    <t>Hornero.JPG</t>
   </si>
 </sst>
 </file>
@@ -5959,7 +5959,7 @@
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6007,7 +6007,7 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6115,7 +6115,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6157,7 +6157,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6205,7 +6205,7 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6253,7 +6253,7 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6349,7 +6349,7 @@
         <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6391,7 +6391,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L44" s="10"/>
     </row>
@@ -6439,7 +6439,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10D845B-EE0B-41D7-809D-F27418820A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A39067-CAD1-4F3C-ACDA-1E55BC933067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="561">
   <si>
     <t>id</t>
   </si>
@@ -1615,6 +1615,9 @@
     <t>Cabecita negra</t>
   </si>
   <si>
+    <t>Torcaza.JPG</t>
+  </si>
+  <si>
     <t>gavilanmixto.jpg</t>
   </si>
   <si>
@@ -1675,52 +1678,52 @@
     <t>Benteveo.JPG</t>
   </si>
   <si>
-    <t>zorzalcolorado.JPG</t>
-  </si>
-  <si>
-    <t>calandria.JPG</t>
-  </si>
-  <si>
-    <t>carancho.JPG</t>
-  </si>
-  <si>
-    <t>chimango.JPG</t>
-  </si>
-  <si>
-    <t>chingolo.JPG</t>
-  </si>
-  <si>
-    <t>gavilanmixto.JPG</t>
-  </si>
-  <si>
-    <t>gorrion.JPG</t>
-  </si>
-  <si>
-    <t>lechucitavizcachera.JPG</t>
-  </si>
-  <si>
-    <t>pechoamarillo.JPG</t>
-  </si>
-  <si>
-    <t>picazuro.JPG</t>
-  </si>
-  <si>
-    <t>pirincho.JPG</t>
-  </si>
-  <si>
-    <t>suiriríreal.JPG</t>
-  </si>
-  <si>
-    <t>tyrannussavana.JPG</t>
-  </si>
-  <si>
-    <t>torcaza.JPG</t>
-  </si>
-  <si>
-    <t>tordorenegrido.JPG</t>
-  </si>
-  <si>
     <t>Hornero.JPG</t>
+  </si>
+  <si>
+    <t>Zorzalcolorado.JPG</t>
+  </si>
+  <si>
+    <t>Calandria.JPG</t>
+  </si>
+  <si>
+    <t>Carancho.JPG</t>
+  </si>
+  <si>
+    <t>Chimango.JPG</t>
+  </si>
+  <si>
+    <t>Chingolo.JPG</t>
+  </si>
+  <si>
+    <t>Gavilanmixto.JPG</t>
+  </si>
+  <si>
+    <t>Gorrion.JPG</t>
+  </si>
+  <si>
+    <t>Lechucitavizcachera.JPG</t>
+  </si>
+  <si>
+    <t>Pechoamarillo.JPG</t>
+  </si>
+  <si>
+    <t>Picazuro.JPG</t>
+  </si>
+  <si>
+    <t>Pirincho.JPG</t>
+  </si>
+  <si>
+    <t>Suiriríreal.JPG</t>
+  </si>
+  <si>
+    <t>Tero.JPG</t>
+  </si>
+  <si>
+    <t>Tyrannussavana.JPG</t>
+  </si>
+  <si>
+    <t>Tordorenegrido.JPG</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>83</v>
@@ -2313,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>88</v>
@@ -2351,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2390,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
@@ -2428,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>102</v>
@@ -2466,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>108</v>
@@ -2504,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>79</v>
@@ -2542,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
@@ -2580,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>121</v>
@@ -2616,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>121</v>
@@ -2654,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>79</v>
@@ -2692,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>88</v>
@@ -2730,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>83</v>
@@ -2769,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
@@ -2807,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>121</v>
@@ -2848,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>148</v>
@@ -2884,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>152</v>
@@ -2922,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>157</v>
@@ -5404,7 +5407,7 @@
         <v>63</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5439,7 +5442,7 @@
         <v>387</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L2" s="10"/>
     </row>
@@ -5469,7 +5472,7 @@
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5531,7 +5534,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5553,7 +5556,7 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L7" s="10"/>
     </row>
@@ -5627,7 +5630,7 @@
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -5655,7 +5658,7 @@
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -5803,7 +5806,7 @@
         <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5891,7 +5894,7 @@
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -5959,7 +5962,7 @@
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6007,7 +6010,7 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6115,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6157,7 +6160,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6205,7 +6208,7 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6253,7 +6256,7 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6321,7 +6324,7 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6349,7 +6352,7 @@
         <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6391,7 +6394,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="L44" s="10"/>
     </row>
@@ -6439,7 +6442,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A39067-CAD1-4F3C-ACDA-1E55BC933067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB55DCD-D803-42F8-904E-588CD668EC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1681,9 +1681,6 @@
     <t>Hornero.JPG</t>
   </si>
   <si>
-    <t>Zorzalcolorado.JPG</t>
-  </si>
-  <si>
     <t>Calandria.JPG</t>
   </si>
   <si>
@@ -1702,12 +1699,6 @@
     <t>Gorrion.JPG</t>
   </si>
   <si>
-    <t>Lechucitavizcachera.JPG</t>
-  </si>
-  <si>
-    <t>Pechoamarillo.JPG</t>
-  </si>
-  <si>
     <t>Picazuro.JPG</t>
   </si>
   <si>
@@ -1720,10 +1711,19 @@
     <t>Tero.JPG</t>
   </si>
   <si>
-    <t>Tyrannussavana.JPG</t>
-  </si>
-  <si>
-    <t>Tordorenegrido.JPG</t>
+    <t>PechoAmarillo.JPG</t>
+  </si>
+  <si>
+    <t>TyrannusSavana.JPG</t>
+  </si>
+  <si>
+    <t>TordoRenegrido.JPG</t>
+  </si>
+  <si>
+    <t>ZorzalColorado.JPG</t>
+  </si>
+  <si>
+    <t>LechucitaVizcachera.JPG</t>
   </si>
 </sst>
 </file>
@@ -5472,7 +5472,7 @@
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5534,7 +5534,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5556,7 +5556,7 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L7" s="10"/>
     </row>
@@ -5630,7 +5630,7 @@
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -5658,7 +5658,7 @@
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -5806,7 +5806,7 @@
         <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5894,7 +5894,7 @@
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -6010,7 +6010,7 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6118,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6256,7 +6256,7 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6324,7 +6324,7 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6352,7 +6352,7 @@
         <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB55DCD-D803-42F8-904E-588CD668EC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC56FA5-E116-4963-BFA7-3CF187B0264D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1600,6 +1600,9 @@
     <t>Vanellus chilensis</t>
   </si>
   <si>
+    <t>Benteveo.jpg</t>
+  </si>
+  <si>
     <t>Fuente.jpg</t>
   </si>
   <si>
@@ -1675,9 +1678,6 @@
     <t>foto1</t>
   </si>
   <si>
-    <t>Benteveo.JPG</t>
-  </si>
-  <si>
     <t>Hornero.JPG</t>
   </si>
   <si>
@@ -1693,12 +1693,15 @@
     <t>Chingolo.JPG</t>
   </si>
   <si>
-    <t>Gavilanmixto.JPG</t>
-  </si>
-  <si>
     <t>Gorrion.JPG</t>
   </si>
   <si>
+    <t>Lechucitavizcachera.JPG</t>
+  </si>
+  <si>
+    <t>Pechoamarillo.JPG</t>
+  </si>
+  <si>
     <t>Picazuro.JPG</t>
   </si>
   <si>
@@ -1711,9 +1714,6 @@
     <t>Tero.JPG</t>
   </si>
   <si>
-    <t>PechoAmarillo.JPG</t>
-  </si>
-  <si>
     <t>TyrannusSavana.JPG</t>
   </si>
   <si>
@@ -1723,7 +1723,7 @@
     <t>ZorzalColorado.JPG</t>
   </si>
   <si>
-    <t>LechucitaVizcachera.JPG</t>
+    <t>GavilanMixto.JPG</t>
   </si>
 </sst>
 </file>
@@ -2204,10 +2204,10 @@
         <v>76</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>83</v>
@@ -2316,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>88</v>
@@ -2354,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2393,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
@@ -2431,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>102</v>
@@ -2469,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>108</v>
@@ -2507,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>79</v>
@@ -2545,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
@@ -2583,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>121</v>
@@ -2619,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>121</v>
@@ -2657,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>79</v>
@@ -2695,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>88</v>
@@ -2733,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>83</v>
@@ -2772,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
@@ -2810,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>121</v>
@@ -2851,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>148</v>
@@ -2887,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>152</v>
@@ -2925,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>157</v>
@@ -5407,7 +5407,7 @@
         <v>63</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5442,7 +5442,7 @@
         <v>387</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="L2" s="10"/>
     </row>
@@ -5501,7 +5501,7 @@
         <v>391</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>477</v>
@@ -5806,7 +5806,7 @@
         <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5894,7 +5894,7 @@
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -6010,7 +6010,7 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6118,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6256,7 +6256,7 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6324,7 +6324,7 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6394,7 +6394,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L44" s="10"/>
     </row>
@@ -6812,7 +6812,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>48</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC56FA5-E116-4963-BFA7-3CF187B0264D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0716534B-38F3-426C-B9DD-D987F399C0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1603,6 +1603,12 @@
     <t>Benteveo.jpg</t>
   </si>
   <si>
+    <t>TyrannusSavana.jpg</t>
+  </si>
+  <si>
+    <t>GavilanMixto.jpg</t>
+  </si>
+  <si>
     <t>Fuente.jpg</t>
   </si>
   <si>
@@ -1681,6 +1687,9 @@
     <t>Hornero.JPG</t>
   </si>
   <si>
+    <t>Zorzalcolorado.JPG</t>
+  </si>
+  <si>
     <t>Calandria.JPG</t>
   </si>
   <si>
@@ -1699,9 +1708,6 @@
     <t>Lechucitavizcachera.JPG</t>
   </si>
   <si>
-    <t>Pechoamarillo.JPG</t>
-  </si>
-  <si>
     <t>Picazuro.JPG</t>
   </si>
   <si>
@@ -1714,16 +1720,10 @@
     <t>Tero.JPG</t>
   </si>
   <si>
-    <t>TyrannusSavana.JPG</t>
+    <t>PechoAmarillo.JPG</t>
   </si>
   <si>
     <t>TordoRenegrido.JPG</t>
-  </si>
-  <si>
-    <t>ZorzalColorado.JPG</t>
-  </si>
-  <si>
-    <t>GavilanMixto.JPG</t>
   </si>
 </sst>
 </file>
@@ -2204,10 +2204,10 @@
         <v>76</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>83</v>
@@ -2316,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>88</v>
@@ -2354,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2393,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
@@ -2431,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>102</v>
@@ -2469,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>108</v>
@@ -2507,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>79</v>
@@ -2545,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
@@ -2583,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>121</v>
@@ -2619,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>121</v>
@@ -2657,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>79</v>
@@ -2695,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>88</v>
@@ -2733,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>83</v>
@@ -2772,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
@@ -2810,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>121</v>
@@ -2851,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>148</v>
@@ -2887,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>152</v>
@@ -2925,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>157</v>
@@ -5407,7 +5407,7 @@
         <v>63</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5472,7 +5472,7 @@
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5501,7 +5501,7 @@
         <v>391</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>477</v>
@@ -5534,7 +5534,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5556,7 +5556,7 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L7" s="10"/>
     </row>
@@ -5630,7 +5630,7 @@
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -5658,7 +5658,7 @@
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -5806,7 +5806,7 @@
         <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5894,7 +5894,7 @@
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6010,7 +6010,7 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6118,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6256,7 +6256,7 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6324,7 +6324,7 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6352,7 +6352,7 @@
         <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6394,7 +6394,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L44" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L46" s="10"/>
     </row>
@@ -6812,7 +6812,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>48</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0716534B-38F3-426C-B9DD-D987F399C0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D75B9-A079-4725-8C44-FACE82B63DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1705,9 +1705,6 @@
     <t>Gorrion.JPG</t>
   </si>
   <si>
-    <t>Lechucitavizcachera.JPG</t>
-  </si>
-  <si>
     <t>Picazuro.JPG</t>
   </si>
   <si>
@@ -1724,6 +1721,9 @@
   </si>
   <si>
     <t>TordoRenegrido.JPG</t>
+  </si>
+  <si>
+    <t>LechucitaVizcachera.JPG</t>
   </si>
 </sst>
 </file>
@@ -6010,7 +6010,7 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6118,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6256,7 +6256,7 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6324,7 +6324,7 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D75B9-A079-4725-8C44-FACE82B63DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644EBA37-4418-4288-A1D6-5000B383C11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1717,10 +1717,10 @@
     <t>Tero.JPG</t>
   </si>
   <si>
+    <t>Tordorenegrido.JPG</t>
+  </si>
+  <si>
     <t>PechoAmarillo.JPG</t>
-  </si>
-  <si>
-    <t>TordoRenegrido.JPG</t>
   </si>
   <si>
     <t>LechucitaVizcachera.JPG</t>
@@ -6118,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644EBA37-4418-4288-A1D6-5000B383C11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CE65C3-4D19-42AB-8ABF-EF02BD6375AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1717,10 +1717,10 @@
     <t>Tero.JPG</t>
   </si>
   <si>
-    <t>Tordorenegrido.JPG</t>
-  </si>
-  <si>
     <t>PechoAmarillo.JPG</t>
+  </si>
+  <si>
+    <t>TordoRenegrido.JPG</t>
   </si>
   <si>
     <t>LechucitaVizcachera.JPG</t>
@@ -6118,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CE65C3-4D19-42AB-8ABF-EF02BD6375AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1DBBBB-E1A0-493E-8531-4688281FD048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1717,10 +1717,10 @@
     <t>Tero.JPG</t>
   </si>
   <si>
+    <t>Tordorenegrido.JPG</t>
+  </si>
+  <si>
     <t>PechoAmarillo.JPG</t>
-  </si>
-  <si>
-    <t>TordoRenegrido.JPG</t>
   </si>
   <si>
     <t>LechucitaVizcachera.JPG</t>
@@ -6118,7 +6118,7 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L46" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1DBBBB-E1A0-493E-8531-4688281FD048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600D3F2F-8828-4584-9D0C-A8D1B1B489F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,9 +112,6 @@
     <t>Acceso principal</t>
   </si>
   <si>
-    <t>entrada.jpg</t>
-  </si>
-  <si>
     <t>P002</t>
   </si>
   <si>
@@ -1609,9 +1606,6 @@
     <t>GavilanMixto.jpg</t>
   </si>
   <si>
-    <t>Fuente.jpg</t>
-  </si>
-  <si>
     <t>destacado</t>
   </si>
   <si>
@@ -1724,6 +1718,12 @@
   </si>
   <si>
     <t>LechucitaVizcachera.JPG</t>
+  </si>
+  <si>
+    <t>Fuente.JPG</t>
+  </si>
+  <si>
+    <t>entrada.JPG</t>
   </si>
 </sst>
 </file>
@@ -2150,7 +2150,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -2174,51 +2174,51 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="R1" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="D2" s="5">
         <v>-57.680154000000002</v>
@@ -2231,13 +2231,13 @@
         <v>2004</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2247,24 +2247,24 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S2">
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="D3" s="5">
         <v>-57.680520999999999</v>
@@ -2275,13 +2275,13 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -2291,7 +2291,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -2299,13 +2299,13 @@
     </row>
     <row r="4" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="D4" s="5">
         <v>-57.680554999999998</v>
@@ -2316,13 +2316,13 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -2332,18 +2332,18 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="D5" s="5">
         <v>-57.680684999999997</v>
@@ -2354,11 +2354,11 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -2368,7 +2368,7 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S5">
         <v>1</v>
@@ -2376,13 +2376,13 @@
     </row>
     <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D6" s="5">
         <v>-57.680737000000001</v>
@@ -2393,10 +2393,10 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>9</v>
@@ -2409,18 +2409,18 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D7" s="5">
         <v>-57.680855999999999</v>
@@ -2431,13 +2431,13 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -2447,18 +2447,18 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="D8" s="5">
         <v>-57.681120999999997</v>
@@ -2469,13 +2469,13 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -2485,18 +2485,18 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="D9" s="5">
         <v>-57.680990000000001</v>
@@ -2507,13 +2507,13 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -2523,18 +2523,18 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="D10" s="5">
         <v>-57.680906999999998</v>
@@ -2545,13 +2545,13 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -2561,18 +2561,18 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" s="5">
         <v>-57.680894000000002</v>
@@ -2583,13 +2583,13 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -2599,16 +2599,16 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D12" s="5">
         <v>-57.680571999999998</v>
@@ -2619,13 +2619,13 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -2635,18 +2635,18 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="D13" s="5">
         <v>-57.680430000000001</v>
@@ -2657,13 +2657,13 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -2673,18 +2673,18 @@
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="D14" s="5">
         <v>-57.679865999999997</v>
@@ -2695,13 +2695,13 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="I14" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -2711,18 +2711,18 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
       <c r="R14" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="D15" s="5">
         <v>-57.679765000000003</v>
@@ -2733,13 +2733,13 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -2749,7 +2749,7 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S15">
         <v>1</v>
@@ -2757,11 +2757,11 @@
     </row>
     <row r="16" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D16" s="5">
         <v>-57.679769</v>
@@ -2772,13 +2772,13 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -2788,18 +2788,18 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="D17" s="5">
         <v>-57.679966999999998</v>
@@ -2810,13 +2810,13 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
@@ -2826,7 +2826,7 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S17">
         <v>1</v>
@@ -2834,13 +2834,13 @@
     </row>
     <row r="18" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="D18" s="5">
         <v>-57.680100000000003</v>
@@ -2851,13 +2851,13 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -2867,16 +2867,16 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D19" s="5">
         <v>-57.680508000000003</v>
@@ -2887,13 +2887,13 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
@@ -2903,18 +2903,18 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="D20" s="5">
         <v>-57.680231999999997</v>
@@ -2925,13 +2925,13 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
@@ -2941,18 +2941,18 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="D21" s="5">
         <v>-57.680526999999998</v>
@@ -2963,13 +2963,13 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -2979,18 +2979,18 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="D22" s="5">
         <v>-57.680582999999999</v>
@@ -3001,13 +3001,13 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -3017,18 +3017,18 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="R22" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="D23" s="5">
         <v>-57.680885000000004</v>
@@ -3039,13 +3039,13 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -3055,16 +3055,16 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
       <c r="R23" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D24" s="5">
         <v>-57.681063999999999</v>
@@ -3075,13 +3075,13 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -3091,16 +3091,16 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D25" s="5">
         <v>-57.681113000000003</v>
@@ -3111,13 +3111,13 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
@@ -3127,18 +3127,18 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D26" s="5">
         <v>-57.681260000000002</v>
@@ -3149,13 +3149,13 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I26" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -3165,18 +3165,18 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="D27" s="5">
         <v>-57.680408999999997</v>
@@ -3187,13 +3187,13 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I27" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
@@ -3203,18 +3203,18 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="D28" s="5">
         <v>-57.679651</v>
@@ -3225,13 +3225,13 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -3241,18 +3241,18 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="D29" s="5">
         <v>-57.679448999999998</v>
@@ -3263,13 +3263,13 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
@@ -3279,18 +3279,18 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
       <c r="R29" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="D30" s="5">
         <v>-57.679357000000003</v>
@@ -3301,13 +3301,13 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
@@ -3317,18 +3317,18 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="D31" s="5">
         <v>-57.679296999999998</v>
@@ -3339,13 +3339,13 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
@@ -3355,18 +3355,18 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="D32" s="5">
         <v>-57.679557000000003</v>
@@ -3377,10 +3377,10 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>9</v>
@@ -3393,18 +3393,18 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>206</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="D33" s="5">
         <v>-57.679313999999998</v>
@@ -3415,10 +3415,10 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>9</v>
@@ -3431,18 +3431,18 @@
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
       <c r="R33" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="D34" s="5">
         <v>-57.679395</v>
@@ -3453,13 +3453,13 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
@@ -3469,16 +3469,16 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="R34" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -3486,7 +3486,7 @@
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -3497,16 +3497,16 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
       <c r="R35" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -3514,7 +3514,7 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -3525,16 +3525,16 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
       <c r="R36" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -3542,7 +3542,7 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -3553,16 +3553,16 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
       <c r="R37" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -3570,7 +3570,7 @@
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -3581,16 +3581,16 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
       <c r="R38" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -3598,7 +3598,7 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -3609,16 +3609,16 @@
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
       <c r="R39" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -3626,7 +3626,7 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
@@ -3637,16 +3637,16 @@
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
       <c r="R40" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -3654,7 +3654,7 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -3665,16 +3665,16 @@
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
       <c r="R41" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -3682,7 +3682,7 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
@@ -3693,16 +3693,16 @@
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
       <c r="R42" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -3710,7 +3710,7 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
@@ -3721,16 +3721,16 @@
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
       <c r="R43" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D44" s="5">
         <v>-57.682848999999997</v>
@@ -3742,10 +3742,10 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J44" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
@@ -3755,16 +3755,16 @@
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
       <c r="R44" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="5">
         <v>-57.682864000000002</v>
@@ -3776,10 +3776,10 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
@@ -3789,16 +3789,16 @@
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
       <c r="R45" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D46" s="5">
         <v>-57.682738999999998</v>
@@ -3810,10 +3810,10 @@
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
@@ -3823,16 +3823,16 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
       <c r="R46" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D47" s="5">
         <v>-57.682726000000002</v>
@@ -3844,10 +3844,10 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
@@ -3857,16 +3857,16 @@
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
       <c r="R47" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D48" s="5">
         <v>-57.682654999999997</v>
@@ -3878,7 +3878,7 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>9</v>
@@ -3891,16 +3891,16 @@
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
       <c r="R48" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D49" s="5">
         <v>-57.682537000000004</v>
@@ -3912,7 +3912,7 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>9</v>
@@ -3925,16 +3925,16 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
       <c r="R49" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D50" s="5">
         <v>-57.682471999999997</v>
@@ -3955,16 +3955,16 @@
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
       <c r="R50" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D51" s="5">
         <v>-57.682428999999999</v>
@@ -3976,7 +3976,7 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>9</v>
@@ -3989,16 +3989,16 @@
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
       <c r="R51" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D52" s="5">
         <v>-57.682437999999998</v>
@@ -4010,10 +4010,10 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
@@ -4023,16 +4023,16 @@
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
       <c r="R52" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D53" s="5">
         <v>-57.682395</v>
@@ -4044,10 +4044,10 @@
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
@@ -4057,16 +4057,16 @@
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
       <c r="R53" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D54" s="5">
         <v>-57.682130000000001</v>
@@ -4078,10 +4078,10 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
@@ -4091,16 +4091,16 @@
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
       <c r="R54" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D55" s="5">
         <v>-57.682079999999999</v>
@@ -4112,7 +4112,7 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>9</v>
@@ -4125,16 +4125,16 @@
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
       <c r="R55" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D56" s="5">
         <v>-57.681980000000003</v>
@@ -4155,16 +4155,16 @@
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
       <c r="R56" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D57" s="5">
         <v>-57.681933000000001</v>
@@ -4176,7 +4176,7 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>9</v>
@@ -4189,16 +4189,16 @@
       <c r="P57" s="5"/>
       <c r="Q57" s="5"/>
       <c r="R57" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D58" s="5">
         <v>-57.681750000000001</v>
@@ -4219,16 +4219,16 @@
       <c r="P58" s="5"/>
       <c r="Q58" s="5"/>
       <c r="R58" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D59" s="5">
         <v>-57.681742999999997</v>
@@ -4240,10 +4240,10 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
@@ -4253,16 +4253,16 @@
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
       <c r="R59" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D60" s="5">
         <v>-57.681628000000003</v>
@@ -4274,10 +4274,10 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J60" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
@@ -4287,16 +4287,16 @@
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
       <c r="R60" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D61" s="5">
         <v>-57.681649</v>
@@ -4308,10 +4308,10 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
@@ -4321,16 +4321,16 @@
       <c r="P61" s="5"/>
       <c r="Q61" s="5"/>
       <c r="R61" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D62" s="5">
         <v>-57.681576999999997</v>
@@ -4342,10 +4342,10 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
@@ -4355,16 +4355,16 @@
       <c r="P62" s="5"/>
       <c r="Q62" s="5"/>
       <c r="R62" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D63" s="5">
         <v>-57.681601000000001</v>
@@ -4376,7 +4376,7 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>9</v>
@@ -4389,16 +4389,16 @@
       <c r="P63" s="5"/>
       <c r="Q63" s="5"/>
       <c r="R63" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D64" s="5">
         <v>-57.681418000000001</v>
@@ -4410,7 +4410,7 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>9</v>
@@ -4423,16 +4423,16 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="5"/>
       <c r="R64" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D65" s="5">
         <v>-57.681415000000001</v>
@@ -4453,16 +4453,16 @@
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
       <c r="R65" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D66" s="5">
         <v>-57.681348999999997</v>
@@ -4474,10 +4474,10 @@
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
@@ -4487,16 +4487,16 @@
       <c r="P66" s="5"/>
       <c r="Q66" s="5"/>
       <c r="R66" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D67" s="5">
         <v>-57.681176999999998</v>
@@ -4508,10 +4508,10 @@
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
@@ -4521,16 +4521,16 @@
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
       <c r="R67" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D68" s="5">
         <v>-57.681095999999997</v>
@@ -4542,7 +4542,7 @@
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>9</v>
@@ -4555,16 +4555,16 @@
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
       <c r="R68" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D69" s="5">
         <v>-57.680937999999998</v>
@@ -4585,16 +4585,16 @@
       <c r="P69" s="5"/>
       <c r="Q69" s="5"/>
       <c r="R69" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D70" s="5">
         <v>-57.680618000000003</v>
@@ -4606,10 +4606,10 @@
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
@@ -4619,16 +4619,16 @@
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
       <c r="R70" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D71" s="5">
         <v>-57.680501</v>
@@ -4640,7 +4640,7 @@
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
@@ -4651,16 +4651,16 @@
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
       <c r="R71" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D72" s="5">
         <v>-57.680428999999997</v>
@@ -4672,10 +4672,10 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
@@ -4685,16 +4685,16 @@
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
       <c r="R72" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D73" s="5">
         <v>-57.680601000000003</v>
@@ -4706,10 +4706,10 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="J73" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>329</v>
       </c>
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
@@ -4719,16 +4719,16 @@
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
       <c r="R73" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D74" s="5">
         <v>-57.680985</v>
@@ -4740,10 +4740,10 @@
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="J74" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="J74" s="5" t="s">
-        <v>329</v>
       </c>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
@@ -4753,16 +4753,16 @@
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
       <c r="R74" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D75" s="5">
         <v>-57.681064999999997</v>
@@ -4774,7 +4774,7 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>9</v>
@@ -4787,16 +4787,16 @@
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
       <c r="R75" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D76" s="5">
         <v>-57.681297000000001</v>
@@ -4817,12 +4817,12 @@
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
       <c r="R76" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
@@ -4838,7 +4838,7 @@
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
       <c r="I77" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>9</v>
@@ -4851,16 +4851,16 @@
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
       <c r="R77" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D78" s="5">
         <v>-57.681655999999997</v>
@@ -4872,10 +4872,10 @@
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
@@ -4885,16 +4885,16 @@
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
       <c r="R78" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D79" s="5">
         <v>-57.682174000000003</v>
@@ -4906,10 +4906,10 @@
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
@@ -4919,16 +4919,16 @@
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
       <c r="R79" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D80" s="5">
         <v>-57.682552000000001</v>
@@ -4940,10 +4940,10 @@
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
@@ -4953,16 +4953,16 @@
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
       <c r="R80" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D81" s="5">
         <v>-57.682554000000003</v>
@@ -4974,10 +4974,10 @@
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
@@ -4987,16 +4987,16 @@
       <c r="P81" s="5"/>
       <c r="Q81" s="5"/>
       <c r="R81" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D82" s="5">
         <v>-57.682775999999997</v>
@@ -5008,10 +5008,10 @@
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K82" s="5"/>
       <c r="L82" s="5"/>
@@ -5021,16 +5021,16 @@
       <c r="P82" s="5"/>
       <c r="Q82" s="5"/>
       <c r="R82" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D83" s="5">
         <v>-57.68253</v>
@@ -5051,16 +5051,16 @@
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
       <c r="R83" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D84" s="5">
         <v>-57.681094999999999</v>
@@ -5072,10 +5072,10 @@
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K84" s="5"/>
       <c r="L84" s="5"/>
@@ -5085,16 +5085,16 @@
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
       <c r="R84" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D85" s="5">
         <v>-57.681427999999997</v>
@@ -5106,10 +5106,10 @@
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K85" s="5"/>
       <c r="L85" s="5"/>
@@ -5119,16 +5119,16 @@
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
       <c r="R85" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="86" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D86" s="5">
         <v>-57.681583000000003</v>
@@ -5140,10 +5140,10 @@
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
@@ -5153,16 +5153,16 @@
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
       <c r="R86" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D87" s="5">
         <v>-57.681491999999999</v>
@@ -5174,10 +5174,10 @@
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
@@ -5187,16 +5187,16 @@
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
       <c r="R87" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D88" s="5">
         <v>-57.681479000000003</v>
@@ -5208,10 +5208,10 @@
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K88" s="5"/>
       <c r="L88" s="5"/>
@@ -5221,16 +5221,16 @@
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
       <c r="R88" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D89" s="5">
         <v>-57.681835</v>
@@ -5242,10 +5242,10 @@
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
@@ -5255,16 +5255,16 @@
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
       <c r="R89" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="90" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D90" s="5">
         <v>-57.681941000000002</v>
@@ -5276,10 +5276,10 @@
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K90" s="5"/>
       <c r="L90" s="5"/>
@@ -5289,16 +5289,16 @@
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
       <c r="R90" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D91" s="5">
         <v>-57.680911999999999</v>
@@ -5310,10 +5310,10 @@
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J91" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K91" s="5"/>
       <c r="L91" s="5"/>
@@ -5323,16 +5323,16 @@
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
       <c r="R91" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D92" s="5">
         <v>-57.680594999999997</v>
@@ -5353,7 +5353,7 @@
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
       <c r="R92" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -5398,27 +5398,27 @@
         <v>11</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="J1" s="13" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>12</v>
@@ -5439,16 +5439,16 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>14</v>
@@ -5469,22 +5469,22 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>390</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -5498,13 +5498,13 @@
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -5518,13 +5518,13 @@
     </row>
     <row r="6" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>393</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -5534,19 +5534,19 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>395</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -5556,19 +5556,19 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>397</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D8" s="10">
         <v>-57.680219000000001</v>
@@ -5581,20 +5581,20 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>399</v>
-      </c>
       <c r="C9" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -5608,13 +5608,13 @@
     </row>
     <row r="10" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>401</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D10" s="10">
         <v>-57.679960999999999</v>
@@ -5627,22 +5627,22 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>403</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D11" s="10">
         <v>-57.681131000000001</v>
@@ -5655,22 +5655,22 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>405</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -5684,13 +5684,13 @@
     </row>
     <row r="13" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>407</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -5704,13 +5704,13 @@
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>409</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -5724,13 +5724,13 @@
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>411</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -5744,13 +5744,13 @@
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>413</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -5764,13 +5764,13 @@
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>415</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -5784,13 +5784,13 @@
     </row>
     <row r="18" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>417</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D18" s="10">
         <v>-57.683276999999997</v>
@@ -5803,22 +5803,22 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>419</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -5832,13 +5832,13 @@
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>421</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -5852,13 +5852,13 @@
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>423</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -5872,13 +5872,13 @@
     </row>
     <row r="22" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>425</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D22" s="10">
         <v>-57.682054000000001</v>
@@ -5891,22 +5891,22 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
       <c r="J22" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="L22" s="10"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>427</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -5920,13 +5920,13 @@
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>429</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -5940,13 +5940,13 @@
     </row>
     <row r="25" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>431</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D25" s="10">
         <v>-57.679361</v>
@@ -5959,22 +5959,22 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>433</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -5988,13 +5988,13 @@
     </row>
     <row r="27" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>435</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D27" s="10">
         <v>-57.684317</v>
@@ -6007,22 +6007,22 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>437</v>
-      </c>
       <c r="C28" s="11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -6036,13 +6036,13 @@
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>439</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -6056,13 +6056,13 @@
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>441</v>
-      </c>
       <c r="C30" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
@@ -6076,13 +6076,13 @@
     </row>
     <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>443</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
@@ -6096,13 +6096,13 @@
     </row>
     <row r="32" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>445</v>
-      </c>
       <c r="C32" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D32" s="10">
         <v>-57.682547</v>
@@ -6115,22 +6115,22 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>447</v>
-      </c>
       <c r="C33" s="11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -6144,13 +6144,13 @@
     </row>
     <row r="34" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>449</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -6160,19 +6160,19 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>451</v>
-      </c>
       <c r="C35" s="11" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
@@ -6186,13 +6186,13 @@
     </row>
     <row r="36" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>453</v>
-      </c>
       <c r="C36" s="11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D36" s="10">
         <v>-57.682281000000003</v>
@@ -6205,22 +6205,22 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="L36" s="10"/>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>455</v>
-      </c>
       <c r="C37" s="11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -6234,13 +6234,13 @@
     </row>
     <row r="38" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>457</v>
-      </c>
       <c r="C38" s="11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D38" s="10">
         <v>-57.685510999999998</v>
@@ -6253,22 +6253,22 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L38" s="10"/>
     </row>
     <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B39" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>459</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -6282,13 +6282,13 @@
     </row>
     <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>461</v>
-      </c>
       <c r="C40" s="11" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -6302,13 +6302,13 @@
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>463</v>
-      </c>
       <c r="C41" s="11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D41" s="10">
         <v>-57.681240000000003</v>
@@ -6321,22 +6321,22 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L41" s="10"/>
     </row>
     <row r="42" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>465</v>
-      </c>
       <c r="C42" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D42" s="10">
         <v>-57.683684</v>
@@ -6349,22 +6349,22 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L42" s="10"/>
     </row>
     <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>467</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -6378,13 +6378,13 @@
     </row>
     <row r="44" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>469</v>
-      </c>
       <c r="C44" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
@@ -6394,19 +6394,19 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L44" s="10"/>
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>471</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
@@ -6420,13 +6420,13 @@
     </row>
     <row r="46" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="B46" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>473</v>
-      </c>
       <c r="C46" s="11" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D46" s="10">
         <v>-57.682558</v>
@@ -6439,22 +6439,22 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="L46" s="10"/>
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>475</v>
-      </c>
       <c r="C47" s="11" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
@@ -6619,7 +6619,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>16</v>
@@ -6628,42 +6628,42 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2">
         <v>900</v>
@@ -6672,10 +6672,10 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>20</v>
@@ -6684,24 +6684,24 @@
         <v>20</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D3" s="2">
         <v>600</v>
@@ -6710,25 +6710,25 @@
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -6777,7 +6777,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -6789,7 +6789,7 @@
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>560</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -6797,13 +6797,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D3" s="8">
         <v>-57.679949999999998</v>
@@ -6812,21 +6812,21 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D4" s="8">
         <v>-57.680886000000001</v>
@@ -6835,21 +6835,21 @@
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="D5" s="8">
         <v>-57.680562999999999</v>
@@ -6894,16 +6894,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -6917,10 +6917,10 @@
         <v>46275</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -6934,10 +6934,10 @@
         <v>46320</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600D3F2F-8828-4584-9D0C-A8D1B1B489F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D86AA5-943B-413B-8C32-E7482C718838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -1606,6 +1606,9 @@
     <t>GavilanMixto.jpg</t>
   </si>
   <si>
+    <t>Fuente.jpg</t>
+  </si>
+  <si>
     <t>destacado</t>
   </si>
   <si>
@@ -1718,9 +1721,6 @@
   </si>
   <si>
     <t>LechucitaVizcachera.JPG</t>
-  </si>
-  <si>
-    <t>Fuente.JPG</t>
   </si>
   <si>
     <t>entrada.JPG</t>
@@ -2204,10 +2204,10 @@
         <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2316,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2354,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2393,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2431,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2469,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2507,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>78</v>
@@ -2545,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2583,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2619,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2657,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -2695,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -2733,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -2772,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -2810,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -2851,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -2887,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -2925,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -5407,7 +5407,7 @@
         <v>62</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5472,7 +5472,7 @@
         <v>386</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5501,7 +5501,7 @@
         <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>476</v>
@@ -5534,7 +5534,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5556,7 +5556,7 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L7" s="10"/>
     </row>
@@ -5630,7 +5630,7 @@
         <v>386</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -5658,7 +5658,7 @@
         <v>386</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -5894,7 +5894,7 @@
         <v>386</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>386</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6010,7 +6010,7 @@
         <v>386</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6118,7 +6118,7 @@
         <v>386</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>386</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6256,7 +6256,7 @@
         <v>386</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6324,7 +6324,7 @@
         <v>386</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6394,7 +6394,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L44" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>386</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L46" s="10"/>
     </row>
@@ -6812,7 +6812,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>559</v>
+        <v>521</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>47</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D86AA5-943B-413B-8C32-E7482C718838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BA2FB8-4DE6-4B8B-9731-FC08B6503936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1606,9 +1606,6 @@
     <t>GavilanMixto.jpg</t>
   </si>
   <si>
-    <t>Fuente.jpg</t>
-  </si>
-  <si>
     <t>destacado</t>
   </si>
   <si>
@@ -1721,6 +1718,9 @@
   </si>
   <si>
     <t>LechucitaVizcachera.JPG</t>
+  </si>
+  <si>
+    <t>Fuente.JPG</t>
   </si>
   <si>
     <t>entrada.JPG</t>
@@ -2204,10 +2204,10 @@
         <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2316,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2354,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2393,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2431,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2469,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2507,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>78</v>
@@ -2545,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2583,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2619,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2657,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -2695,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -2733,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -2772,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -2810,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -2851,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -2887,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -2925,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -5407,7 +5407,7 @@
         <v>62</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5472,7 +5472,7 @@
         <v>386</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5501,7 +5501,7 @@
         <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>476</v>
@@ -5534,7 +5534,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5556,7 +5556,7 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L7" s="10"/>
     </row>
@@ -5630,7 +5630,7 @@
         <v>386</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -5658,7 +5658,7 @@
         <v>386</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -5894,7 +5894,7 @@
         <v>386</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>386</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6010,7 +6010,7 @@
         <v>386</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -6118,7 +6118,7 @@
         <v>386</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L32" s="10"/>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L34" s="10"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>386</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L36" s="10"/>
     </row>
@@ -6256,7 +6256,7 @@
         <v>386</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -6324,7 +6324,7 @@
         <v>386</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L41" s="10"/>
     </row>
@@ -6394,7 +6394,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L44" s="10"/>
     </row>
@@ -6442,7 +6442,7 @@
         <v>386</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L46" s="10"/>
     </row>
@@ -6812,7 +6812,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>47</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BA2FB8-4DE6-4B8B-9731-FC08B6503936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FFB14D-ADFF-4F5E-A41F-16015A01A0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -1600,6 +1600,9 @@
     <t>Benteveo.jpg</t>
   </si>
   <si>
+    <t>Calandria.jpg</t>
+  </si>
+  <si>
     <t>TyrannusSavana.jpg</t>
   </si>
   <si>
@@ -1682,9 +1685,6 @@
   </si>
   <si>
     <t>Zorzalcolorado.JPG</t>
-  </si>
-  <si>
-    <t>Calandria.JPG</t>
   </si>
   <si>
     <t>Carancho.JPG</t>
@@ -2204,10 +2204,10 @@
         <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2316,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2354,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2393,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2431,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2469,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2507,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>78</v>
@@ -2545,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2583,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2619,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2657,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -2695,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -2733,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -2772,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -2810,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -2851,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -2887,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -2925,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -5407,7 +5407,7 @@
         <v>62</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5472,7 +5472,7 @@
         <v>386</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5501,7 +5501,7 @@
         <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>476</v>
@@ -5526,15 +5526,19 @@
       <c r="C6" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="D6" s="10">
+        <v>-57.678601</v>
+      </c>
+      <c r="E6" s="10">
+        <v>-38.056950999999998</v>
+      </c>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5806,7 +5810,7 @@
         <v>386</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5962,7 +5966,7 @@
         <v>386</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6352,7 +6356,7 @@
         <v>386</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6394,7 +6398,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L44" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FFB14D-ADFF-4F5E-A41F-16015A01A0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91ADCD71-17D8-4B62-8158-67EB8197F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1600,9 +1600,6 @@
     <t>Benteveo.jpg</t>
   </si>
   <si>
-    <t>Calandria.jpg</t>
-  </si>
-  <si>
     <t>TyrannusSavana.jpg</t>
   </si>
   <si>
@@ -1685,6 +1682,9 @@
   </si>
   <si>
     <t>Zorzalcolorado.JPG</t>
+  </si>
+  <si>
+    <t>Calandria.JPG</t>
   </si>
   <si>
     <t>Carancho.JPG</t>
@@ -2204,10 +2204,10 @@
         <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2316,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2354,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2393,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2431,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2469,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2507,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>78</v>
@@ -2545,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2583,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2619,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2657,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -2695,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -2733,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -2772,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -2810,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -2851,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -2887,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -2925,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -5407,7 +5407,7 @@
         <v>62</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5472,7 +5472,7 @@
         <v>386</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5501,7 +5501,7 @@
         <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>476</v>
@@ -5538,7 +5538,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5810,7 +5810,7 @@
         <v>386</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5966,7 +5966,7 @@
         <v>386</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6356,7 +6356,7 @@
         <v>386</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6398,7 +6398,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L44" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91ADCD71-17D8-4B62-8158-67EB8197F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA60075-5880-4BD3-998E-D3E1C20ABF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1600,6 +1600,9 @@
     <t>Benteveo.jpg</t>
   </si>
   <si>
+    <t>Calandria.jpg</t>
+  </si>
+  <si>
     <t>TyrannusSavana.jpg</t>
   </si>
   <si>
@@ -1682,9 +1685,6 @@
   </si>
   <si>
     <t>Zorzalcolorado.JPG</t>
-  </si>
-  <si>
-    <t>Calandria.JPG</t>
   </si>
   <si>
     <t>Carancho.JPG</t>
@@ -2204,10 +2204,10 @@
         <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2316,7 +2316,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2354,7 +2354,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2393,7 +2393,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2431,7 +2431,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2469,7 +2469,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2507,7 +2507,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>78</v>
@@ -2545,7 +2545,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2583,7 +2583,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2619,7 +2619,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2657,7 +2657,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -2695,7 +2695,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -2733,7 +2733,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -2772,7 +2772,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -2810,7 +2810,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -2851,7 +2851,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -2887,7 +2887,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -2925,7 +2925,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -5407,7 +5407,7 @@
         <v>62</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -5472,7 +5472,7 @@
         <v>386</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L3" s="10"/>
     </row>
@@ -5501,7 +5501,7 @@
         <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>476</v>
@@ -5538,7 +5538,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -5810,7 +5810,7 @@
         <v>386</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L18" s="10"/>
     </row>
@@ -5966,7 +5966,7 @@
         <v>386</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -6356,7 +6356,7 @@
         <v>386</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L42" s="10"/>
     </row>
@@ -6398,7 +6398,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L44" s="10"/>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA60075-5880-4BD3-998E-D3E1C20ABF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FDD35B-F74D-4816-A2AF-6470438A64F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="564">
   <si>
     <t>id</t>
   </si>
@@ -1724,6 +1724,15 @@
   </si>
   <si>
     <t>entrada.JPG</t>
+  </si>
+  <si>
+    <t>Cedrodecrista.jpg</t>
+  </si>
+  <si>
+    <t>Cedrodecristal.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uno de los pocos ejemplares relevados en el pais. </t>
   </si>
 </sst>
 </file>
@@ -3668,7 +3677,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>239</v>
       </c>
@@ -3680,7 +3689,9 @@
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
+      <c r="H42" s="5" t="s">
+        <v>561</v>
+      </c>
       <c r="I42" s="5" t="s">
         <v>171</v>
       </c>
@@ -6749,7 +6760,7 @@
     <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.453125" customWidth="1"/>
     <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" customWidth="1"/>
     <col min="7" max="7" width="35.1796875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6845,7 +6856,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>48</v>
       </c>
@@ -6860,6 +6871,12 @@
       </c>
       <c r="E5" s="8">
         <v>-38.056685000000002</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FDD35B-F74D-4816-A2AF-6470438A64F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD22E5E-658D-485A-94C8-2658AFD31D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="563">
   <si>
     <t>id</t>
   </si>
@@ -1189,9 +1189,6 @@
     <t>Fuente</t>
   </si>
   <si>
-    <t>araucaria.jpg</t>
-  </si>
-  <si>
     <t>Cedro de Cristal</t>
   </si>
   <si>
@@ -1729,10 +1726,10 @@
     <t>Cedrodecrista.jpg</t>
   </si>
   <si>
+    <t>Araucaria.jpg</t>
+  </si>
+  <si>
     <t>Cedrodecristal.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uno de los pocos ejemplares relevados en el pais. </t>
   </si>
 </sst>
 </file>
@@ -2213,10 +2210,10 @@
         <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2240,7 +2237,7 @@
         <v>2004</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>78</v>
@@ -2262,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2284,7 +2281,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2325,7 +2322,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2363,7 +2360,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2402,7 +2399,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2440,7 +2437,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2478,7 +2475,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2516,7 +2513,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>78</v>
@@ -2554,7 +2551,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2592,7 +2589,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2628,7 +2625,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2666,7 +2663,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -2704,7 +2701,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -2742,7 +2739,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -2781,7 +2778,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -2819,7 +2816,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -2860,7 +2857,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -2896,7 +2893,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -2934,7 +2931,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -2972,7 +2969,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>161</v>
@@ -3010,7 +3007,7 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>166</v>
@@ -3048,7 +3045,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>171</v>
@@ -3084,7 +3081,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>78</v>
@@ -3120,7 +3117,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>78</v>
@@ -3158,7 +3155,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>101</v>
@@ -3196,7 +3193,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>87</v>
@@ -3234,7 +3231,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>82</v>
@@ -3272,7 +3269,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>171</v>
@@ -3310,7 +3307,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>194</v>
@@ -3348,7 +3345,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>199</v>
@@ -3386,7 +3383,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>204</v>
@@ -3424,7 +3421,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>78</v>
@@ -3462,7 +3459,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>213</v>
@@ -3690,7 +3687,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>171</v>
@@ -5418,13 +5415,13 @@
         <v>62</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -5450,10 +5447,10 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L2" s="10"/>
     </row>
@@ -5480,22 +5477,22 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>389</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -5509,13 +5506,13 @@
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -5529,13 +5526,13 @@
     </row>
     <row r="6" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>392</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D6" s="10">
         <v>-57.678601</v>
@@ -5549,19 +5546,19 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>394</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -5571,19 +5568,19 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>396</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D8" s="10">
         <v>-57.680219000000001</v>
@@ -5596,20 +5593,20 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>398</v>
-      </c>
       <c r="C9" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -5623,13 +5620,13 @@
     </row>
     <row r="10" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>400</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D10" s="10">
         <v>-57.679960999999999</v>
@@ -5642,22 +5639,22 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>402</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D11" s="10">
         <v>-57.681131000000001</v>
@@ -5670,22 +5667,22 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>404</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -5699,13 +5696,13 @@
     </row>
     <row r="13" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>406</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -5719,13 +5716,13 @@
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>408</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -5739,13 +5736,13 @@
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>410</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -5759,13 +5756,13 @@
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>412</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -5779,13 +5776,13 @@
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>414</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -5799,13 +5796,13 @@
     </row>
     <row r="18" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>416</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D18" s="10">
         <v>-57.683276999999997</v>
@@ -5818,22 +5815,22 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>418</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -5847,13 +5844,13 @@
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>420</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -5867,13 +5864,13 @@
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>422</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -5887,13 +5884,13 @@
     </row>
     <row r="22" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>424</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D22" s="10">
         <v>-57.682054000000001</v>
@@ -5906,22 +5903,22 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
       <c r="J22" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L22" s="10"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>426</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -5935,13 +5932,13 @@
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>428</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -5955,13 +5952,13 @@
     </row>
     <row r="25" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>430</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D25" s="10">
         <v>-57.679361</v>
@@ -5974,22 +5971,22 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>432</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -6003,13 +6000,13 @@
     </row>
     <row r="27" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>434</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D27" s="10">
         <v>-57.684317</v>
@@ -6022,22 +6019,22 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>436</v>
-      </c>
       <c r="C28" s="11" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -6051,13 +6048,13 @@
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>438</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -6071,13 +6068,13 @@
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>440</v>
-      </c>
       <c r="C30" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
@@ -6091,13 +6088,13 @@
     </row>
     <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>442</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
@@ -6111,13 +6108,13 @@
     </row>
     <row r="32" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>444</v>
-      </c>
       <c r="C32" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D32" s="10">
         <v>-57.682547</v>
@@ -6130,22 +6127,22 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>446</v>
-      </c>
       <c r="C33" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -6159,13 +6156,13 @@
     </row>
     <row r="34" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>448</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -6175,19 +6172,19 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>450</v>
-      </c>
       <c r="C35" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
@@ -6201,13 +6198,13 @@
     </row>
     <row r="36" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>452</v>
-      </c>
       <c r="C36" s="11" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D36" s="10">
         <v>-57.682281000000003</v>
@@ -6220,22 +6217,22 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L36" s="10"/>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>454</v>
-      </c>
       <c r="C37" s="11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -6249,13 +6246,13 @@
     </row>
     <row r="38" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>456</v>
-      </c>
       <c r="C38" s="11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D38" s="10">
         <v>-57.685510999999998</v>
@@ -6268,22 +6265,22 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L38" s="10"/>
     </row>
     <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="B39" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>458</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -6297,13 +6294,13 @@
     </row>
     <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>460</v>
-      </c>
       <c r="C40" s="11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -6317,13 +6314,13 @@
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>462</v>
-      </c>
       <c r="C41" s="11" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D41" s="10">
         <v>-57.681240000000003</v>
@@ -6336,22 +6333,22 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L41" s="10"/>
     </row>
     <row r="42" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>464</v>
-      </c>
       <c r="C42" s="11" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D42" s="10">
         <v>-57.683684</v>
@@ -6364,22 +6361,22 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L42" s="10"/>
     </row>
     <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>466</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -6393,13 +6390,13 @@
     </row>
     <row r="44" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>468</v>
-      </c>
       <c r="C44" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
@@ -6409,19 +6406,19 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L44" s="10"/>
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>470</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
@@ -6435,13 +6432,13 @@
     </row>
     <row r="46" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="B46" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>472</v>
-      </c>
       <c r="C46" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D46" s="10">
         <v>-57.682558</v>
@@ -6454,22 +6451,22 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L46" s="10"/>
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>474</v>
-      </c>
       <c r="C47" s="11" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
@@ -6760,7 +6757,7 @@
     <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.453125" customWidth="1"/>
     <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="35.1796875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6804,7 +6801,7 @@
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -6818,7 +6815,7 @@
         <v>381</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D3" s="8">
         <v>-57.679949999999998</v>
@@ -6827,7 +6824,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>47</v>
@@ -6841,7 +6838,7 @@
         <v>169</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="8">
         <v>-57.680886000000001</v>
@@ -6850,21 +6847,21 @@
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>382</v>
+        <v>561</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="D5" s="8">
         <v>-57.680562999999999</v>
@@ -6875,9 +6872,7 @@
       <c r="F5" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>563</v>
-      </c>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD22E5E-658D-485A-94C8-2658AFD31D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC78344-D661-4E84-99F7-D5A04739D4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="564">
   <si>
     <t>id</t>
   </si>
@@ -1730,6 +1730,9 @@
   </si>
   <si>
     <t>Cedrodecristal.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uno de los pocos ejemplares relevados en el pais. </t>
   </si>
 </sst>
 </file>
@@ -6853,7 +6856,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>48</v>
       </c>
@@ -6872,7 +6875,9 @@
       <c r="F5" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC78344-D661-4E84-99F7-D5A04739D4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE964F76-5001-4625-8A32-DEECDDE6253B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1720,9 +1720,6 @@
     <t>Fuente.JPG</t>
   </si>
   <si>
-    <t>entrada.JPG</t>
-  </si>
-  <si>
     <t>Cedrodecrista.jpg</t>
   </si>
   <si>
@@ -1733,6 +1730,9 @@
   </si>
   <si>
     <t xml:space="preserve">Uno de los pocos ejemplares relevados en el pais. </t>
+  </si>
+  <si>
+    <t>Estacionamiento.jpg</t>
   </si>
 </sst>
 </file>
@@ -3690,7 +3690,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>171</v>
@@ -6804,7 +6804,7 @@
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -6850,7 +6850,7 @@
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>49</v>
@@ -6873,10 +6873,10 @@
         <v>-38.056685000000002</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE964F76-5001-4625-8A32-DEECDDE6253B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84642F3-B1B5-47AA-81AB-1A9F8D236733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="569">
   <si>
     <t>id</t>
   </si>
@@ -1192,6 +1192,12 @@
     <t>Cedro de Cristal</t>
   </si>
   <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
     <t>Arbol</t>
   </si>
   <si>
@@ -1733,6 +1739,15 @@
   </si>
   <si>
     <t>Estacionamiento.jpg</t>
+  </si>
+  <si>
+    <t>Descanso.jpg</t>
+  </si>
+  <si>
+    <t>Descanso</t>
+  </si>
+  <si>
+    <t>Bosque de Eucaliptos</t>
   </si>
 </sst>
 </file>
@@ -2213,10 +2228,10 @@
         <v>75</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -2240,7 +2255,7 @@
         <v>2004</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>78</v>
@@ -2262,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
@@ -2284,7 +2299,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2325,7 +2340,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2363,7 +2378,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2402,7 +2417,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2440,7 +2455,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2478,7 +2493,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2516,7 +2531,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>78</v>
@@ -2554,7 +2569,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2592,7 +2607,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2628,7 +2643,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2666,7 +2681,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -2704,7 +2719,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -2742,7 +2757,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -2781,7 +2796,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -2819,7 +2834,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -2860,7 +2875,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -2896,7 +2911,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -2934,7 +2949,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -2972,7 +2987,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>161</v>
@@ -3010,7 +3025,7 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>166</v>
@@ -3048,7 +3063,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>171</v>
@@ -3084,7 +3099,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>78</v>
@@ -3120,7 +3135,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>78</v>
@@ -3158,7 +3173,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>101</v>
@@ -3196,7 +3211,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>87</v>
@@ -3234,7 +3249,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>82</v>
@@ -3272,7 +3287,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>171</v>
@@ -3310,7 +3325,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>194</v>
@@ -3348,7 +3363,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>199</v>
@@ -3386,7 +3401,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>204</v>
@@ -3424,7 +3439,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>78</v>
@@ -3462,7 +3477,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>213</v>
@@ -3690,7 +3705,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>171</v>
@@ -5418,13 +5433,13 @@
         <v>62</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -5450,10 +5465,10 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L2" s="10"/>
     </row>
@@ -5480,22 +5495,22 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -5509,13 +5524,13 @@
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -5529,13 +5544,13 @@
     </row>
     <row r="6" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D6" s="10">
         <v>-57.678601</v>
@@ -5549,19 +5564,19 @@
       <c r="I6" s="10"/>
       <c r="J6" s="14"/>
       <c r="K6" s="5" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -5571,19 +5586,19 @@
       <c r="I7" s="10"/>
       <c r="J7" s="14"/>
       <c r="K7" s="5" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D8" s="10">
         <v>-57.680219000000001</v>
@@ -5596,20 +5611,20 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -5623,13 +5638,13 @@
     </row>
     <row r="10" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D10" s="10">
         <v>-57.679960999999999</v>
@@ -5642,22 +5657,22 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D11" s="10">
         <v>-57.681131000000001</v>
@@ -5670,22 +5685,22 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -5699,13 +5714,13 @@
     </row>
     <row r="13" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -5719,13 +5734,13 @@
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -5739,13 +5754,13 @@
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -5759,13 +5774,13 @@
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -5779,13 +5794,13 @@
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -5799,13 +5814,13 @@
     </row>
     <row r="18" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D18" s="10">
         <v>-57.683276999999997</v>
@@ -5818,22 +5833,22 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -5847,13 +5862,13 @@
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -5867,13 +5882,13 @@
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -5887,13 +5902,13 @@
     </row>
     <row r="22" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D22" s="10">
         <v>-57.682054000000001</v>
@@ -5906,22 +5921,22 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
       <c r="J22" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L22" s="10"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -5935,13 +5950,13 @@
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -5955,13 +5970,13 @@
     </row>
     <row r="25" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D25" s="10">
         <v>-57.679361</v>
@@ -5974,22 +5989,22 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -6003,13 +6018,13 @@
     </row>
     <row r="27" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D27" s="10">
         <v>-57.684317</v>
@@ -6022,22 +6037,22 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -6051,13 +6066,13 @@
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -6071,13 +6086,13 @@
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
@@ -6091,13 +6106,13 @@
     </row>
     <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
@@ -6111,13 +6126,13 @@
     </row>
     <row r="32" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D32" s="10">
         <v>-57.682547</v>
@@ -6130,22 +6145,22 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -6159,13 +6174,13 @@
     </row>
     <row r="34" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -6175,19 +6190,19 @@
       <c r="I34" s="10"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
@@ -6201,13 +6216,13 @@
     </row>
     <row r="36" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D36" s="10">
         <v>-57.682281000000003</v>
@@ -6220,22 +6235,22 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L36" s="10"/>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -6249,13 +6264,13 @@
     </row>
     <row r="38" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D38" s="10">
         <v>-57.685510999999998</v>
@@ -6268,22 +6283,22 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L38" s="10"/>
     </row>
     <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -6297,13 +6312,13 @@
     </row>
     <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -6317,13 +6332,13 @@
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D41" s="10">
         <v>-57.681240000000003</v>
@@ -6336,22 +6351,22 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L41" s="10"/>
     </row>
     <row r="42" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D42" s="10">
         <v>-57.683684</v>
@@ -6364,22 +6379,22 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L42" s="10"/>
     </row>
     <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -6393,13 +6408,13 @@
     </row>
     <row r="44" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
@@ -6409,19 +6424,19 @@
       <c r="I44" s="10"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L44" s="10"/>
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
@@ -6435,13 +6450,13 @@
     </row>
     <row r="46" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D46" s="10">
         <v>-57.682558</v>
@@ -6454,22 +6469,22 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L46" s="10"/>
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
@@ -6804,7 +6819,7 @@
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -6818,7 +6833,7 @@
         <v>381</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D3" s="8">
         <v>-57.679949999999998</v>
@@ -6827,7 +6842,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>47</v>
@@ -6841,7 +6856,7 @@
         <v>169</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D4" s="8">
         <v>-57.680886000000001</v>
@@ -6850,7 +6865,7 @@
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>49</v>
@@ -6864,7 +6879,7 @@
         <v>382</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D5" s="8">
         <v>-57.680562999999999</v>
@@ -6873,21 +6888,38 @@
         <v>-38.056685000000002</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>386</v>
+      </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>385</v>
+      </c>
       <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84642F3-B1B5-47AA-81AB-1A9F8D236733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB51F28-2F97-4732-8760-2068A574D390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="570">
   <si>
     <t>id</t>
   </si>
@@ -1748,13 +1748,16 @@
   </si>
   <si>
     <t>Bosque de Eucaliptos</t>
+  </si>
+  <si>
+    <t>Bosquedeeucaliptus.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1775,11 +1778,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <color rgb="FF007B8B"/>
-      <name val="Roboto"/>
     </font>
     <font>
       <u/>
@@ -1843,7 +1841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1861,26 +1859,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5405,1096 +5402,1096 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>546</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>-57.680154000000002</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <v>-38.056790999999997</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <v>46242</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
       <c r="J2" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="L2" s="10"/>
+      <c r="L2" s="9"/>
     </row>
     <row r="3" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>-57.680520999999999</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>-38.056471999999999</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>46242</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
       <c r="J3" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="L3" s="10"/>
+      <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="14"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="13"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="10"/>
+      <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="14"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="10"/>
+      <c r="L5" s="9"/>
     </row>
     <row r="6" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>-57.678601</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>-38.056950999999998</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="14"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="13"/>
       <c r="K6" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="L6" s="10"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="14"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="13"/>
       <c r="K7" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="L7" s="10"/>
+      <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>-57.680219000000001</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>-38.057253000000003</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
       <c r="J8" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="10"/>
+      <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="10"/>
+      <c r="L9" s="9"/>
     </row>
     <row r="10" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>-57.679960999999999</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>-38.055588999999998</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
       <c r="J10" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="L10" s="10"/>
+      <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>-57.681131000000001</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>-38.055318</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="L11" s="10"/>
+      <c r="L11" s="9"/>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
-      <c r="L12" s="10"/>
+      <c r="L12" s="9"/>
     </row>
     <row r="13" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>485</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="10"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="10"/>
+      <c r="L14" s="9"/>
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
-      <c r="L15" s="10"/>
+      <c r="L15" s="9"/>
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="10"/>
+      <c r="L16" s="9"/>
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="10"/>
+      <c r="L17" s="9"/>
     </row>
     <row r="18" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>-57.683276999999997</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>-38.053451000000003</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="L18" s="10"/>
+      <c r="L18" s="9"/>
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="10"/>
+      <c r="L19" s="9"/>
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
-      <c r="L20" s="10"/>
+      <c r="L20" s="9"/>
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
-      <c r="L21" s="10"/>
+      <c r="L21" s="9"/>
     </row>
     <row r="22" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>-57.682054000000001</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>-38.055081999999999</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
       <c r="J22" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="L22" s="10"/>
+      <c r="L22" s="9"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="10"/>
+      <c r="L23" s="9"/>
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="10"/>
+      <c r="L24" s="9"/>
     </row>
     <row r="25" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>-57.679361</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>-38.057346000000003</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
       <c r="J25" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="L25" s="10"/>
+      <c r="L25" s="9"/>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="10"/>
+      <c r="L26" s="9"/>
     </row>
     <row r="27" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>-57.684317</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>-38.055689999999998</v>
       </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
       <c r="J27" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="L27" s="10"/>
+      <c r="L27" s="9"/>
     </row>
     <row r="28" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="10"/>
+      <c r="L28" s="9"/>
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="10"/>
+      <c r="L29" s="9"/>
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="10"/>
+      <c r="L30" s="9"/>
     </row>
     <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="10"/>
+      <c r="L31" s="9"/>
     </row>
     <row r="32" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>-57.682547</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <v>-38.057102999999998</v>
       </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="L32" s="10"/>
+      <c r="L32" s="9"/>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="10"/>
+      <c r="L33" s="9"/>
     </row>
     <row r="34" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="L34" s="10"/>
+      <c r="L34" s="9"/>
     </row>
     <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="10"/>
+      <c r="L35" s="9"/>
     </row>
     <row r="36" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>-57.682281000000003</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="9">
         <v>-38.057195999999998</v>
       </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
       <c r="J36" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="L36" s="10"/>
+      <c r="L36" s="9"/>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="10"/>
+      <c r="L37" s="9"/>
     </row>
     <row r="38" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="9">
         <v>-57.685510999999998</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <v>-38.054340000000003</v>
       </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
       <c r="J38" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="L38" s="10"/>
+      <c r="L38" s="9"/>
     </row>
     <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
-      <c r="L39" s="10"/>
+      <c r="L39" s="9"/>
     </row>
     <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="10"/>
+      <c r="L40" s="9"/>
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="9">
         <v>-57.681240000000003</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="9">
         <v>-38.055633</v>
       </c>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
       <c r="J41" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="L41" s="10"/>
+      <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="9">
         <v>-57.683684</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <v>-38.054684999999999</v>
       </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
       <c r="J42" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="L42" s="10"/>
+      <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="10"/>
+      <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="L44" s="10"/>
+      <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="10"/>
+      <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="9">
         <v>-57.682558</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="9">
         <v>-38.055816999999998</v>
       </c>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
       <c r="J46" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="L46" s="10"/>
+      <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="14"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="13"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="10"/>
+      <c r="L47" s="9"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K48" s="5"/>
@@ -6812,10 +6809,10 @@
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>-57.683934999999998</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -6835,10 +6832,10 @@
       <c r="C3" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>-57.679949999999998</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -6858,10 +6855,10 @@
       <c r="C4" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>-57.680886000000001</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -6881,10 +6878,10 @@
       <c r="C5" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>-57.680562999999999</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>-38.056685000000002</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -6904,8 +6901,12 @@
       <c r="C6" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="D6" s="7">
+        <v>-57.680033999999999</v>
+      </c>
+      <c r="E6" s="7">
+        <v>-38.056984999999997</v>
+      </c>
       <c r="F6" s="2" t="s">
         <v>566</v>
       </c>
@@ -6920,11 +6921,19 @@
       <c r="C7" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="7">
+        <v>-57.683433999999998</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-38.055428999999997</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>569</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB51F28-2F97-4732-8760-2068A574D390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60765BE-D457-4408-80A1-39AE4DC9C857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="645">
   <si>
     <t>id</t>
   </si>
@@ -1751,13 +1751,238 @@
   </si>
   <si>
     <t>Bosquedeeucaliptus.jpg</t>
+  </si>
+  <si>
+    <t>América del Norte</t>
+  </si>
+  <si>
+    <t>Hemisferio Norte / Variable</t>
+  </si>
+  <si>
+    <t>Europa / Asia Occidental</t>
+  </si>
+  <si>
+    <t>Europa / África del Norte / Asia</t>
+  </si>
+  <si>
+    <t>Cipreses</t>
+  </si>
+  <si>
+    <t>Europa (Mediterráneo) / Asia</t>
+  </si>
+  <si>
+    <t>África (Norte)</t>
+  </si>
+  <si>
+    <t>Eucalipto blanco</t>
+  </si>
+  <si>
+    <t>Oceanía (Australia)</t>
+  </si>
+  <si>
+    <t>América (del Norte y del Sur)</t>
+  </si>
+  <si>
+    <t>América del Sur</t>
+  </si>
+  <si>
+    <t>Asia (Origen hortícola/Híbrido)</t>
+  </si>
+  <si>
+    <t>Espino</t>
+  </si>
+  <si>
+    <t>Europa / Origen Híbrido</t>
+  </si>
+  <si>
+    <t>Ciprés de Monterrey</t>
+  </si>
+  <si>
+    <t>Europa (Mediterráneo) / África del Norte</t>
+  </si>
+  <si>
+    <t>Europa (Balcanes)</t>
+  </si>
+  <si>
+    <t>Asia / Europa</t>
+  </si>
+  <si>
+    <t>Asia (Japón)</t>
+  </si>
+  <si>
+    <t>América del Norte / Asia</t>
+  </si>
+  <si>
+    <t>Secuoya roja</t>
+  </si>
+  <si>
+    <t>Ahuehuete</t>
+  </si>
+  <si>
+    <t>América del Norte (México)</t>
+  </si>
+  <si>
+    <t>Ciprés de las Guaitecas</t>
+  </si>
+  <si>
+    <t>América del Sur (Andes)</t>
+  </si>
+  <si>
+    <t>Tejo común</t>
+  </si>
+  <si>
+    <t>Abeto de Douglas</t>
+  </si>
+  <si>
+    <t>Hipericón canario</t>
+  </si>
+  <si>
+    <t>África (Islas Canarias)</t>
+  </si>
+  <si>
+    <t>Carex</t>
+  </si>
+  <si>
+    <t>Global / Cosmopolita</t>
+  </si>
+  <si>
+    <t>Damara</t>
+  </si>
+  <si>
+    <t>Asia (Sudeste Asiático)</t>
+  </si>
+  <si>
+    <t>Árbol de los tulipanes</t>
+  </si>
+  <si>
+    <t>Roble rojo</t>
+  </si>
+  <si>
+    <t>Aliso andino</t>
+  </si>
+  <si>
+    <t>Macasar</t>
+  </si>
+  <si>
+    <t>Asia (China)</t>
+  </si>
+  <si>
+    <t>Ciprés de Hinoki</t>
+  </si>
+  <si>
+    <t>Corona de novia</t>
+  </si>
+  <si>
+    <t>Cedro</t>
+  </si>
+  <si>
+    <t>África / Asia / Europa</t>
+  </si>
+  <si>
+    <t>Ginkgo</t>
+  </si>
+  <si>
+    <t>Espino blanco</t>
+  </si>
+  <si>
+    <t>Hemisferio Norte</t>
+  </si>
+  <si>
+    <t>Dodonea</t>
+  </si>
+  <si>
+    <t>Oceanía / América / África (Cosmopolita tropical)</t>
+  </si>
+  <si>
+    <t>Ligustro</t>
+  </si>
+  <si>
+    <t>Canforero</t>
+  </si>
+  <si>
+    <t>Asia (China / Japón)</t>
+  </si>
+  <si>
+    <t>Boj</t>
+  </si>
+  <si>
+    <t>Europa / Asia / África</t>
+  </si>
+  <si>
+    <t>Acacia mimosa</t>
+  </si>
+  <si>
+    <t>Liquidámbar de Formosa</t>
+  </si>
+  <si>
+    <t>Asia (China / Taiwán)</t>
+  </si>
+  <si>
+    <t>Espino de fuego</t>
+  </si>
+  <si>
+    <t>Europa / Asia</t>
+  </si>
+  <si>
+    <t>Oceanía / América / África</t>
+  </si>
+  <si>
+    <t>Eucalipto medicinal</t>
+  </si>
+  <si>
+    <t>Secuoya</t>
+  </si>
+  <si>
+    <t>Pino insigne</t>
+  </si>
+  <si>
+    <t>Coihue</t>
+  </si>
+  <si>
+    <t>América del Sur (Patagonia)</t>
+  </si>
+  <si>
+    <t>Roble pellín</t>
+  </si>
+  <si>
+    <t>Criptomeria</t>
+  </si>
+  <si>
+    <t>Boj común</t>
+  </si>
+  <si>
+    <t>Europa / Asia Occidental / África del Norte</t>
+  </si>
+  <si>
+    <t>Duraznero</t>
+  </si>
+  <si>
+    <t>Pino radiata</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Damasco</t>
+  </si>
+  <si>
+    <t>Asia (Central)</t>
+  </si>
+  <si>
+    <t>Cedro del Atlas</t>
+  </si>
+  <si>
+    <t>Haya común</t>
+  </si>
+  <si>
+    <t>Olmo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1805,16 +2030,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F9F6"/>
+        <bgColor rgb="FFF5F9F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1837,11 +2072,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1879,6 +2129,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2247,7 +2503,9 @@
       <c r="E2" s="5">
         <v>-38.056790999999997</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G2" s="5">
         <v>2004</v>
       </c>
@@ -2277,7 +2535,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -2293,7 +2551,9 @@
       <c r="E3" s="5">
         <v>-38.056471999999999</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>571</v>
+      </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
         <v>538</v>
@@ -2318,7 +2578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -2334,7 +2594,9 @@
       <c r="E4" s="5">
         <v>-38.056541000000003</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>572</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
         <v>540</v>
@@ -2356,7 +2618,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -2372,7 +2634,9 @@
       <c r="E5" s="5">
         <v>-38.056569000000003</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>573</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
         <v>539</v>
@@ -2411,7 +2675,9 @@
       <c r="E6" s="5">
         <v>-38.056548999999997</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
         <v>541</v>
@@ -2433,7 +2699,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -2449,7 +2715,9 @@
       <c r="E7" s="5">
         <v>-38.056437000000003</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>571</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
         <v>543</v>
@@ -2471,7 +2739,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -2487,7 +2755,9 @@
       <c r="E8" s="5">
         <v>-38.056372000000003</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>575</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
         <v>542</v>
@@ -2525,7 +2795,9 @@
       <c r="E9" s="5">
         <v>-38.056238999999998</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
         <v>528</v>
@@ -2563,7 +2835,9 @@
       <c r="E10" s="5">
         <v>-38.056201000000001</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>576</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
         <v>529</v>
@@ -2601,7 +2875,9 @@
       <c r="E11" s="5">
         <v>-38.056054000000003</v>
       </c>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
         <v>530</v>
@@ -2637,7 +2913,9 @@
       <c r="E12" s="5">
         <v>-38.056331</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>578</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
         <v>531</v>
@@ -2659,7 +2937,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -2675,7 +2953,9 @@
       <c r="E13" s="5">
         <v>-38.056328999999998</v>
       </c>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>571</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
         <v>532</v>
@@ -2713,7 +2993,9 @@
       <c r="E14" s="5">
         <v>-38.056373000000001</v>
       </c>
-      <c r="F14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
         <v>533</v>
@@ -2735,7 +3017,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -2751,7 +3033,9 @@
       <c r="E15" s="5">
         <v>-38.056550999999999</v>
       </c>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>579</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
         <v>534</v>
@@ -2790,7 +3074,9 @@
       <c r="E16" s="5">
         <v>-38.056643999999999</v>
       </c>
-      <c r="F16" s="5"/>
+      <c r="F16" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
         <v>535</v>
@@ -2812,7 +3098,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -2828,7 +3114,9 @@
       <c r="E17" s="5">
         <v>-38.056727000000002</v>
       </c>
-      <c r="F17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>580</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
         <v>545</v>
@@ -2853,7 +3141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>144</v>
       </c>
@@ -2869,7 +3157,9 @@
       <c r="E18" s="5">
         <v>-38.056677999999998</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>581</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
         <v>536</v>
@@ -2891,7 +3181,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -2905,7 +3195,9 @@
       <c r="E19" s="5">
         <v>-38.056843999999998</v>
       </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>571</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
         <v>537</v>
@@ -2943,7 +3235,9 @@
       <c r="E20" s="5">
         <v>-38.057062000000002</v>
       </c>
-      <c r="F20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
         <v>544</v>
@@ -2965,7 +3259,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>158</v>
       </c>
@@ -2981,7 +3275,9 @@
       <c r="E21" s="5">
         <v>-38.057076000000002</v>
       </c>
-      <c r="F21" s="5"/>
+      <c r="F21" s="5" t="s">
+        <v>583</v>
+      </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
         <v>387</v>
@@ -3003,7 +3299,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>163</v>
       </c>
@@ -3019,7 +3315,9 @@
       <c r="E22" s="5">
         <v>-38.057192000000001</v>
       </c>
-      <c r="F22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>571</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
         <v>387</v>
@@ -3041,7 +3339,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -3057,7 +3355,9 @@
       <c r="E23" s="5">
         <v>-38.056908999999997</v>
       </c>
-      <c r="F23" s="5"/>
+      <c r="F23" s="5" t="s">
+        <v>578</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
         <v>387</v>
@@ -3079,11 +3379,13 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" ht="29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>173</v>
       </c>
-      <c r="B24" s="5"/>
+      <c r="B24" s="14" t="s">
+        <v>584</v>
+      </c>
       <c r="C24" s="5" t="s">
         <v>174</v>
       </c>
@@ -3093,7 +3395,9 @@
       <c r="E24" s="5">
         <v>-38.056840000000001</v>
       </c>
-      <c r="F24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
         <v>387</v>
@@ -3115,11 +3419,13 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" ht="58" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>176</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="15" t="s">
+        <v>574</v>
+      </c>
       <c r="C25" s="5" t="s">
         <v>127</v>
       </c>
@@ -3129,7 +3435,9 @@
       <c r="E25" s="5">
         <v>-38.056933999999998</v>
       </c>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>571</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
         <v>387</v>
@@ -3151,7 +3459,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>178</v>
       </c>
@@ -3167,7 +3475,9 @@
       <c r="E26" s="5">
         <v>-38.056655999999997</v>
       </c>
-      <c r="F26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>571</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
         <v>387</v>
@@ -3189,7 +3499,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -3205,7 +3515,9 @@
       <c r="E27" s="5">
         <v>-38.055928999999999</v>
       </c>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5" t="s">
+        <v>585</v>
+      </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
         <v>387</v>
@@ -3227,7 +3539,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>184</v>
       </c>
@@ -3243,7 +3555,9 @@
       <c r="E28" s="5">
         <v>-38.056055999999998</v>
       </c>
-      <c r="F28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>585</v>
+      </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>387</v>
@@ -3265,7 +3579,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>189</v>
       </c>
@@ -3281,7 +3595,9 @@
       <c r="E29" s="5">
         <v>-38.056057000000003</v>
       </c>
-      <c r="F29" s="5"/>
+      <c r="F29" s="5" t="s">
+        <v>578</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
         <v>387</v>
@@ -3319,7 +3635,9 @@
       <c r="E30" s="5">
         <v>-38.056168</v>
       </c>
-      <c r="F30" s="5"/>
+      <c r="F30" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
         <v>387</v>
@@ -3341,7 +3659,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>196</v>
       </c>
@@ -3357,7 +3675,9 @@
       <c r="E31" s="5">
         <v>-38.056126999999996</v>
       </c>
-      <c r="F31" s="5"/>
+      <c r="F31" s="5" t="s">
+        <v>586</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
         <v>387</v>
@@ -3395,7 +3715,9 @@
       <c r="E32" s="5">
         <v>-38.056092999999997</v>
       </c>
-      <c r="F32" s="5"/>
+      <c r="F32" s="5" t="s">
+        <v>587</v>
+      </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
         <v>387</v>
@@ -3433,7 +3755,9 @@
       <c r="E33" s="5">
         <v>-38.056373999999998</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>588</v>
+      </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
         <v>387</v>
@@ -3455,7 +3779,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>210</v>
       </c>
@@ -3471,7 +3795,9 @@
       <c r="E34" s="5">
         <v>-38.056545</v>
       </c>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>589</v>
+      </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
         <v>387</v>
@@ -3493,17 +3819,21 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>215</v>
       </c>
-      <c r="B35" s="5"/>
+      <c r="B35" s="5" t="s">
+        <v>590</v>
+      </c>
       <c r="C35" s="5" t="s">
         <v>216</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
@@ -3521,17 +3851,21 @@
         <v>217</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>218</v>
       </c>
-      <c r="B36" s="5"/>
+      <c r="B36" s="5" t="s">
+        <v>591</v>
+      </c>
       <c r="C36" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="5" t="s">
+        <v>592</v>
+      </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
@@ -3549,17 +3883,21 @@
         <v>220</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>221</v>
       </c>
-      <c r="B37" s="5"/>
+      <c r="B37" s="5" t="s">
+        <v>593</v>
+      </c>
       <c r="C37" s="5" t="s">
         <v>222</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="F37" s="5" t="s">
+        <v>594</v>
+      </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
@@ -3577,17 +3915,21 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>224</v>
       </c>
-      <c r="B38" s="5"/>
+      <c r="B38" s="5" t="s">
+        <v>595</v>
+      </c>
       <c r="C38" s="5" t="s">
         <v>225</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="5" t="s">
+        <v>573</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
@@ -3605,17 +3947,21 @@
         <v>226</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="5"/>
+      <c r="B39" s="5" t="s">
+        <v>596</v>
+      </c>
       <c r="C39" s="5" t="s">
         <v>228</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="F39" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
@@ -3633,17 +3979,21 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>231</v>
       </c>
-      <c r="B40" s="5"/>
+      <c r="B40" s="5" t="s">
+        <v>597</v>
+      </c>
       <c r="C40" s="5" t="s">
         <v>232</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="F40" s="5" t="s">
+        <v>598</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
@@ -3661,17 +4011,21 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>235</v>
       </c>
-      <c r="B41" s="5"/>
+      <c r="B41" s="5" t="s">
+        <v>599</v>
+      </c>
       <c r="C41" s="5" t="s">
         <v>236</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="F41" s="5" t="s">
+        <v>600</v>
+      </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
@@ -3689,17 +4043,21 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>239</v>
       </c>
-      <c r="B42" s="5"/>
+      <c r="B42" s="5" t="s">
+        <v>601</v>
+      </c>
       <c r="C42" s="5" t="s">
         <v>240</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>602</v>
+      </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
         <v>561</v>
@@ -3719,17 +4077,21 @@
         <v>241</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>242</v>
       </c>
-      <c r="B43" s="5"/>
+      <c r="B43" s="5" t="s">
+        <v>603</v>
+      </c>
       <c r="C43" s="5" t="s">
         <v>243</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="F43" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
@@ -3747,11 +4109,13 @@
         <v>244</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>245</v>
       </c>
-      <c r="B44" s="5"/>
+      <c r="B44" s="5" t="s">
+        <v>604</v>
+      </c>
       <c r="C44" s="5" t="s">
         <v>131</v>
       </c>
@@ -3761,7 +4125,9 @@
       <c r="E44" s="5">
         <v>-38.055799999999998</v>
       </c>
-      <c r="F44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
@@ -3781,11 +4147,13 @@
         <v>246</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>247</v>
       </c>
-      <c r="B45" s="5"/>
+      <c r="B45" s="5" t="s">
+        <v>605</v>
+      </c>
       <c r="C45" s="5" t="s">
         <v>135</v>
       </c>
@@ -3795,7 +4163,9 @@
       <c r="E45" s="5">
         <v>-38.05574</v>
       </c>
-      <c r="F45" s="5"/>
+      <c r="F45" s="5" t="s">
+        <v>579</v>
+      </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
@@ -3819,7 +4189,9 @@
       <c r="A46" t="s">
         <v>250</v>
       </c>
-      <c r="B46" s="5"/>
+      <c r="B46" s="5" t="s">
+        <v>606</v>
+      </c>
       <c r="C46" s="5" t="s">
         <v>251</v>
       </c>
@@ -3829,7 +4201,9 @@
       <c r="E46" s="5">
         <v>-38.055729999999997</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="F46" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
@@ -3853,7 +4227,9 @@
       <c r="A47" t="s">
         <v>254</v>
       </c>
-      <c r="B47" s="5"/>
+      <c r="B47" s="5" t="s">
+        <v>608</v>
+      </c>
       <c r="C47" s="5" t="s">
         <v>255</v>
       </c>
@@ -3863,7 +4239,9 @@
       <c r="E47" s="5">
         <v>-38.055759999999999</v>
       </c>
-      <c r="F47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>588</v>
+      </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
@@ -3883,11 +4261,13 @@
         <v>256</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>257</v>
       </c>
-      <c r="B48" s="5"/>
+      <c r="B48" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C48" s="5" t="s">
         <v>258</v>
       </c>
@@ -3897,7 +4277,9 @@
       <c r="E48" s="5">
         <v>-38.055639999999997</v>
       </c>
-      <c r="F48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
@@ -3917,11 +4299,13 @@
         <v>259</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>260</v>
       </c>
-      <c r="B49" s="5"/>
+      <c r="B49" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C49" s="5" t="s">
         <v>258</v>
       </c>
@@ -3931,7 +4315,9 @@
       <c r="E49" s="5">
         <v>-38.055630000000001</v>
       </c>
-      <c r="F49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
@@ -3951,11 +4337,13 @@
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>262</v>
       </c>
-      <c r="B50" s="5"/>
+      <c r="B50" s="5" t="s">
+        <v>610</v>
+      </c>
       <c r="C50" s="5" t="s">
         <v>263</v>
       </c>
@@ -3965,7 +4353,9 @@
       <c r="E50" s="5">
         <v>-38.055610000000001</v>
       </c>
-      <c r="F50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>611</v>
+      </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -3981,11 +4371,13 @@
         <v>264</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>265</v>
       </c>
-      <c r="B51" s="5"/>
+      <c r="B51" s="5" t="s">
+        <v>612</v>
+      </c>
       <c r="C51" s="5" t="s">
         <v>266</v>
       </c>
@@ -3995,7 +4387,9 @@
       <c r="E51" s="5">
         <v>-38.055759999999999</v>
       </c>
-      <c r="F51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
@@ -4019,7 +4413,9 @@
       <c r="A52" t="s">
         <v>268</v>
       </c>
-      <c r="B52" s="5"/>
+      <c r="B52" s="5" t="s">
+        <v>613</v>
+      </c>
       <c r="C52" s="5" t="s">
         <v>150</v>
       </c>
@@ -4029,7 +4425,9 @@
       <c r="E52" s="5">
         <v>-38.055729999999997</v>
       </c>
-      <c r="F52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>614</v>
+      </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
@@ -4049,11 +4447,13 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>271</v>
       </c>
-      <c r="B53" s="5"/>
+      <c r="B53" s="5" t="s">
+        <v>615</v>
+      </c>
       <c r="C53" s="5" t="s">
         <v>272</v>
       </c>
@@ -4063,7 +4463,9 @@
       <c r="E53" s="5">
         <v>-38.055720000000001</v>
       </c>
-      <c r="F53" s="5"/>
+      <c r="F53" s="5" t="s">
+        <v>616</v>
+      </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
@@ -4087,7 +4489,9 @@
       <c r="A54" t="s">
         <v>274</v>
       </c>
-      <c r="B54" s="5"/>
+      <c r="B54" s="5" t="s">
+        <v>606</v>
+      </c>
       <c r="C54" s="5" t="s">
         <v>251</v>
       </c>
@@ -4097,7 +4501,9 @@
       <c r="E54" s="5">
         <v>-38.05574</v>
       </c>
-      <c r="F54" s="5"/>
+      <c r="F54" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
@@ -4117,11 +4523,13 @@
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>276</v>
       </c>
-      <c r="B55" s="5"/>
+      <c r="B55" s="5" t="s">
+        <v>617</v>
+      </c>
       <c r="C55" s="5" t="s">
         <v>277</v>
       </c>
@@ -4131,7 +4539,9 @@
       <c r="E55" s="5">
         <v>-38.055689999999998</v>
       </c>
-      <c r="F55" s="5"/>
+      <c r="F55" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
@@ -4151,11 +4561,13 @@
         <v>279</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>280</v>
       </c>
-      <c r="B56" s="5"/>
+      <c r="B56" s="5" t="s">
+        <v>610</v>
+      </c>
       <c r="C56" s="5" t="s">
         <v>281</v>
       </c>
@@ -4165,7 +4577,9 @@
       <c r="E56" s="5">
         <v>-38.055720000000001</v>
       </c>
-      <c r="F56" s="5"/>
+      <c r="F56" s="5" t="s">
+        <v>611</v>
+      </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -4181,11 +4595,13 @@
         <v>282</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>283</v>
       </c>
-      <c r="B57" s="5"/>
+      <c r="B57" s="5" t="s">
+        <v>618</v>
+      </c>
       <c r="C57" s="5" t="s">
         <v>284</v>
       </c>
@@ -4195,7 +4611,9 @@
       <c r="E57" s="5">
         <v>-38.05585</v>
       </c>
-      <c r="F57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>619</v>
+      </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
@@ -4215,11 +4633,13 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>286</v>
       </c>
-      <c r="B58" s="5"/>
+      <c r="B58" s="5" t="s">
+        <v>620</v>
+      </c>
       <c r="C58" s="5" t="s">
         <v>287</v>
       </c>
@@ -4229,7 +4649,9 @@
       <c r="E58" s="5">
         <v>-38.055779999999999</v>
       </c>
-      <c r="F58" s="5"/>
+      <c r="F58" s="5" t="s">
+        <v>621</v>
+      </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -4245,11 +4667,13 @@
         <v>288</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>289</v>
       </c>
-      <c r="B59" s="5"/>
+      <c r="B59" s="5" t="s">
+        <v>622</v>
+      </c>
       <c r="C59" s="5" t="s">
         <v>290</v>
       </c>
@@ -4259,7 +4683,9 @@
       <c r="E59" s="5">
         <v>-38.055900000000001</v>
       </c>
-      <c r="F59" s="5"/>
+      <c r="F59" s="5" t="s">
+        <v>578</v>
+      </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
@@ -4279,11 +4705,13 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>293</v>
       </c>
-      <c r="B60" s="5"/>
+      <c r="B60" s="5" t="s">
+        <v>604</v>
+      </c>
       <c r="C60" s="5" t="s">
         <v>131</v>
       </c>
@@ -4293,7 +4721,9 @@
       <c r="E60" s="5">
         <v>-38.055770000000003</v>
       </c>
-      <c r="F60" s="5"/>
+      <c r="F60" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
@@ -4317,7 +4747,9 @@
       <c r="A61" t="s">
         <v>295</v>
       </c>
-      <c r="B61" s="5"/>
+      <c r="B61" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="C61" s="5" t="s">
         <v>272</v>
       </c>
@@ -4327,7 +4759,9 @@
       <c r="E61" s="5">
         <v>-38.055639999999997</v>
       </c>
-      <c r="F61" s="5"/>
+      <c r="F61" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
@@ -4347,11 +4781,13 @@
         <v>296</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>297</v>
       </c>
-      <c r="B62" s="5"/>
+      <c r="B62" s="5" t="s">
+        <v>622</v>
+      </c>
       <c r="C62" s="5" t="s">
         <v>290</v>
       </c>
@@ -4361,7 +4797,9 @@
       <c r="E62" s="5">
         <v>-38.055669999999999</v>
       </c>
-      <c r="F62" s="5"/>
+      <c r="F62" s="5" t="s">
+        <v>578</v>
+      </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
@@ -4381,11 +4819,13 @@
         <v>298</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>299</v>
       </c>
-      <c r="B63" s="5"/>
+      <c r="B63" s="5" t="s">
+        <v>623</v>
+      </c>
       <c r="C63" s="5" t="s">
         <v>300</v>
       </c>
@@ -4395,7 +4835,9 @@
       <c r="E63" s="5">
         <v>-38.055529999999997</v>
       </c>
-      <c r="F63" s="5"/>
+      <c r="F63" s="5" t="s">
+        <v>624</v>
+      </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
@@ -4415,11 +4857,13 @@
         <v>301</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>302</v>
       </c>
-      <c r="B64" s="5"/>
+      <c r="B64" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="C64" s="5" t="s">
         <v>258</v>
       </c>
@@ -4429,7 +4873,9 @@
       <c r="E64" s="5">
         <v>-38.055540000000001</v>
       </c>
-      <c r="F64" s="5"/>
+      <c r="F64" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
@@ -4449,11 +4895,13 @@
         <v>303</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>304</v>
       </c>
-      <c r="B65" s="5"/>
+      <c r="B65" s="5" t="s">
+        <v>610</v>
+      </c>
       <c r="C65" s="5" t="s">
         <v>263</v>
       </c>
@@ -4463,7 +4911,9 @@
       <c r="E65" s="5">
         <v>-38.055500000000002</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="5" t="s">
+        <v>611</v>
+      </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
@@ -4483,7 +4933,9 @@
       <c r="A66" t="s">
         <v>306</v>
       </c>
-      <c r="B66" s="5"/>
+      <c r="B66" s="5" t="s">
+        <v>625</v>
+      </c>
       <c r="C66" s="5" t="s">
         <v>307</v>
       </c>
@@ -4493,7 +4945,9 @@
       <c r="E66" s="5">
         <v>-38.055599999999998</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="5" t="s">
+        <v>626</v>
+      </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="5" t="s">
@@ -4513,11 +4967,13 @@
         <v>309</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>310</v>
       </c>
-      <c r="B67" s="5"/>
+      <c r="B67" s="5" t="s">
+        <v>615</v>
+      </c>
       <c r="C67" s="5" t="s">
         <v>272</v>
       </c>
@@ -4527,7 +4983,9 @@
       <c r="E67" s="5">
         <v>-38.055230000000002</v>
       </c>
-      <c r="F67" s="5"/>
+      <c r="F67" s="5" t="s">
+        <v>627</v>
+      </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5" t="s">
@@ -4547,11 +5005,13 @@
         <v>311</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>312</v>
       </c>
-      <c r="B68" s="5"/>
+      <c r="B68" s="5" t="s">
+        <v>617</v>
+      </c>
       <c r="C68" s="5" t="s">
         <v>277</v>
       </c>
@@ -4561,7 +5021,9 @@
       <c r="E68" s="5">
         <v>-38.055210000000002</v>
       </c>
-      <c r="F68" s="5"/>
+      <c r="F68" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5" t="s">
@@ -4581,11 +5043,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>314</v>
       </c>
-      <c r="B69" s="5"/>
+      <c r="B69" s="5" t="s">
+        <v>620</v>
+      </c>
       <c r="C69" s="5" t="s">
         <v>287</v>
       </c>
@@ -4595,7 +5059,9 @@
       <c r="E69" s="5">
         <v>-38.055079999999997</v>
       </c>
-      <c r="F69" s="5"/>
+      <c r="F69" s="5" t="s">
+        <v>621</v>
+      </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
@@ -4611,11 +5077,13 @@
         <v>315</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>316</v>
       </c>
-      <c r="B70" s="5"/>
+      <c r="B70" s="5" t="s">
+        <v>628</v>
+      </c>
       <c r="C70" s="5" t="s">
         <v>317</v>
       </c>
@@ -4625,7 +5093,9 @@
       <c r="E70" s="5">
         <v>-38.055019999999999</v>
       </c>
-      <c r="F70" s="5"/>
+      <c r="F70" s="5" t="s">
+        <v>578</v>
+      </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5" t="s">
@@ -4645,11 +5115,13 @@
         <v>318</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>319</v>
       </c>
-      <c r="B71" s="5"/>
+      <c r="B71" s="5" t="s">
+        <v>629</v>
+      </c>
       <c r="C71" s="5" t="s">
         <v>320</v>
       </c>
@@ -4659,7 +5131,9 @@
       <c r="E71" s="5">
         <v>-38.055030000000002</v>
       </c>
-      <c r="F71" s="5"/>
+      <c r="F71" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5" t="s">
@@ -4681,7 +5155,9 @@
       <c r="A72" t="s">
         <v>322</v>
       </c>
-      <c r="B72" s="5"/>
+      <c r="B72" s="5" t="s">
+        <v>630</v>
+      </c>
       <c r="C72" s="5" t="s">
         <v>323</v>
       </c>
@@ -4691,7 +5167,9 @@
       <c r="E72" s="5">
         <v>-38.055320000000002</v>
       </c>
-      <c r="F72" s="5"/>
+      <c r="F72" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5" t="s">
@@ -4711,11 +5189,13 @@
         <v>324</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>325</v>
       </c>
-      <c r="B73" s="5"/>
+      <c r="B73" s="5" t="s">
+        <v>631</v>
+      </c>
       <c r="C73" s="5" t="s">
         <v>326</v>
       </c>
@@ -4725,7 +5205,9 @@
       <c r="E73" s="5">
         <v>-38.055289999999999</v>
       </c>
-      <c r="F73" s="5"/>
+      <c r="F73" s="5" t="s">
+        <v>632</v>
+      </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5" t="s">
@@ -4745,11 +5227,13 @@
         <v>329</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>330</v>
       </c>
-      <c r="B74" s="5"/>
+      <c r="B74" s="5" t="s">
+        <v>633</v>
+      </c>
       <c r="C74" s="5" t="s">
         <v>331</v>
       </c>
@@ -4759,7 +5243,9 @@
       <c r="E74" s="5">
         <v>-38.055529999999997</v>
       </c>
-      <c r="F74" s="5"/>
+      <c r="F74" s="5" t="s">
+        <v>632</v>
+      </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5" t="s">
@@ -4779,11 +5265,13 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>333</v>
       </c>
-      <c r="B75" s="5"/>
+      <c r="B75" s="5" t="s">
+        <v>634</v>
+      </c>
       <c r="C75" s="5" t="s">
         <v>334</v>
       </c>
@@ -4793,7 +5281,9 @@
       <c r="E75" s="5">
         <v>-38.055660000000003</v>
       </c>
-      <c r="F75" s="5"/>
+      <c r="F75" s="5" t="s">
+        <v>588</v>
+      </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5" t="s">
@@ -4813,11 +5303,13 @@
         <v>335</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>336</v>
       </c>
-      <c r="B76" s="5"/>
+      <c r="B76" s="5" t="s">
+        <v>610</v>
+      </c>
       <c r="C76" s="5" t="s">
         <v>263</v>
       </c>
@@ -4827,7 +5319,9 @@
       <c r="E76" s="5">
         <v>-38.055929999999996</v>
       </c>
-      <c r="F76" s="5"/>
+      <c r="F76" s="5" t="s">
+        <v>611</v>
+      </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
@@ -4843,11 +5337,13 @@
         <v>337</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>338</v>
       </c>
-      <c r="B77" s="5"/>
+      <c r="B77" s="5" t="s">
+        <v>612</v>
+      </c>
       <c r="C77" s="5" t="s">
         <v>8</v>
       </c>
@@ -4857,7 +5353,9 @@
       <c r="E77" s="5">
         <v>-38.055999999999997</v>
       </c>
-      <c r="F77" s="5"/>
+      <c r="F77" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
       <c r="I77" s="5" t="s">
@@ -4877,11 +5375,13 @@
         <v>340</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>341</v>
       </c>
-      <c r="B78" s="5"/>
+      <c r="B78" s="5" t="s">
+        <v>577</v>
+      </c>
       <c r="C78" s="5" t="s">
         <v>123</v>
       </c>
@@ -4891,7 +5391,9 @@
       <c r="E78" s="5">
         <v>-38.056220000000003</v>
       </c>
-      <c r="F78" s="5"/>
+      <c r="F78" s="5" t="s">
+        <v>578</v>
+      </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="5" t="s">
@@ -4911,11 +5413,13 @@
         <v>342</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>343</v>
       </c>
-      <c r="B79" s="5"/>
+      <c r="B79" s="5" t="s">
+        <v>591</v>
+      </c>
       <c r="C79" s="5" t="s">
         <v>219</v>
       </c>
@@ -4925,7 +5429,9 @@
       <c r="E79" s="5">
         <v>-38.056489999999997</v>
       </c>
-      <c r="F79" s="5"/>
+      <c r="F79" s="5" t="s">
+        <v>592</v>
+      </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5" t="s">
@@ -4945,11 +5451,13 @@
         <v>345</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" ht="87" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>346</v>
       </c>
-      <c r="B80" s="5"/>
+      <c r="B80" s="5" t="s">
+        <v>635</v>
+      </c>
       <c r="C80" s="5" t="s">
         <v>347</v>
       </c>
@@ -4959,7 +5467,9 @@
       <c r="E80" s="5">
         <v>-38.056080000000001</v>
       </c>
-      <c r="F80" s="5"/>
+      <c r="F80" s="5" t="s">
+        <v>636</v>
+      </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="5" t="s">
@@ -4979,11 +5489,13 @@
         <v>349</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>350</v>
       </c>
-      <c r="B81" s="5"/>
+      <c r="B81" s="5" t="s">
+        <v>637</v>
+      </c>
       <c r="C81" s="5" t="s">
         <v>351</v>
       </c>
@@ -4993,7 +5505,9 @@
       <c r="E81" s="5">
         <v>-38.056100000000001</v>
       </c>
-      <c r="F81" s="5"/>
+      <c r="F81" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5" t="s">
@@ -5017,7 +5531,9 @@
       <c r="A82" t="s">
         <v>353</v>
       </c>
-      <c r="B82" s="5"/>
+      <c r="B82" s="5" t="s">
+        <v>638</v>
+      </c>
       <c r="C82" s="5" t="s">
         <v>323</v>
       </c>
@@ -5027,7 +5543,9 @@
       <c r="E82" s="5">
         <v>-38.05547</v>
       </c>
-      <c r="F82" s="5"/>
+      <c r="F82" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" s="5" t="s">
@@ -5047,11 +5565,13 @@
         <v>354</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>355</v>
       </c>
-      <c r="B83" s="5"/>
+      <c r="B83" s="5" t="s">
+        <v>582</v>
+      </c>
       <c r="C83" s="5" t="s">
         <v>356</v>
       </c>
@@ -5061,7 +5581,9 @@
       <c r="E83" s="5">
         <v>-38.05527</v>
       </c>
-      <c r="F83" s="5"/>
+      <c r="F83" s="5" t="s">
+        <v>614</v>
+      </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -5081,7 +5603,9 @@
       <c r="A84" t="s">
         <v>358</v>
       </c>
-      <c r="B84" s="5"/>
+      <c r="B84" s="5" t="s">
+        <v>599</v>
+      </c>
       <c r="C84" s="5" t="s">
         <v>236</v>
       </c>
@@ -5091,7 +5615,9 @@
       <c r="E84" s="5">
         <v>-38.054609999999997</v>
       </c>
-      <c r="F84" s="5"/>
+      <c r="F84" s="5" t="s">
+        <v>639</v>
+      </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5" t="s">
@@ -5115,7 +5641,9 @@
       <c r="A85" t="s">
         <v>360</v>
       </c>
-      <c r="B85" s="5"/>
+      <c r="B85" s="5" t="s">
+        <v>640</v>
+      </c>
       <c r="C85" s="5" t="s">
         <v>361</v>
       </c>
@@ -5125,7 +5653,9 @@
       <c r="E85" s="5">
         <v>-38.05491</v>
       </c>
-      <c r="F85" s="5"/>
+      <c r="F85" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5" t="s">
@@ -5149,7 +5679,9 @@
       <c r="A86" t="s">
         <v>364</v>
       </c>
-      <c r="B86" s="5"/>
+      <c r="B86" s="5" t="s">
+        <v>599</v>
+      </c>
       <c r="C86" s="5" t="s">
         <v>236</v>
       </c>
@@ -5159,7 +5691,9 @@
       <c r="E86" s="5">
         <v>-38.054940000000002</v>
       </c>
-      <c r="F86" s="5"/>
+      <c r="F86" s="5" t="s">
+        <v>639</v>
+      </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5" t="s">
@@ -5183,7 +5717,9 @@
       <c r="A87" t="s">
         <v>366</v>
       </c>
-      <c r="B87" s="5"/>
+      <c r="B87" s="5" t="s">
+        <v>599</v>
+      </c>
       <c r="C87" s="5" t="s">
         <v>236</v>
       </c>
@@ -5193,7 +5729,9 @@
       <c r="E87" s="5">
         <v>-38.055030000000002</v>
       </c>
-      <c r="F87" s="5"/>
+      <c r="F87" s="5" t="s">
+        <v>639</v>
+      </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5" t="s">
@@ -5217,7 +5755,9 @@
       <c r="A88" t="s">
         <v>368</v>
       </c>
-      <c r="B88" s="5"/>
+      <c r="B88" s="5" t="s">
+        <v>642</v>
+      </c>
       <c r="C88" s="5" t="s">
         <v>116</v>
       </c>
@@ -5227,7 +5767,9 @@
       <c r="E88" s="5">
         <v>-38.055059999999997</v>
       </c>
-      <c r="F88" s="5"/>
+      <c r="F88" s="5" t="s">
+        <v>576</v>
+      </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5" t="s">
@@ -5251,7 +5793,9 @@
       <c r="A89" t="s">
         <v>370</v>
       </c>
-      <c r="B89" s="5"/>
+      <c r="B89" s="5" t="s">
+        <v>642</v>
+      </c>
       <c r="C89" s="5" t="s">
         <v>116</v>
       </c>
@@ -5261,7 +5805,9 @@
       <c r="E89" s="5">
         <v>-38.055280000000003</v>
       </c>
-      <c r="F89" s="5"/>
+      <c r="F89" s="5" t="s">
+        <v>576</v>
+      </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5" t="s">
@@ -5285,7 +5831,9 @@
       <c r="A90" t="s">
         <v>372</v>
       </c>
-      <c r="B90" s="5"/>
+      <c r="B90" s="5" t="s">
+        <v>591</v>
+      </c>
       <c r="C90" s="5" t="s">
         <v>219</v>
       </c>
@@ -5295,7 +5843,9 @@
       <c r="E90" s="5">
         <v>-38.055250000000001</v>
       </c>
-      <c r="F90" s="5"/>
+      <c r="F90" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5" t="s">
@@ -5319,7 +5869,9 @@
       <c r="A91" t="s">
         <v>374</v>
       </c>
-      <c r="B91" s="5"/>
+      <c r="B91" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="C91" s="5" t="s">
         <v>375</v>
       </c>
@@ -5329,7 +5881,9 @@
       <c r="E91" s="5">
         <v>-38.055039999999998</v>
       </c>
-      <c r="F91" s="5"/>
+      <c r="F91" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5" t="s">
@@ -5349,11 +5903,13 @@
         <v>376</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>377</v>
       </c>
-      <c r="B92" s="5"/>
+      <c r="B92" s="5" t="s">
+        <v>644</v>
+      </c>
       <c r="C92" s="5" t="s">
         <v>378</v>
       </c>
@@ -5363,7 +5919,9 @@
       <c r="E92" s="5">
         <v>-38.055100000000003</v>
       </c>
-      <c r="F92" s="5"/>
+      <c r="F92" s="5" t="s">
+        <v>614</v>
+      </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60765BE-D457-4408-80A1-39AE4DC9C857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9359AE-7068-4205-90F9-81A65421ADC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2421,6 +2421,7 @@
   <cols>
     <col min="2" max="2" width="19.81640625" customWidth="1"/>
     <col min="3" max="3" width="27.36328125" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
     <col min="9" max="9" width="14.54296875" customWidth="1"/>
     <col min="18" max="18" width="13.36328125" customWidth="1"/>
   </cols>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9359AE-7068-4205-90F9-81A65421ADC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5F51D9-CD3E-42FF-8E40-7B48E96D6664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="659">
   <si>
     <t>id</t>
   </si>
@@ -1976,6 +1976,48 @@
   </si>
   <si>
     <t>Olmo</t>
+  </si>
+  <si>
+    <t>Permanente</t>
+  </si>
+  <si>
+    <t>Todo el año</t>
+  </si>
+  <si>
+    <t>Todo el año (Más visible en Otoño/Invierno)</t>
+  </si>
+  <si>
+    <t>Permanente / Visitante estival</t>
+  </si>
+  <si>
+    <t>Todo el año (Mayor abundancia en Primavera/Verano)</t>
+  </si>
+  <si>
+    <t>Visitante invernal / Escaso</t>
+  </si>
+  <si>
+    <t>Otoño e Invierno</t>
+  </si>
+  <si>
+    <t>Migratorio estival</t>
+  </si>
+  <si>
+    <t>Primavera y Verano</t>
+  </si>
+  <si>
+    <t>Permanente / Movimientos locales</t>
+  </si>
+  <si>
+    <t>Primavera y Verano (Emblemático de Verano)</t>
+  </si>
+  <si>
+    <t>Migratorio interno / Permanente</t>
+  </si>
+  <si>
+    <t>Todo el año (Más abundante en Otoño/Invierno)</t>
+  </si>
+  <si>
+    <t>residencia</t>
   </si>
 </sst>
 </file>
@@ -5947,7 +5989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A580122F-82B9-4D2E-B07E-0D8C98A0F809}">
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
@@ -5958,9 +6000,10 @@
     <col min="7" max="7" width="12.08984375" customWidth="1"/>
     <col min="9" max="10" width="16.08984375" customWidth="1"/>
     <col min="12" max="12" width="19.36328125" customWidth="1"/>
+    <col min="13" max="14" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -5997,8 +6040,14 @@
       <c r="L1" s="8" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M1" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>72</v>
       </c>
@@ -6027,8 +6076,14 @@
         <v>519</v>
       </c>
       <c r="L2" s="9"/>
-    </row>
-    <row r="3" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M2" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
         <v>73</v>
       </c>
@@ -6057,8 +6112,14 @@
         <v>548</v>
       </c>
       <c r="L3" s="9"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M3" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>389</v>
       </c>
@@ -6077,8 +6138,14 @@
       <c r="J4" s="13"/>
       <c r="K4" s="5"/>
       <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M4" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
         <v>391</v>
       </c>
@@ -6097,8 +6164,14 @@
       <c r="J5" s="13"/>
       <c r="K5" s="5"/>
       <c r="L5" s="9"/>
-    </row>
-    <row r="6" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M5" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>392</v>
       </c>
@@ -6123,8 +6196,14 @@
         <v>520</v>
       </c>
       <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M6" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
         <v>394</v>
       </c>
@@ -6145,8 +6224,14 @@
         <v>549</v>
       </c>
       <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M7" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
         <v>396</v>
       </c>
@@ -6171,8 +6256,14 @@
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M8" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
         <v>398</v>
       </c>
@@ -6191,8 +6282,14 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M9" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
         <v>400</v>
       </c>
@@ -6219,8 +6316,14 @@
         <v>550</v>
       </c>
       <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M10" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
         <v>402</v>
       </c>
@@ -6247,8 +6350,14 @@
         <v>551</v>
       </c>
       <c r="L11" s="9"/>
-    </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M11" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
         <v>404</v>
       </c>
@@ -6267,8 +6376,14 @@
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M12" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
         <v>406</v>
       </c>
@@ -6287,8 +6402,14 @@
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M13" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
         <v>408</v>
       </c>
@@ -6307,8 +6428,14 @@
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M14" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
         <v>410</v>
       </c>
@@ -6327,8 +6454,14 @@
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M15" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="9" t="s">
         <v>412</v>
       </c>
@@ -6347,8 +6480,14 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M16" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
         <v>414</v>
       </c>
@@ -6367,8 +6506,14 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M17" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="9" t="s">
         <v>416</v>
       </c>
@@ -6395,8 +6540,14 @@
         <v>522</v>
       </c>
       <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M18" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="9" t="s">
         <v>418</v>
       </c>
@@ -6415,8 +6566,14 @@
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M19" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
         <v>420</v>
       </c>
@@ -6435,8 +6592,14 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M20" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
         <v>422</v>
       </c>
@@ -6455,8 +6618,14 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M21" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
         <v>424</v>
       </c>
@@ -6483,8 +6652,14 @@
         <v>552</v>
       </c>
       <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M22" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
         <v>426</v>
       </c>
@@ -6503,8 +6678,14 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="9"/>
-    </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M23" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
         <v>428</v>
       </c>
@@ -6523,8 +6704,14 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M24" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="9" t="s">
         <v>430</v>
       </c>
@@ -6551,8 +6738,14 @@
         <v>547</v>
       </c>
       <c r="L25" s="9"/>
-    </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M25" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
         <v>432</v>
       </c>
@@ -6571,8 +6764,14 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="9"/>
-    </row>
-    <row r="27" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M26" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="9" t="s">
         <v>434</v>
       </c>
@@ -6599,8 +6798,14 @@
         <v>559</v>
       </c>
       <c r="L27" s="9"/>
-    </row>
-    <row r="28" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M27" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="9" t="s">
         <v>436</v>
       </c>
@@ -6619,8 +6824,14 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="9"/>
-    </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M28" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
         <v>438</v>
       </c>
@@ -6639,8 +6850,14 @@
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="9"/>
-    </row>
-    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M29" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="9" t="s">
         <v>440</v>
       </c>
@@ -6659,8 +6876,14 @@
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="9"/>
-    </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M30" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="9" t="s">
         <v>442</v>
       </c>
@@ -6679,8 +6902,14 @@
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="9"/>
-    </row>
-    <row r="32" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M31" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="9" t="s">
         <v>444</v>
       </c>
@@ -6707,8 +6936,14 @@
         <v>558</v>
       </c>
       <c r="L32" s="9"/>
-    </row>
-    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M32" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="9" t="s">
         <v>446</v>
       </c>
@@ -6727,8 +6962,14 @@
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="9"/>
-    </row>
-    <row r="34" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M33" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="9" t="s">
         <v>448</v>
       </c>
@@ -6749,8 +6990,14 @@
         <v>553</v>
       </c>
       <c r="L34" s="9"/>
-    </row>
-    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M34" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="9" t="s">
         <v>450</v>
       </c>
@@ -6769,8 +7016,14 @@
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="9"/>
-    </row>
-    <row r="36" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M35" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="9" t="s">
         <v>452</v>
       </c>
@@ -6797,8 +7050,14 @@
         <v>554</v>
       </c>
       <c r="L36" s="9"/>
-    </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M36" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="9" t="s">
         <v>454</v>
       </c>
@@ -6817,8 +7076,14 @@
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="9"/>
-    </row>
-    <row r="38" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M37" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="9" t="s">
         <v>456</v>
       </c>
@@ -6845,8 +7110,14 @@
         <v>555</v>
       </c>
       <c r="L38" s="9"/>
-    </row>
-    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M38" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
         <v>458</v>
       </c>
@@ -6865,8 +7136,14 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="9"/>
-    </row>
-    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M39" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
         <v>460</v>
       </c>
@@ -6885,8 +7162,14 @@
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="9"/>
-    </row>
-    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M40" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N40" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
         <v>462</v>
       </c>
@@ -6913,8 +7196,14 @@
         <v>556</v>
       </c>
       <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M41" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N41" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="9" t="s">
         <v>464</v>
       </c>
@@ -6941,8 +7230,14 @@
         <v>521</v>
       </c>
       <c r="L42" s="9"/>
-    </row>
-    <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M42" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="9" t="s">
         <v>466</v>
       </c>
@@ -6961,8 +7256,14 @@
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="9"/>
-    </row>
-    <row r="44" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M43" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="9" t="s">
         <v>468</v>
       </c>
@@ -6983,8 +7284,14 @@
         <v>527</v>
       </c>
       <c r="L44" s="9"/>
-    </row>
-    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M44" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N44" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="9" t="s">
         <v>470</v>
       </c>
@@ -7003,8 +7310,14 @@
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="9"/>
-    </row>
-    <row r="46" spans="1:12" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M45" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="9" t="s">
         <v>472</v>
       </c>
@@ -7031,8 +7344,14 @@
         <v>557</v>
       </c>
       <c r="L46" s="9"/>
-    </row>
-    <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M46" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="N46" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="9" t="s">
         <v>474</v>
       </c>
@@ -7051,8 +7370,14 @@
       <c r="J47" s="13"/>
       <c r="K47" s="5"/>
       <c r="L47" s="9"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M47" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="K48" s="5"/>
     </row>
     <row r="49" spans="11:11" x14ac:dyDescent="0.35">

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5F51D9-CD3E-42FF-8E40-7B48E96D6664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491DD50A-E8A7-452E-96FF-E0E63C321177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -1630,21 +1630,12 @@
     <t>gavilanmixto.jpg</t>
   </si>
   <si>
-    <t>gorrion.jpg</t>
-  </si>
-  <si>
     <t>hornero.jpg</t>
   </si>
   <si>
-    <t>lechucitavizcachera.jpg</t>
-  </si>
-  <si>
     <t>pechoamarillo.jpg</t>
   </si>
   <si>
-    <t>picazuro.jpg</t>
-  </si>
-  <si>
     <t>pirincho.jpg</t>
   </si>
   <si>
@@ -1666,9 +1657,6 @@
     <t xml:space="preserve">calandria.jpg </t>
   </si>
   <si>
-    <t xml:space="preserve">carpinteroscampestres.jpg </t>
-  </si>
-  <si>
     <t xml:space="preserve">chingolo.jpg </t>
   </si>
   <si>
@@ -1678,9 +1666,6 @@
     <t xml:space="preserve">tordorenegrido.jpg </t>
   </si>
   <si>
-    <t>tero.JPG</t>
-  </si>
-  <si>
     <t>foto1</t>
   </si>
   <si>
@@ -2018,6 +2003,21 @@
   </si>
   <si>
     <t>residencia</t>
+  </si>
+  <si>
+    <t>Limpiatubos.jpg</t>
+  </si>
+  <si>
+    <t>Eucaliptoaustraliano.jpg</t>
+  </si>
+  <si>
+    <t>Cedroverdedeodara.jpg</t>
+  </si>
+  <si>
+    <t>Cedroazul.jpg</t>
+  </si>
+  <si>
+    <t>Roblerojoamericano.jpg</t>
   </si>
 </sst>
 </file>
@@ -2464,6 +2464,7 @@
     <col min="2" max="2" width="19.81640625" customWidth="1"/>
     <col min="3" max="3" width="27.36328125" customWidth="1"/>
     <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="12.7265625" customWidth="1"/>
     <col min="9" max="9" width="14.54296875" customWidth="1"/>
     <col min="18" max="18" width="13.36328125" customWidth="1"/>
   </cols>
@@ -2547,7 +2548,7 @@
         <v>-38.056790999999997</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G2" s="5">
         <v>2004</v>
@@ -2595,11 +2596,11 @@
         <v>-38.056471999999999</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>82</v>
@@ -2638,11 +2639,11 @@
         <v>-38.056541000000003</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2678,11 +2679,11 @@
         <v>-38.056569000000003</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2723,7 +2724,7 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>541</v>
+        <v>656</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2759,11 +2760,11 @@
         <v>-38.056437000000003</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>101</v>
@@ -2799,11 +2800,11 @@
         <v>-38.056372000000003</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>107</v>
@@ -2839,7 +2840,7 @@
         <v>-38.056238999999998</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
@@ -2879,11 +2880,11 @@
         <v>-38.056201000000001</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>529</v>
+        <v>657</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2923,7 +2924,7 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>120</v>
@@ -2957,11 +2958,11 @@
         <v>-38.056331</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>531</v>
+        <v>655</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2997,11 +2998,11 @@
         <v>-38.056328999999998</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>78</v>
@@ -3020,7 +3021,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>129</v>
       </c>
@@ -3037,11 +3038,11 @@
         <v>-38.056373000000001</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>533</v>
+        <v>658</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -3077,11 +3078,11 @@
         <v>-38.056550999999999</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -3122,7 +3123,7 @@
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>82</v>
@@ -3158,11 +3159,13 @@
         <v>-38.056727000000002</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="G17" s="5"/>
+        <v>575</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1988</v>
+      </c>
       <c r="H17" s="5" t="s">
-        <v>545</v>
+        <v>654</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -3201,11 +3204,11 @@
         <v>-38.056677999999998</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>147</v>
@@ -3239,11 +3242,11 @@
         <v>-38.056843999999998</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -3279,11 +3282,11 @@
         <v>-38.057062000000002</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -3319,7 +3322,7 @@
         <v>-38.057076000000002</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
@@ -3342,7 +3345,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>163</v>
       </c>
@@ -3359,9 +3362,11 @@
         <v>-38.057192000000001</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="G22" s="5"/>
+        <v>566</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1990</v>
+      </c>
       <c r="H22" s="5" t="s">
         <v>387</v>
       </c>
@@ -3382,7 +3387,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -3399,11 +3404,11 @@
         <v>-38.056908999999997</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>387</v>
+        <v>557</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>171</v>
@@ -3427,7 +3432,7 @@
         <v>173</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>174</v>
@@ -3439,7 +3444,7 @@
         <v>-38.056840000000001</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
@@ -3467,7 +3472,7 @@
         <v>176</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>127</v>
@@ -3479,7 +3484,7 @@
         <v>-38.056933999999998</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
@@ -3519,7 +3524,7 @@
         <v>-38.056655999999997</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
@@ -3559,7 +3564,7 @@
         <v>-38.055928999999999</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
@@ -3599,7 +3604,7 @@
         <v>-38.056055999999998</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
@@ -3639,7 +3644,7 @@
         <v>-38.056057000000003</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
@@ -3679,7 +3684,7 @@
         <v>-38.056168</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
@@ -3719,7 +3724,7 @@
         <v>-38.056126999999996</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
@@ -3759,7 +3764,7 @@
         <v>-38.056092999999997</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
@@ -3799,7 +3804,7 @@
         <v>-38.056373999999998</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
@@ -3839,7 +3844,7 @@
         <v>-38.056545</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
@@ -3867,7 +3872,7 @@
         <v>215</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>216</v>
@@ -3875,7 +3880,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3899,7 +3904,7 @@
         <v>218</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>219</v>
@@ -3907,7 +3912,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3931,7 +3936,7 @@
         <v>221</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>222</v>
@@ -3939,7 +3944,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -3963,7 +3968,7 @@
         <v>224</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>225</v>
@@ -3971,7 +3976,7 @@
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -3995,7 +4000,7 @@
         <v>227</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>228</v>
@@ -4003,7 +4008,7 @@
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -4027,7 +4032,7 @@
         <v>231</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>232</v>
@@ -4035,7 +4040,7 @@
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -4059,7 +4064,7 @@
         <v>235</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>236</v>
@@ -4067,7 +4072,7 @@
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -4091,7 +4096,7 @@
         <v>239</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>240</v>
@@ -4099,11 +4104,11 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>171</v>
@@ -4125,7 +4130,7 @@
         <v>242</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>243</v>
@@ -4133,7 +4138,7 @@
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -4157,7 +4162,7 @@
         <v>245</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>131</v>
@@ -4169,7 +4174,7 @@
         <v>-38.055799999999998</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -4195,7 +4200,7 @@
         <v>247</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>135</v>
@@ -4207,7 +4212,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -4233,7 +4238,7 @@
         <v>250</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>251</v>
@@ -4245,7 +4250,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4271,7 +4276,7 @@
         <v>254</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>255</v>
@@ -4283,7 +4288,7 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -4309,7 +4314,7 @@
         <v>257</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>258</v>
@@ -4321,7 +4326,7 @@
         <v>-38.055639999999997</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4347,7 +4352,7 @@
         <v>260</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>258</v>
@@ -4359,7 +4364,7 @@
         <v>-38.055630000000001</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4385,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>263</v>
@@ -4397,7 +4402,7 @@
         <v>-38.055610000000001</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -4414,12 +4419,12 @@
         <v>264</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>265</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>266</v>
@@ -4431,9 +4436,11 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G51" s="5"/>
+        <v>602</v>
+      </c>
+      <c r="G51" s="5">
+        <v>2002</v>
+      </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
         <v>199</v>
@@ -4457,7 +4464,7 @@
         <v>268</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>150</v>
@@ -4469,7 +4476,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4495,7 +4502,7 @@
         <v>271</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>272</v>
@@ -4507,7 +4514,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4533,7 +4540,7 @@
         <v>274</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>251</v>
@@ -4545,7 +4552,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4571,7 +4578,7 @@
         <v>276</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>277</v>
@@ -4583,7 +4590,7 @@
         <v>-38.055689999999998</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4609,7 +4616,7 @@
         <v>280</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>281</v>
@@ -4621,7 +4628,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4643,7 +4650,7 @@
         <v>283</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>284</v>
@@ -4655,7 +4662,7 @@
         <v>-38.05585</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4681,7 +4688,7 @@
         <v>286</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>287</v>
@@ -4693,7 +4700,7 @@
         <v>-38.055779999999999</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -4715,7 +4722,7 @@
         <v>289</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>290</v>
@@ -4727,7 +4734,7 @@
         <v>-38.055900000000001</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -4753,7 +4760,7 @@
         <v>293</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>131</v>
@@ -4765,7 +4772,7 @@
         <v>-38.055770000000003</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -4829,7 +4836,7 @@
         <v>297</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>290</v>
@@ -4841,7 +4848,7 @@
         <v>-38.055669999999999</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -4867,7 +4874,7 @@
         <v>299</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>300</v>
@@ -4879,7 +4886,7 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -4905,7 +4912,7 @@
         <v>302</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>258</v>
@@ -4917,7 +4924,7 @@
         <v>-38.055540000000001</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -4943,7 +4950,7 @@
         <v>304</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>263</v>
@@ -4955,7 +4962,7 @@
         <v>-38.055500000000002</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -4977,7 +4984,7 @@
         <v>306</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>307</v>
@@ -4989,7 +4996,7 @@
         <v>-38.055599999999998</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -5015,7 +5022,7 @@
         <v>310</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>272</v>
@@ -5027,7 +5034,7 @@
         <v>-38.055230000000002</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -5053,7 +5060,7 @@
         <v>312</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>277</v>
@@ -5065,7 +5072,7 @@
         <v>-38.055210000000002</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5091,7 +5098,7 @@
         <v>314</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>287</v>
@@ -5103,7 +5110,7 @@
         <v>-38.055079999999997</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5125,7 +5132,7 @@
         <v>316</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>317</v>
@@ -5137,7 +5144,7 @@
         <v>-38.055019999999999</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5163,7 +5170,7 @@
         <v>319</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>320</v>
@@ -5175,7 +5182,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5199,7 +5206,7 @@
         <v>322</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>323</v>
@@ -5211,7 +5218,7 @@
         <v>-38.055320000000002</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5237,7 +5244,7 @@
         <v>325</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>326</v>
@@ -5249,7 +5256,7 @@
         <v>-38.055289999999999</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5275,7 +5282,7 @@
         <v>330</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>331</v>
@@ -5287,7 +5294,7 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5313,7 +5320,7 @@
         <v>333</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>334</v>
@@ -5325,7 +5332,7 @@
         <v>-38.055660000000003</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5351,7 +5358,7 @@
         <v>336</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>263</v>
@@ -5363,7 +5370,7 @@
         <v>-38.055929999999996</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5385,7 +5392,7 @@
         <v>338</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>8</v>
@@ -5397,7 +5404,7 @@
         <v>-38.055999999999997</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5423,7 +5430,7 @@
         <v>341</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>123</v>
@@ -5435,7 +5442,7 @@
         <v>-38.056220000000003</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5461,7 +5468,7 @@
         <v>343</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>219</v>
@@ -5473,7 +5480,7 @@
         <v>-38.056489999999997</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5499,7 +5506,7 @@
         <v>346</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>347</v>
@@ -5511,7 +5518,7 @@
         <v>-38.056080000000001</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5537,7 +5544,7 @@
         <v>350</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>351</v>
@@ -5549,7 +5556,7 @@
         <v>-38.056100000000001</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5575,7 +5582,7 @@
         <v>353</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>323</v>
@@ -5587,7 +5594,7 @@
         <v>-38.05547</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5613,7 +5620,7 @@
         <v>355</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>356</v>
@@ -5625,7 +5632,7 @@
         <v>-38.05527</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5647,7 +5654,7 @@
         <v>358</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>236</v>
@@ -5659,7 +5666,7 @@
         <v>-38.054609999999997</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5685,7 +5692,7 @@
         <v>360</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>361</v>
@@ -5697,7 +5704,7 @@
         <v>-38.05491</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5723,7 +5730,7 @@
         <v>364</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>236</v>
@@ -5735,7 +5742,7 @@
         <v>-38.054940000000002</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5761,7 +5768,7 @@
         <v>366</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>236</v>
@@ -5773,7 +5780,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5799,7 +5806,7 @@
         <v>368</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>116</v>
@@ -5811,7 +5818,7 @@
         <v>-38.055059999999997</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5837,7 +5844,7 @@
         <v>370</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>116</v>
@@ -5849,7 +5856,7 @@
         <v>-38.055280000000003</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5875,7 +5882,7 @@
         <v>372</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>219</v>
@@ -5887,7 +5894,7 @@
         <v>-38.055250000000001</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -5913,7 +5920,7 @@
         <v>374</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>375</v>
@@ -5951,7 +5958,7 @@
         <v>377</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>378</v>
@@ -5963,7 +5970,7 @@
         <v>-38.055100000000003</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6032,7 +6039,7 @@
         <v>62</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -6041,7 +6048,7 @@
         <v>388</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>65</v>
@@ -6077,10 +6084,10 @@
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -6109,14 +6116,14 @@
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6139,10 +6146,10 @@
       <c r="K4" s="5"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6165,10 +6172,10 @@
       <c r="K5" s="5"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6197,10 +6204,10 @@
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6221,14 +6228,14 @@
       <c r="I7" s="9"/>
       <c r="J7" s="13"/>
       <c r="K7" s="5" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6257,10 +6264,10 @@
       <c r="K8" s="5"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6283,10 +6290,10 @@
       <c r="K9" s="5"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6313,14 +6320,14 @@
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="L10" s="9"/>
       <c r="M10" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6347,14 +6354,14 @@
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="L11" s="9"/>
       <c r="M11" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6377,10 +6384,10 @@
       <c r="K12" s="5"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6403,10 +6410,10 @@
       <c r="K13" s="5"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6429,10 +6436,10 @@
       <c r="K14" s="5"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6455,10 +6462,10 @@
       <c r="K15" s="5"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6481,10 +6488,10 @@
       <c r="K16" s="5"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6507,10 +6514,10 @@
       <c r="K17" s="5"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6541,10 +6548,10 @@
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6567,10 +6574,10 @@
       <c r="K19" s="5"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6593,10 +6600,10 @@
       <c r="K20" s="5"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6619,10 +6626,10 @@
       <c r="K21" s="5"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6649,14 +6656,14 @@
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="L22" s="9"/>
       <c r="M22" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6679,10 +6686,10 @@
       <c r="K23" s="5"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6705,10 +6712,10 @@
       <c r="K24" s="5"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6735,14 +6742,14 @@
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6765,10 +6772,10 @@
       <c r="K26" s="5"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -6795,14 +6802,14 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="L27" s="9"/>
       <c r="M27" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6825,10 +6832,10 @@
       <c r="K28" s="5"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6851,10 +6858,10 @@
       <c r="K29" s="5"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6877,10 +6884,10 @@
       <c r="K30" s="5"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6903,10 +6910,10 @@
       <c r="K31" s="5"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6933,14 +6940,14 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="L32" s="9"/>
       <c r="M32" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6963,10 +6970,10 @@
       <c r="K33" s="5"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6987,14 +6994,14 @@
       <c r="I34" s="9"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7017,10 +7024,10 @@
       <c r="K35" s="5"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7047,14 +7054,14 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7077,10 +7084,10 @@
       <c r="K37" s="5"/>
       <c r="L37" s="9"/>
       <c r="M37" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7107,14 +7114,14 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="L38" s="9"/>
       <c r="M38" s="9" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7137,10 +7144,10 @@
       <c r="K39" s="5"/>
       <c r="L39" s="9"/>
       <c r="M39" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7163,10 +7170,10 @@
       <c r="K40" s="5"/>
       <c r="L40" s="9"/>
       <c r="M40" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7193,14 +7200,14 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="L41" s="9"/>
       <c r="M41" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7231,10 +7238,10 @@
       </c>
       <c r="L42" s="9"/>
       <c r="M42" s="9" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7257,10 +7264,10 @@
       <c r="K43" s="5"/>
       <c r="L43" s="9"/>
       <c r="M43" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7285,10 +7292,10 @@
       </c>
       <c r="L44" s="9"/>
       <c r="M44" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7311,10 +7318,10 @@
       <c r="K45" s="5"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -7341,14 +7348,14 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="9" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7371,10 +7378,10 @@
       <c r="K47" s="5"/>
       <c r="L47" s="9"/>
       <c r="M47" s="9" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -7700,7 +7707,7 @@
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -7723,7 +7730,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>47</v>
@@ -7746,7 +7753,7 @@
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>49</v>
@@ -7769,10 +7776,10 @@
         <v>-38.056685000000002</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -7780,7 +7787,7 @@
         <v>383</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>386</v>
@@ -7792,7 +7799,7 @@
         <v>-38.056984999999997</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7800,7 +7807,7 @@
         <v>384</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>385</v>
@@ -7812,7 +7819,7 @@
         <v>-38.055428999999997</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491DD50A-E8A7-452E-96FF-E0E63C321177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD782D0-5050-451F-9812-89592D47041E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2618,9 +2618,6 @@
       <c r="R3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -2661,6 +2658,9 @@
       <c r="R4" s="5" t="s">
         <v>89</v>
       </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -2699,9 +2699,6 @@
       <c r="R5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -2742,6 +2739,9 @@
       <c r="R6" s="5" t="s">
         <v>97</v>
       </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -2902,6 +2902,9 @@
       <c r="R10" s="5" t="s">
         <v>118</v>
       </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -3060,6 +3063,9 @@
       <c r="R14" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -3426,6 +3432,9 @@
       <c r="R23" s="5" t="s">
         <v>172</v>
       </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:19" ht="29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
@@ -3586,6 +3595,9 @@
       <c r="R27" s="5" t="s">
         <v>183</v>
       </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:19" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
@@ -3666,6 +3678,9 @@
       <c r="R29" s="5" t="s">
         <v>190</v>
       </c>
+      <c r="S29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
@@ -3746,6 +3761,9 @@
       <c r="R31" s="5" t="s">
         <v>200</v>
       </c>
+      <c r="S31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
@@ -3787,7 +3805,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>206</v>
       </c>
@@ -3826,8 +3844,11 @@
       <c r="R33" s="5" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="S33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>210</v>
       </c>
@@ -3867,7 +3888,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>215</v>
       </c>
@@ -3898,8 +3919,11 @@
       <c r="R35" s="5" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="S35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>218</v>
       </c>
@@ -3931,7 +3955,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>221</v>
       </c>
@@ -3963,7 +3987,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>224</v>
       </c>
@@ -3995,7 +4019,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>227</v>
       </c>
@@ -4027,7 +4051,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>231</v>
       </c>
@@ -4059,7 +4083,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>235</v>
       </c>
@@ -4091,7 +4115,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>239</v>
       </c>
@@ -4124,8 +4148,11 @@
       <c r="R42" s="5" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="S42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>242</v>
       </c>
@@ -4156,8 +4183,11 @@
       <c r="R43" s="5" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="S43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>245</v>
       </c>
@@ -4195,7 +4225,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>247</v>
       </c>
@@ -4233,7 +4263,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>250</v>
       </c>
@@ -4271,7 +4301,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>254</v>
       </c>
@@ -4309,7 +4339,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>257</v>
       </c>
@@ -4347,7 +4377,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>260</v>
       </c>
@@ -4385,7 +4415,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>262</v>
       </c>
@@ -4419,7 +4449,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>265</v>
       </c>
@@ -4458,8 +4488,11 @@
       <c r="R51" s="5" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="S51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>268</v>
       </c>
@@ -4497,7 +4530,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>271</v>
       </c>
@@ -4535,7 +4568,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>274</v>
       </c>
@@ -4573,7 +4606,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>276</v>
       </c>
@@ -4611,7 +4644,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>280</v>
       </c>
@@ -4645,7 +4678,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>283</v>
       </c>
@@ -4683,7 +4716,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>286</v>
       </c>
@@ -4717,7 +4750,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>289</v>
       </c>
@@ -4755,7 +4788,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>293</v>
       </c>
@@ -4793,7 +4826,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>295</v>
       </c>
@@ -4831,7 +4864,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>297</v>
       </c>
@@ -4869,7 +4902,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>299</v>
       </c>
@@ -4907,7 +4940,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>302</v>
       </c>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD782D0-5050-451F-9812-89592D47041E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043A9A98-5F86-40C9-8D8B-FDF7951D0BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="656">
   <si>
     <t>id</t>
   </si>
@@ -1627,45 +1627,6 @@
     <t>Torcaza.JPG</t>
   </si>
   <si>
-    <t>gavilanmixto.jpg</t>
-  </si>
-  <si>
-    <t>hornero.jpg</t>
-  </si>
-  <si>
-    <t>pechoamarillo.jpg</t>
-  </si>
-  <si>
-    <t>pirincho.jpg</t>
-  </si>
-  <si>
-    <t>suiriríreal.jpg</t>
-  </si>
-  <si>
-    <t>tyrannussavana.jpg</t>
-  </si>
-  <si>
-    <t>torcaza.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zorzalcolorado.jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">carancho.jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">calandria.jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">chingolo.jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">chimango.jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tordorenegrido.jpg </t>
-  </si>
-  <si>
     <t>foto1</t>
   </si>
   <si>
@@ -2018,6 +1979,36 @@
   </si>
   <si>
     <t>Roblerojoamericano.jpg</t>
+  </si>
+  <si>
+    <t>Quercusrobur.jpg</t>
+  </si>
+  <si>
+    <t>Falsomuerdago.jpg</t>
+  </si>
+  <si>
+    <t>Abeto.jpg</t>
+  </si>
+  <si>
+    <t>Magnolia.jpg</t>
+  </si>
+  <si>
+    <t>Tilo.jpg</t>
+  </si>
+  <si>
+    <t>Cedrojapones.jpg</t>
+  </si>
+  <si>
+    <t>Castañodeindias.jpg</t>
+  </si>
+  <si>
+    <t>Crataegus</t>
+  </si>
+  <si>
+    <t>Crataegus.jpg</t>
+  </si>
+  <si>
+    <t>Platanus.jpg</t>
   </si>
 </sst>
 </file>
@@ -2548,7 +2539,7 @@
         <v>-38.056790999999997</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G2" s="5">
         <v>2004</v>
@@ -2579,7 +2570,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -2596,12 +2587,10 @@
         <v>-38.056471999999999</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
-        <v>535</v>
-      </c>
+      <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
         <v>82</v>
       </c>
@@ -2619,7 +2608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -2636,11 +2625,11 @@
         <v>-38.056541000000003</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>537</v>
+        <v>646</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2662,7 +2651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -2679,11 +2668,11 @@
         <v>-38.056569000000003</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>536</v>
+        <v>647</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2721,7 +2710,7 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2743,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -2760,12 +2749,10 @@
         <v>-38.056437000000003</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
-        <v>539</v>
-      </c>
+      <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
         <v>101</v>
       </c>
@@ -2783,7 +2770,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -2800,12 +2787,10 @@
         <v>-38.056372000000003</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
-        <v>538</v>
-      </c>
+      <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
         <v>107</v>
       </c>
@@ -2840,12 +2825,10 @@
         <v>-38.056238999999998</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
-        <v>528</v>
-      </c>
+      <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
         <v>78</v>
       </c>
@@ -2880,11 +2863,11 @@
         <v>-38.056201000000001</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2906,7 +2889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -2926,9 +2909,7 @@
         <v>83</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
-        <v>529</v>
-      </c>
+      <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
         <v>120</v>
       </c>
@@ -2961,11 +2942,11 @@
         <v>-38.056331</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2984,7 +2965,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -3001,12 +2982,10 @@
         <v>-38.056328999999998</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="5" t="s">
-        <v>530</v>
-      </c>
+      <c r="H13" s="5"/>
       <c r="I13" s="5" t="s">
         <v>78</v>
       </c>
@@ -3041,11 +3020,11 @@
         <v>-38.056373000000001</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -3067,7 +3046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -3084,11 +3063,11 @@
         <v>-38.056550999999999</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>531</v>
+        <v>648</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -3110,7 +3089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>137</v>
       </c>
@@ -3128,9 +3107,7 @@
         <v>83</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
-        <v>532</v>
-      </c>
+      <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
         <v>82</v>
       </c>
@@ -3165,13 +3142,13 @@
         <v>-38.056727000000002</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="G17" s="5">
         <v>1988</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -3193,7 +3170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>144</v>
       </c>
@@ -3210,12 +3187,10 @@
         <v>-38.056677999999998</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
-        <v>533</v>
-      </c>
+      <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
         <v>147</v>
       </c>
@@ -3233,11 +3208,13 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>653</v>
+      </c>
       <c r="C19" s="5" t="s">
         <v>150</v>
       </c>
@@ -3248,11 +3225,11 @@
         <v>-38.056843999999998</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>534</v>
+        <v>654</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -3271,7 +3248,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>153</v>
       </c>
@@ -3288,11 +3265,11 @@
         <v>-38.057062000000002</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>540</v>
+        <v>649</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -3311,7 +3288,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>158</v>
       </c>
@@ -3328,11 +3305,11 @@
         <v>-38.057076000000002</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>387</v>
+        <v>655</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>161</v>
@@ -3368,13 +3345,13 @@
         <v>-38.057192000000001</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="G22" s="5">
         <v>1990</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>387</v>
+        <v>650</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>166</v>
@@ -3410,11 +3387,11 @@
         <v>-38.056908999999997</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>171</v>
@@ -3441,7 +3418,7 @@
         <v>173</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>174</v>
@@ -3453,12 +3430,10 @@
         <v>-38.056840000000001</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G24" s="5"/>
-      <c r="H24" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H24" s="5"/>
       <c r="I24" s="5" t="s">
         <v>78</v>
       </c>
@@ -3476,12 +3451,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="58" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:19" ht="29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>176</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>127</v>
@@ -3493,12 +3468,10 @@
         <v>-38.056933999999998</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="G25" s="5"/>
-      <c r="H25" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H25" s="5"/>
       <c r="I25" s="5" t="s">
         <v>78</v>
       </c>
@@ -3516,7 +3489,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>178</v>
       </c>
@@ -3533,12 +3506,10 @@
         <v>-38.056655999999997</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H26" s="5"/>
       <c r="I26" s="5" t="s">
         <v>101</v>
       </c>
@@ -3556,7 +3527,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -3573,12 +3544,10 @@
         <v>-38.055928999999999</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H27" s="5"/>
       <c r="I27" s="5" t="s">
         <v>87</v>
       </c>
@@ -3599,7 +3568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>184</v>
       </c>
@@ -3616,12 +3585,10 @@
         <v>-38.056055999999998</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="G28" s="5"/>
-      <c r="H28" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
         <v>82</v>
       </c>
@@ -3639,7 +3606,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>189</v>
       </c>
@@ -3656,11 +3623,11 @@
         <v>-38.056057000000003</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>387</v>
+        <v>544</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>171</v>
@@ -3699,12 +3666,10 @@
         <v>-38.056168</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G30" s="5"/>
-      <c r="H30" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H30" s="5"/>
       <c r="I30" s="5" t="s">
         <v>194</v>
       </c>
@@ -3739,11 +3704,11 @@
         <v>-38.056126999999996</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>387</v>
+        <v>652</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>199</v>
@@ -3765,7 +3730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>201</v>
       </c>
@@ -3782,12 +3747,10 @@
         <v>-38.056092999999997</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="G32" s="5"/>
-      <c r="H32" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
         <v>204</v>
       </c>
@@ -3822,11 +3785,11 @@
         <v>-38.056373999999998</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>387</v>
+        <v>651</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>78</v>
@@ -3848,7 +3811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>210</v>
       </c>
@@ -3865,12 +3828,10 @@
         <v>-38.056545</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="G34" s="5"/>
-      <c r="H34" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="H34" s="5"/>
       <c r="I34" s="5" t="s">
         <v>213</v>
       </c>
@@ -3893,7 +3854,7 @@
         <v>215</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>216</v>
@@ -3901,7 +3862,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3928,7 +3889,7 @@
         <v>218</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>219</v>
@@ -3936,7 +3897,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3960,7 +3921,7 @@
         <v>221</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>222</v>
@@ -3968,7 +3929,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -3992,7 +3953,7 @@
         <v>224</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>225</v>
@@ -4000,7 +3961,7 @@
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -4024,7 +3985,7 @@
         <v>227</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>228</v>
@@ -4032,7 +3993,7 @@
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -4056,7 +4017,7 @@
         <v>231</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>232</v>
@@ -4064,7 +4025,7 @@
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -4088,7 +4049,7 @@
         <v>235</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>236</v>
@@ -4096,7 +4057,7 @@
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -4120,7 +4081,7 @@
         <v>239</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>240</v>
@@ -4128,11 +4089,11 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>171</v>
@@ -4157,7 +4118,7 @@
         <v>242</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>243</v>
@@ -4165,7 +4126,7 @@
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -4192,7 +4153,7 @@
         <v>245</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>131</v>
@@ -4204,7 +4165,7 @@
         <v>-38.055799999999998</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -4230,7 +4191,7 @@
         <v>247</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>135</v>
@@ -4242,7 +4203,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -4268,7 +4229,7 @@
         <v>250</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>251</v>
@@ -4280,7 +4241,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4306,7 +4267,7 @@
         <v>254</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>255</v>
@@ -4318,7 +4279,7 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -4344,7 +4305,7 @@
         <v>257</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>258</v>
@@ -4356,7 +4317,7 @@
         <v>-38.055639999999997</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4382,7 +4343,7 @@
         <v>260</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>258</v>
@@ -4394,7 +4355,7 @@
         <v>-38.055630000000001</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4420,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>263</v>
@@ -4432,7 +4393,7 @@
         <v>-38.055610000000001</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -4454,7 +4415,7 @@
         <v>265</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>266</v>
@@ -4466,7 +4427,7 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G51" s="5">
         <v>2002</v>
@@ -4497,7 +4458,7 @@
         <v>268</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>150</v>
@@ -4509,7 +4470,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4535,7 +4496,7 @@
         <v>271</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>272</v>
@@ -4547,7 +4508,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4573,7 +4534,7 @@
         <v>274</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>251</v>
@@ -4585,7 +4546,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4611,7 +4572,7 @@
         <v>276</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>277</v>
@@ -4623,7 +4584,7 @@
         <v>-38.055689999999998</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4649,7 +4610,7 @@
         <v>280</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>281</v>
@@ -4661,7 +4622,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4683,7 +4644,7 @@
         <v>283</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>284</v>
@@ -4695,7 +4656,7 @@
         <v>-38.05585</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4721,7 +4682,7 @@
         <v>286</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>287</v>
@@ -4733,7 +4694,7 @@
         <v>-38.055779999999999</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -4755,7 +4716,7 @@
         <v>289</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>290</v>
@@ -4767,7 +4728,7 @@
         <v>-38.055900000000001</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -4793,7 +4754,7 @@
         <v>293</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>131</v>
@@ -4805,7 +4766,7 @@
         <v>-38.055770000000003</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -4869,7 +4830,7 @@
         <v>297</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>290</v>
@@ -4881,7 +4842,7 @@
         <v>-38.055669999999999</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -4907,7 +4868,7 @@
         <v>299</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>300</v>
@@ -4919,7 +4880,7 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -4945,7 +4906,7 @@
         <v>302</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>258</v>
@@ -4957,7 +4918,7 @@
         <v>-38.055540000000001</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -4983,7 +4944,7 @@
         <v>304</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>263</v>
@@ -4995,7 +4956,7 @@
         <v>-38.055500000000002</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -5017,7 +4978,7 @@
         <v>306</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>307</v>
@@ -5029,7 +4990,7 @@
         <v>-38.055599999999998</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -5055,7 +5016,7 @@
         <v>310</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>272</v>
@@ -5067,7 +5028,7 @@
         <v>-38.055230000000002</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -5093,7 +5054,7 @@
         <v>312</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>277</v>
@@ -5105,7 +5066,7 @@
         <v>-38.055210000000002</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5131,7 +5092,7 @@
         <v>314</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>287</v>
@@ -5143,7 +5104,7 @@
         <v>-38.055079999999997</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5165,7 +5126,7 @@
         <v>316</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>317</v>
@@ -5177,7 +5138,7 @@
         <v>-38.055019999999999</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5203,7 +5164,7 @@
         <v>319</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>320</v>
@@ -5215,7 +5176,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5239,7 +5200,7 @@
         <v>322</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>323</v>
@@ -5251,7 +5212,7 @@
         <v>-38.055320000000002</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5277,7 +5238,7 @@
         <v>325</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>326</v>
@@ -5289,7 +5250,7 @@
         <v>-38.055289999999999</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5315,7 +5276,7 @@
         <v>330</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>331</v>
@@ -5327,7 +5288,7 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5353,7 +5314,7 @@
         <v>333</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>334</v>
@@ -5365,7 +5326,7 @@
         <v>-38.055660000000003</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5391,7 +5352,7 @@
         <v>336</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>263</v>
@@ -5403,7 +5364,7 @@
         <v>-38.055929999999996</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5425,7 +5386,7 @@
         <v>338</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>8</v>
@@ -5437,7 +5398,7 @@
         <v>-38.055999999999997</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5463,7 +5424,7 @@
         <v>341</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>123</v>
@@ -5475,7 +5436,7 @@
         <v>-38.056220000000003</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5501,7 +5462,7 @@
         <v>343</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>219</v>
@@ -5513,7 +5474,7 @@
         <v>-38.056489999999997</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5539,7 +5500,7 @@
         <v>346</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>347</v>
@@ -5551,7 +5512,7 @@
         <v>-38.056080000000001</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5577,7 +5538,7 @@
         <v>350</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>351</v>
@@ -5589,7 +5550,7 @@
         <v>-38.056100000000001</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5615,7 +5576,7 @@
         <v>353</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>323</v>
@@ -5627,7 +5588,7 @@
         <v>-38.05547</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5653,7 +5614,7 @@
         <v>355</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>356</v>
@@ -5665,7 +5626,7 @@
         <v>-38.05527</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5687,7 +5648,7 @@
         <v>358</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>236</v>
@@ -5699,7 +5660,7 @@
         <v>-38.054609999999997</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5725,7 +5686,7 @@
         <v>360</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>361</v>
@@ -5737,7 +5698,7 @@
         <v>-38.05491</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5763,7 +5724,7 @@
         <v>364</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>236</v>
@@ -5775,7 +5736,7 @@
         <v>-38.054940000000002</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5801,7 +5762,7 @@
         <v>366</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>236</v>
@@ -5813,7 +5774,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5839,7 +5800,7 @@
         <v>368</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>116</v>
@@ -5851,7 +5812,7 @@
         <v>-38.055059999999997</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5877,7 +5838,7 @@
         <v>370</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>116</v>
@@ -5889,7 +5850,7 @@
         <v>-38.055280000000003</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5915,7 +5876,7 @@
         <v>372</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>219</v>
@@ -5927,7 +5888,7 @@
         <v>-38.055250000000001</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -5953,7 +5914,7 @@
         <v>374</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>375</v>
@@ -5991,7 +5952,7 @@
         <v>377</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>378</v>
@@ -6003,7 +5964,7 @@
         <v>-38.055100000000003</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6072,7 +6033,7 @@
         <v>62</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
@@ -6081,7 +6042,7 @@
         <v>388</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>65</v>
@@ -6117,10 +6078,10 @@
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -6149,14 +6110,14 @@
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6179,10 +6140,10 @@
       <c r="K4" s="5"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6205,10 +6166,10 @@
       <c r="K5" s="5"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6237,10 +6198,10 @@
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6261,14 +6222,14 @@
       <c r="I7" s="9"/>
       <c r="J7" s="13"/>
       <c r="K7" s="5" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6297,10 +6258,10 @@
       <c r="K8" s="5"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6323,10 +6284,10 @@
       <c r="K9" s="5"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6353,14 +6314,14 @@
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="L10" s="9"/>
       <c r="M10" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6387,14 +6348,14 @@
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="L11" s="9"/>
       <c r="M11" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6417,10 +6378,10 @@
       <c r="K12" s="5"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6443,10 +6404,10 @@
       <c r="K13" s="5"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6469,10 +6430,10 @@
       <c r="K14" s="5"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6495,10 +6456,10 @@
       <c r="K15" s="5"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6521,10 +6482,10 @@
       <c r="K16" s="5"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6547,10 +6508,10 @@
       <c r="K17" s="5"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6581,10 +6542,10 @@
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6607,10 +6568,10 @@
       <c r="K19" s="5"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6633,10 +6594,10 @@
       <c r="K20" s="5"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6659,10 +6620,10 @@
       <c r="K21" s="5"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6689,14 +6650,14 @@
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="L22" s="9"/>
       <c r="M22" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6719,10 +6680,10 @@
       <c r="K23" s="5"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6745,10 +6706,10 @@
       <c r="K24" s="5"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6775,14 +6736,14 @@
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6805,10 +6766,10 @@
       <c r="K26" s="5"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -6835,14 +6796,14 @@
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="L27" s="9"/>
       <c r="M27" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6865,10 +6826,10 @@
       <c r="K28" s="5"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6891,10 +6852,10 @@
       <c r="K29" s="5"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6917,10 +6878,10 @@
       <c r="K30" s="5"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6943,10 +6904,10 @@
       <c r="K31" s="5"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6973,14 +6934,14 @@
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="L32" s="9"/>
       <c r="M32" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7003,10 +6964,10 @@
       <c r="K33" s="5"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7027,14 +6988,14 @@
       <c r="I34" s="9"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7057,10 +7018,10 @@
       <c r="K35" s="5"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7087,14 +7048,14 @@
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7117,10 +7078,10 @@
       <c r="K37" s="5"/>
       <c r="L37" s="9"/>
       <c r="M37" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7147,14 +7108,14 @@
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="L38" s="9"/>
       <c r="M38" s="9" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7177,10 +7138,10 @@
       <c r="K39" s="5"/>
       <c r="L39" s="9"/>
       <c r="M39" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7203,10 +7164,10 @@
       <c r="K40" s="5"/>
       <c r="L40" s="9"/>
       <c r="M40" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7233,14 +7194,14 @@
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="L41" s="9"/>
       <c r="M41" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7271,10 +7232,10 @@
       </c>
       <c r="L42" s="9"/>
       <c r="M42" s="9" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7297,10 +7258,10 @@
       <c r="K43" s="5"/>
       <c r="L43" s="9"/>
       <c r="M43" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7325,10 +7286,10 @@
       </c>
       <c r="L44" s="9"/>
       <c r="M44" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7351,10 +7312,10 @@
       <c r="K45" s="5"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -7381,14 +7342,14 @@
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="9" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7411,10 +7372,10 @@
       <c r="K47" s="5"/>
       <c r="L47" s="9"/>
       <c r="M47" s="9" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -7740,7 +7701,7 @@
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -7763,7 +7724,7 @@
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>47</v>
@@ -7786,7 +7747,7 @@
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>49</v>
@@ -7809,10 +7770,10 @@
         <v>-38.056685000000002</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -7820,7 +7781,7 @@
         <v>383</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>386</v>
@@ -7832,7 +7793,7 @@
         <v>-38.056984999999997</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7840,7 +7801,7 @@
         <v>384</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>385</v>
@@ -7852,7 +7813,7 @@
         <v>-38.055428999999997</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043A9A98-5F86-40C9-8D8B-FDF7951D0BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06621212-366A-4D55-8AAA-39DF8E71FA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1999,9 +1999,6 @@
     <t>Cedrojapones.jpg</t>
   </si>
   <si>
-    <t>Castañodeindias.jpg</t>
-  </si>
-  <si>
     <t>Crataegus</t>
   </si>
   <si>
@@ -2009,6 +2006,9 @@
   </si>
   <si>
     <t>Platanus.jpg</t>
+  </si>
+  <si>
+    <t>Castanodeindias.jpg</t>
   </si>
 </sst>
 </file>
@@ -3213,7 +3213,7 @@
         <v>149</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>150</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>161</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>199</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06621212-366A-4D55-8AAA-39DF8E71FA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5252B67E-E03C-4B9B-A89B-359D9B240616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="663">
   <si>
     <t>id</t>
   </si>
@@ -1672,9 +1672,6 @@
     <t>Fuente.JPG</t>
   </si>
   <si>
-    <t>Cedrodecrista.jpg</t>
-  </si>
-  <si>
     <t>Araucaria.jpg</t>
   </si>
   <si>
@@ -1996,6 +1993,9 @@
     <t>Tilo.jpg</t>
   </si>
   <si>
+    <t>Liquidambar.jpg</t>
+  </si>
+  <si>
     <t>Cedrojapones.jpg</t>
   </si>
   <si>
@@ -2009,13 +2009,34 @@
   </si>
   <si>
     <t>Castanodeindias.jpg</t>
+  </si>
+  <si>
+    <t>Pinoinsignia.jpg</t>
+  </si>
+  <si>
+    <t>Sequoiaroja.jpg</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>Visita Botanicas</t>
+  </si>
+  <si>
+    <t>Visitas</t>
+  </si>
+  <si>
+    <t>Visitasbotanicas.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una de las atracciones </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2036,12 +2057,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="6"/>
-      <color rgb="FF007B8B"/>
-      <name val="Roboto"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2124,7 +2139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2141,32 +2156,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2539,7 +2553,7 @@
         <v>-38.056790999999997</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G2" s="5">
         <v>2004</v>
@@ -2587,7 +2601,7 @@
         <v>-38.056471999999999</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -2625,11 +2639,11 @@
         <v>-38.056541000000003</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2668,11 +2682,11 @@
         <v>-38.056569000000003</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2710,7 +2724,7 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2749,7 +2763,7 @@
         <v>-38.056437000000003</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -2787,7 +2801,7 @@
         <v>-38.056372000000003</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -2825,7 +2839,7 @@
         <v>-38.056238999999998</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -2863,11 +2877,11 @@
         <v>-38.056201000000001</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2942,11 +2956,11 @@
         <v>-38.056331</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2982,7 +2996,7 @@
         <v>-38.056328999999998</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -3020,11 +3034,11 @@
         <v>-38.056373000000001</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -3063,11 +3077,11 @@
         <v>-38.056550999999999</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -3142,13 +3156,13 @@
         <v>-38.056727000000002</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G17" s="5">
         <v>1988</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -3187,7 +3201,7 @@
         <v>-38.056677999999998</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -3225,7 +3239,7 @@
         <v>-38.056843999999998</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
@@ -3265,11 +3279,11 @@
         <v>-38.057062000000002</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -3305,7 +3319,7 @@
         <v>-38.057076000000002</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
@@ -3345,13 +3359,13 @@
         <v>-38.057192000000001</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G22" s="5">
         <v>1990</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>166</v>
@@ -3387,11 +3401,11 @@
         <v>-38.056908999999997</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>171</v>
@@ -3417,8 +3431,8 @@
       <c r="A24" t="s">
         <v>173</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>566</v>
+      <c r="B24" s="13" t="s">
+        <v>565</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>174</v>
@@ -3430,7 +3444,7 @@
         <v>-38.056840000000001</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -3455,8 +3469,8 @@
       <c r="A25" t="s">
         <v>176</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>556</v>
+      <c r="B25" s="14" t="s">
+        <v>555</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>127</v>
@@ -3468,7 +3482,7 @@
         <v>-38.056933999999998</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -3506,7 +3520,7 @@
         <v>-38.056655999999997</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -3544,7 +3558,7 @@
         <v>-38.055928999999999</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -3585,7 +3599,7 @@
         <v>-38.056055999999998</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -3623,11 +3637,11 @@
         <v>-38.056057000000003</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>171</v>
@@ -3666,7 +3680,7 @@
         <v>-38.056168</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -3704,7 +3718,7 @@
         <v>-38.056126999999996</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
@@ -3747,7 +3761,7 @@
         <v>-38.056092999999997</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -3785,7 +3799,7 @@
         <v>-38.056373999999998</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
@@ -3828,7 +3842,7 @@
         <v>-38.056545</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -3854,7 +3868,7 @@
         <v>215</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>216</v>
@@ -3862,10 +3876,12 @@
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="H35" s="5" t="s">
+        <v>657</v>
+      </c>
       <c r="I35" s="5" t="s">
         <v>78</v>
       </c>
@@ -3889,7 +3905,7 @@
         <v>218</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>219</v>
@@ -3897,7 +3913,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3921,7 +3937,7 @@
         <v>221</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>222</v>
@@ -3929,7 +3945,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -3953,7 +3969,7 @@
         <v>224</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>225</v>
@@ -3961,7 +3977,7 @@
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -3985,7 +4001,7 @@
         <v>227</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>228</v>
@@ -3993,7 +4009,7 @@
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -4017,7 +4033,7 @@
         <v>231</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>232</v>
@@ -4025,7 +4041,7 @@
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -4049,7 +4065,7 @@
         <v>235</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>236</v>
@@ -4057,7 +4073,7 @@
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -4076,12 +4092,12 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>239</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>240</v>
@@ -4089,11 +4105,11 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>171</v>
@@ -4113,12 +4129,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>242</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>243</v>
@@ -4126,7 +4142,7 @@
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -4153,7 +4169,7 @@
         <v>245</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>131</v>
@@ -4165,7 +4181,7 @@
         <v>-38.055799999999998</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -4191,7 +4207,7 @@
         <v>247</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>135</v>
@@ -4203,7 +4219,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -4229,7 +4245,7 @@
         <v>250</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>251</v>
@@ -4241,7 +4257,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4267,7 +4283,7 @@
         <v>254</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>255</v>
@@ -4279,7 +4295,7 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -4305,7 +4321,7 @@
         <v>257</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>258</v>
@@ -4317,7 +4333,7 @@
         <v>-38.055639999999997</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4343,7 +4359,7 @@
         <v>260</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>258</v>
@@ -4355,7 +4371,7 @@
         <v>-38.055630000000001</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4381,7 +4397,7 @@
         <v>262</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>263</v>
@@ -4393,7 +4409,7 @@
         <v>-38.055610000000001</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -4415,7 +4431,7 @@
         <v>265</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>266</v>
@@ -4427,7 +4443,7 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G51" s="5">
         <v>2002</v>
@@ -4458,7 +4474,7 @@
         <v>268</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>150</v>
@@ -4470,7 +4486,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4496,7 +4512,7 @@
         <v>271</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>272</v>
@@ -4508,7 +4524,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4534,7 +4550,7 @@
         <v>274</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>251</v>
@@ -4546,7 +4562,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4572,7 +4588,7 @@
         <v>276</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>277</v>
@@ -4584,7 +4600,7 @@
         <v>-38.055689999999998</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4610,7 +4626,7 @@
         <v>280</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>281</v>
@@ -4622,7 +4638,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4644,7 +4660,7 @@
         <v>283</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>284</v>
@@ -4656,7 +4672,7 @@
         <v>-38.05585</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4682,7 +4698,7 @@
         <v>286</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>287</v>
@@ -4694,7 +4710,7 @@
         <v>-38.055779999999999</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -4716,7 +4732,7 @@
         <v>289</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>290</v>
@@ -4728,7 +4744,7 @@
         <v>-38.055900000000001</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -4754,7 +4770,7 @@
         <v>293</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>131</v>
@@ -4766,7 +4782,7 @@
         <v>-38.055770000000003</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -4830,7 +4846,7 @@
         <v>297</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>290</v>
@@ -4842,7 +4858,7 @@
         <v>-38.055669999999999</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -4863,12 +4879,12 @@
         <v>298</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>299</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>300</v>
@@ -4880,10 +4896,12 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
+      <c r="H63" s="5" t="s">
+        <v>650</v>
+      </c>
       <c r="I63" s="5" t="s">
         <v>213</v>
       </c>
@@ -4906,7 +4924,7 @@
         <v>302</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>258</v>
@@ -4918,7 +4936,7 @@
         <v>-38.055540000000001</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -4944,7 +4962,7 @@
         <v>304</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>263</v>
@@ -4956,7 +4974,7 @@
         <v>-38.055500000000002</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -4978,7 +4996,7 @@
         <v>306</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>307</v>
@@ -4990,7 +5008,7 @@
         <v>-38.055599999999998</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -5016,7 +5034,7 @@
         <v>310</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>272</v>
@@ -5028,7 +5046,7 @@
         <v>-38.055230000000002</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -5054,7 +5072,7 @@
         <v>312</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>277</v>
@@ -5066,7 +5084,7 @@
         <v>-38.055210000000002</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5092,7 +5110,7 @@
         <v>314</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>287</v>
@@ -5104,7 +5122,7 @@
         <v>-38.055079999999997</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5126,7 +5144,7 @@
         <v>316</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>317</v>
@@ -5138,7 +5156,7 @@
         <v>-38.055019999999999</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5164,7 +5182,7 @@
         <v>319</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>320</v>
@@ -5176,7 +5194,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5200,7 +5218,7 @@
         <v>322</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>323</v>
@@ -5212,10 +5230,12 @@
         <v>-38.055320000000002</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
+      <c r="H72" s="5" t="s">
+        <v>656</v>
+      </c>
       <c r="I72" s="5" t="s">
         <v>82</v>
       </c>
@@ -5238,7 +5258,7 @@
         <v>325</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>326</v>
@@ -5250,7 +5270,7 @@
         <v>-38.055289999999999</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5276,7 +5296,7 @@
         <v>330</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>331</v>
@@ -5288,7 +5308,7 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5314,7 +5334,7 @@
         <v>333</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>334</v>
@@ -5326,7 +5346,7 @@
         <v>-38.055660000000003</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5352,7 +5372,7 @@
         <v>336</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>263</v>
@@ -5364,7 +5384,7 @@
         <v>-38.055929999999996</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5386,7 +5406,7 @@
         <v>338</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>8</v>
@@ -5398,7 +5418,7 @@
         <v>-38.055999999999997</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5424,7 +5444,7 @@
         <v>341</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>123</v>
@@ -5436,7 +5456,7 @@
         <v>-38.056220000000003</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5462,7 +5482,7 @@
         <v>343</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>219</v>
@@ -5474,7 +5494,7 @@
         <v>-38.056489999999997</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5500,7 +5520,7 @@
         <v>346</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>347</v>
@@ -5512,7 +5532,7 @@
         <v>-38.056080000000001</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5538,7 +5558,7 @@
         <v>350</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>351</v>
@@ -5550,7 +5570,7 @@
         <v>-38.056100000000001</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5576,7 +5596,7 @@
         <v>353</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>323</v>
@@ -5588,7 +5608,7 @@
         <v>-38.05547</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5614,7 +5634,7 @@
         <v>355</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>356</v>
@@ -5626,7 +5646,7 @@
         <v>-38.05527</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5648,7 +5668,7 @@
         <v>358</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>236</v>
@@ -5660,7 +5680,7 @@
         <v>-38.054609999999997</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5686,7 +5706,7 @@
         <v>360</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>361</v>
@@ -5698,7 +5718,7 @@
         <v>-38.05491</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5724,7 +5744,7 @@
         <v>364</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>236</v>
@@ -5736,7 +5756,7 @@
         <v>-38.054940000000002</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5762,7 +5782,7 @@
         <v>366</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>236</v>
@@ -5774,7 +5794,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5800,7 +5820,7 @@
         <v>368</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>116</v>
@@ -5812,7 +5832,7 @@
         <v>-38.055059999999997</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5838,7 +5858,7 @@
         <v>370</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>116</v>
@@ -5850,7 +5870,7 @@
         <v>-38.055280000000003</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5876,7 +5896,7 @@
         <v>372</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>219</v>
@@ -5888,7 +5908,7 @@
         <v>-38.055250000000001</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -5914,7 +5934,7 @@
         <v>374</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>375</v>
@@ -5952,7 +5972,7 @@
         <v>377</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>378</v>
@@ -5964,7 +5984,7 @@
         <v>-38.055100000000003</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6005,1377 +6025,1377 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>528</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="M1" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>-57.680154000000002</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <v>-38.056790999999997</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>46242</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
       <c r="J2" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9" t="s">
+      <c r="L2" s="8"/>
+      <c r="M2" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="3" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>-57.680520999999999</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>-38.056471999999999</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>46242</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
       <c r="J3" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9" t="s">
+      <c r="L3" s="8"/>
+      <c r="M3" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N3" s="9" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>629</v>
-      </c>
-    </row>
     <row r="6" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>-57.678601</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>-38.056950999999998</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="13"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9" t="s">
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N6" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N6" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="7" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="13"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9" t="s">
+      <c r="L7" s="8"/>
+      <c r="M7" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N7" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>-57.680219000000001</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>-38.057253000000003</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
       <c r="J8" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9" t="s">
+      <c r="L8" s="8"/>
+      <c r="M8" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N8" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="9" spans="1:14" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9" t="s">
+      <c r="L9" s="8"/>
+      <c r="M9" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>631</v>
-      </c>
     </row>
     <row r="10" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>-57.679960999999999</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>-38.055588999999998</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
       <c r="J10" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9" t="s">
+      <c r="L10" s="8"/>
+      <c r="M10" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N10" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N10" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="11" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>-57.681131000000001</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>-38.055318</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
       <c r="J11" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9" t="s">
+      <c r="L11" s="8"/>
+      <c r="M11" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N11" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9" t="s">
+      <c r="L12" s="8"/>
+      <c r="M12" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N12" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N12" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9" t="s">
+      <c r="L13" s="8"/>
+      <c r="M13" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="N13" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="N13" s="9" t="s">
-        <v>633</v>
-      </c>
     </row>
     <row r="14" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9" t="s">
+      <c r="L14" s="8"/>
+      <c r="M14" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="N14" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="N14" s="9" t="s">
-        <v>635</v>
-      </c>
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9" t="s">
+      <c r="L15" s="8"/>
+      <c r="M15" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N15" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N15" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9" t="s">
+      <c r="L16" s="8"/>
+      <c r="M16" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N16" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="17" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>628</v>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>-57.683276999999997</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>-38.053451000000003</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
       <c r="J18" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9" t="s">
+      <c r="L18" s="8"/>
+      <c r="M18" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N18" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9" t="s">
+      <c r="L19" s="8"/>
+      <c r="M19" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N19" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N19" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="20" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9" t="s">
+      <c r="L20" s="8"/>
+      <c r="M20" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="N20" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="N20" s="9" t="s">
-        <v>635</v>
-      </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9" t="s">
+      <c r="L21" s="8"/>
+      <c r="M21" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="N21" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="N21" s="9" t="s">
-        <v>635</v>
-      </c>
     </row>
     <row r="22" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>-57.682054000000001</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <v>-38.055081999999999</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
       <c r="J22" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9" t="s">
+      <c r="L22" s="8"/>
+      <c r="M22" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N22" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N22" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9" t="s">
+      <c r="L23" s="8"/>
+      <c r="M23" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N23" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9" t="s">
+      <c r="L24" s="8"/>
+      <c r="M24" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N24" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N24" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="25" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <v>-57.679361</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="8">
         <v>-38.057346000000003</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
       <c r="J25" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9" t="s">
+      <c r="L25" s="8"/>
+      <c r="M25" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N25" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N25" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9" t="s">
+      <c r="L26" s="8"/>
+      <c r="M26" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N26" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="27" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>-57.684317</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <v>-38.055689999999998</v>
       </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
       <c r="J27" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9" t="s">
+      <c r="L27" s="8"/>
+      <c r="M27" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N27" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N27" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="28" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9" t="s">
+      <c r="L28" s="8"/>
+      <c r="M28" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N28" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N28" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9" t="s">
+      <c r="L29" s="8"/>
+      <c r="M29" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N29" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N29" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9" t="s">
+      <c r="L30" s="8"/>
+      <c r="M30" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N30" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N30" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9" t="s">
+      <c r="L31" s="8"/>
+      <c r="M31" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N31" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N31" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="32" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>-57.682547</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="8">
         <v>-38.057102999999998</v>
       </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
       <c r="J32" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9" t="s">
+      <c r="L32" s="8"/>
+      <c r="M32" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N32" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N32" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="33" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9" t="s">
+      <c r="L33" s="8"/>
+      <c r="M33" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="N33" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="N33" s="9" t="s">
-        <v>635</v>
-      </c>
     </row>
     <row r="34" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9" t="s">
+      <c r="L34" s="8"/>
+      <c r="M34" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N34" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N34" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="35" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9" t="s">
+      <c r="L35" s="8"/>
+      <c r="M35" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N35" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N35" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="36" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>-57.682281000000003</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="8">
         <v>-38.057195999999998</v>
       </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
       <c r="J36" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9" t="s">
+      <c r="L36" s="8"/>
+      <c r="M36" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N36" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N36" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="37" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9" t="s">
+      <c r="L37" s="8"/>
+      <c r="M37" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N37" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N37" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="38" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>-57.685510999999998</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="8">
         <v>-38.054340000000003</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
       <c r="J38" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9" t="s">
+      <c r="L38" s="8"/>
+      <c r="M38" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="N38" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="N38" s="9" t="s">
-        <v>635</v>
-      </c>
     </row>
     <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9" t="s">
+      <c r="L39" s="8"/>
+      <c r="M39" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N39" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N39" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="40" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9" t="s">
+      <c r="L40" s="8"/>
+      <c r="M40" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N40" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N40" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="41" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>-57.681240000000003</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="8">
         <v>-38.055633</v>
       </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
       <c r="J41" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9" t="s">
+      <c r="L41" s="8"/>
+      <c r="M41" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N41" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N41" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="42" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="9" t="s">
         <v>513</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>-57.683684</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="8">
         <v>-38.054684999999999</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
       <c r="J42" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>637</v>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9" t="s">
+      <c r="L43" s="8"/>
+      <c r="M43" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N43" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N43" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="44" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9" t="s">
+      <c r="L44" s="8"/>
+      <c r="M44" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N44" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N44" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9" t="s">
+      <c r="L45" s="8"/>
+      <c r="M45" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N45" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N45" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="46" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>-57.682558</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="8">
         <v>-38.055816999999998</v>
       </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
       <c r="J46" s="5" t="s">
         <v>387</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9" t="s">
+      <c r="L46" s="8"/>
+      <c r="M46" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="N46" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N46" s="9" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="47" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="13"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="12"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9" t="s">
+      <c r="L47" s="8"/>
+      <c r="M47" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="N47" s="8" t="s">
         <v>638</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -7694,14 +7714,14 @@
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>-57.683934999999998</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>-38.056013999999998</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -7717,10 +7737,10 @@
       <c r="C3" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>-57.679949999999998</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>-38.056936999999998</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -7740,14 +7760,14 @@
       <c r="C4" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>-57.680886000000001</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>-38.056910999999999</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>49</v>
@@ -7763,17 +7783,17 @@
       <c r="C5" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>-57.680562999999999</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>-38.056685000000002</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -7781,19 +7801,19 @@
         <v>383</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>-57.680033999999999</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>-38.056984999999997</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7801,28 +7821,48 @@
         <v>384</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>-57.683433999999998</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>-38.055428999999997</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="A8" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-57.679726000000002</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-38.055993000000001</v>
+      </c>
+      <c r="F8" t="s">
+        <v>661</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>662</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5252B67E-E03C-4B9B-A89B-359D9B240616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61229F68-AB47-41DF-A990-55E8E03BDBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Árboles" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="677">
   <si>
     <t>id</t>
   </si>
@@ -1693,9 +1693,6 @@
     <t>Bosque de Eucaliptos</t>
   </si>
   <si>
-    <t>Bosquedeeucaliptus.jpg</t>
-  </si>
-  <si>
     <t>América del Norte</t>
   </si>
   <si>
@@ -2029,7 +2026,52 @@
     <t>Visitasbotanicas.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Una de las atracciones </t>
+    <t>Bosquedeeucaliptus2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una de las principales actividades abiertas a la comunidad. </t>
+  </si>
+  <si>
+    <t>roblecomun</t>
+  </si>
+  <si>
+    <t>cedrodelhimalaya</t>
+  </si>
+  <si>
+    <t>cedroazul</t>
+  </si>
+  <si>
+    <t>roblerojo</t>
+  </si>
+  <si>
+    <t>abeto</t>
+  </si>
+  <si>
+    <t>limpiatubos</t>
+  </si>
+  <si>
+    <t>araucariaaustraliana</t>
+  </si>
+  <si>
+    <t>encina</t>
+  </si>
+  <si>
+    <t>castanodeindias</t>
+  </si>
+  <si>
+    <t>cedrojapones</t>
+  </si>
+  <si>
+    <t>secuoiaroja</t>
+  </si>
+  <si>
+    <t>damara</t>
+  </si>
+  <si>
+    <t>arboldelostulipanes</t>
+  </si>
+  <si>
+    <t>gingko</t>
   </si>
 </sst>
 </file>
@@ -2553,7 +2595,7 @@
         <v>-38.056790999999997</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G2" s="5">
         <v>2004</v>
@@ -2601,7 +2643,7 @@
         <v>-38.056471999999999</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -2639,11 +2681,11 @@
         <v>-38.056541000000003</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>87</v>
@@ -2664,6 +2706,9 @@
       <c r="S4">
         <v>1</v>
       </c>
+      <c r="T4" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -2682,11 +2727,11 @@
         <v>-38.056569000000003</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
@@ -2724,7 +2769,7 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>82</v>
@@ -2745,6 +2790,9 @@
       <c r="S6">
         <v>1</v>
       </c>
+      <c r="T6" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -2763,7 +2811,7 @@
         <v>-38.056437000000003</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -2801,7 +2849,7 @@
         <v>-38.056372000000003</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -2839,7 +2887,7 @@
         <v>-38.056238999999998</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -2877,11 +2925,11 @@
         <v>-38.056201000000001</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>82</v>
@@ -2902,6 +2950,9 @@
       <c r="S10">
         <v>1</v>
       </c>
+      <c r="T10" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -2956,11 +3007,11 @@
         <v>-38.056331</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>120</v>
@@ -2996,7 +3047,7 @@
         <v>-38.056328999999998</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -3034,11 +3085,11 @@
         <v>-38.056373000000001</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>87</v>
@@ -3059,6 +3110,9 @@
       <c r="S14">
         <v>1</v>
       </c>
+      <c r="T14" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -3077,11 +3131,11 @@
         <v>-38.056550999999999</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>82</v>
@@ -3102,6 +3156,9 @@
       <c r="S15">
         <v>1</v>
       </c>
+      <c r="T15" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -3139,7 +3196,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -3156,13 +3213,13 @@
         <v>-38.056727000000002</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G17" s="5">
         <v>1988</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
@@ -3183,8 +3240,11 @@
       <c r="S17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="T17" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>144</v>
       </c>
@@ -3201,7 +3261,7 @@
         <v>-38.056677999999998</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -3222,12 +3282,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>149</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>150</v>
@@ -3239,11 +3299,11 @@
         <v>-38.056843999999998</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>151</v>
@@ -3262,7 +3322,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>153</v>
       </c>
@@ -3279,11 +3339,11 @@
         <v>-38.057062000000002</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>156</v>
@@ -3302,7 +3362,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>158</v>
       </c>
@@ -3319,11 +3379,11 @@
         <v>-38.057076000000002</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>161</v>
@@ -3342,7 +3402,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>163</v>
       </c>
@@ -3359,13 +3419,13 @@
         <v>-38.057192000000001</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G22" s="5">
         <v>1990</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>166</v>
@@ -3384,7 +3444,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -3401,7 +3461,7 @@
         <v>-38.056908999999997</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
@@ -3426,13 +3486,16 @@
       <c r="S23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" ht="29" x14ac:dyDescent="0.45">
+      <c r="T23" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>173</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>174</v>
@@ -3444,7 +3507,7 @@
         <v>-38.056840000000001</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -3465,12 +3528,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="29" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:20" ht="29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>176</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>127</v>
@@ -3482,7 +3545,7 @@
         <v>-38.056933999999998</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -3503,7 +3566,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>178</v>
       </c>
@@ -3520,7 +3583,7 @@
         <v>-38.056655999999997</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -3541,7 +3604,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -3558,7 +3621,7 @@
         <v>-38.055928999999999</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -3581,8 +3644,11 @@
       <c r="S27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="T27" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>184</v>
       </c>
@@ -3599,7 +3665,7 @@
         <v>-38.056055999999998</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -3620,7 +3686,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>189</v>
       </c>
@@ -3637,7 +3703,7 @@
         <v>-38.056057000000003</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
@@ -3659,11 +3725,11 @@
       <c r="R29" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="S29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="T29" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>191</v>
       </c>
@@ -3680,7 +3746,7 @@
         <v>-38.056168</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -3701,7 +3767,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>196</v>
       </c>
@@ -3718,11 +3784,11 @@
         <v>-38.056126999999996</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>199</v>
@@ -3743,8 +3809,11 @@
       <c r="S31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T31" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>201</v>
       </c>
@@ -3761,7 +3830,7 @@
         <v>-38.056092999999997</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -3782,7 +3851,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>206</v>
       </c>
@@ -3799,11 +3868,11 @@
         <v>-38.056373999999998</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>78</v>
@@ -3824,8 +3893,11 @@
       <c r="S33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="T33" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>210</v>
       </c>
@@ -3842,7 +3914,7 @@
         <v>-38.056545</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -3863,12 +3935,12 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>215</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>216</v>
@@ -3876,11 +3948,11 @@
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>78</v>
@@ -3899,13 +3971,16 @@
       <c r="S35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="T35" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>218</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>219</v>
@@ -3913,7 +3988,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3932,12 +4007,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>221</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>222</v>
@@ -3945,7 +4020,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -3964,12 +4039,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>224</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>225</v>
@@ -3977,7 +4052,7 @@
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -3996,12 +4071,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>227</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>228</v>
@@ -4009,7 +4084,7 @@
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -4028,12 +4103,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>231</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>232</v>
@@ -4041,7 +4116,7 @@
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -4060,12 +4135,12 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>235</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>236</v>
@@ -4073,7 +4148,7 @@
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -4092,12 +4167,12 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>239</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>240</v>
@@ -4105,7 +4180,7 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
@@ -4128,13 +4203,16 @@
       <c r="S42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T42" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>242</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>243</v>
@@ -4142,7 +4220,7 @@
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -4163,13 +4241,16 @@
       <c r="S43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="T43" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>245</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>131</v>
@@ -4181,7 +4262,7 @@
         <v>-38.055799999999998</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -4202,12 +4283,12 @@
         <v>246</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>247</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>135</v>
@@ -4219,7 +4300,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -4240,12 +4321,12 @@
         <v>249</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>250</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>251</v>
@@ -4257,7 +4338,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4278,12 +4359,12 @@
         <v>253</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>254</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>255</v>
@@ -4295,7 +4376,7 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -4316,12 +4397,12 @@
         <v>256</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>257</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>258</v>
@@ -4333,7 +4414,7 @@
         <v>-38.055639999999997</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4354,12 +4435,12 @@
         <v>259</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>260</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>258</v>
@@ -4371,7 +4452,7 @@
         <v>-38.055630000000001</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4392,12 +4473,12 @@
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>262</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>263</v>
@@ -4409,7 +4490,7 @@
         <v>-38.055610000000001</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -4426,12 +4507,12 @@
         <v>264</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>265</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>266</v>
@@ -4443,7 +4524,7 @@
         <v>-38.055759999999999</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G51" s="5">
         <v>2002</v>
@@ -4468,13 +4549,16 @@
       <c r="S51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+      <c r="T51" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>268</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>150</v>
@@ -4486,7 +4570,7 @@
         <v>-38.055729999999997</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4507,12 +4591,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>271</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>272</v>
@@ -4524,7 +4608,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4545,12 +4629,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>274</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>251</v>
@@ -4562,7 +4646,7 @@
         <v>-38.05574</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4583,12 +4667,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>276</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>277</v>
@@ -4600,7 +4684,7 @@
         <v>-38.055689999999998</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4621,12 +4705,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>280</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>281</v>
@@ -4638,7 +4722,7 @@
         <v>-38.055720000000001</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4655,12 +4739,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>283</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>284</v>
@@ -4672,7 +4756,7 @@
         <v>-38.05585</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4693,12 +4777,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>286</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>287</v>
@@ -4710,7 +4794,7 @@
         <v>-38.055779999999999</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -4727,12 +4811,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>289</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>290</v>
@@ -4744,7 +4828,7 @@
         <v>-38.055900000000001</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -4765,12 +4849,12 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>293</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>131</v>
@@ -4782,7 +4866,7 @@
         <v>-38.055770000000003</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -4803,7 +4887,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>295</v>
       </c>
@@ -4841,12 +4925,12 @@
         <v>296</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>297</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>290</v>
@@ -4858,7 +4942,7 @@
         <v>-38.055669999999999</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -4879,12 +4963,12 @@
         <v>298</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>299</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>300</v>
@@ -4896,11 +4980,11 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>213</v>
@@ -4919,12 +5003,12 @@
         <v>301</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>302</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>258</v>
@@ -4936,7 +5020,7 @@
         <v>-38.055540000000001</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -4962,7 +5046,7 @@
         <v>304</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>263</v>
@@ -4974,7 +5058,7 @@
         <v>-38.055500000000002</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -4996,7 +5080,7 @@
         <v>306</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>307</v>
@@ -5008,7 +5092,7 @@
         <v>-38.055599999999998</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -5034,7 +5118,7 @@
         <v>310</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>272</v>
@@ -5046,7 +5130,7 @@
         <v>-38.055230000000002</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -5072,7 +5156,7 @@
         <v>312</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>277</v>
@@ -5084,7 +5168,7 @@
         <v>-38.055210000000002</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5110,7 +5194,7 @@
         <v>314</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>287</v>
@@ -5122,7 +5206,7 @@
         <v>-38.055079999999997</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5144,7 +5228,7 @@
         <v>316</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>317</v>
@@ -5156,7 +5240,7 @@
         <v>-38.055019999999999</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5182,7 +5266,7 @@
         <v>319</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>320</v>
@@ -5194,7 +5278,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5218,7 +5302,7 @@
         <v>322</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>323</v>
@@ -5230,11 +5314,11 @@
         <v>-38.055320000000002</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>82</v>
@@ -5258,7 +5342,7 @@
         <v>325</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>326</v>
@@ -5270,7 +5354,7 @@
         <v>-38.055289999999999</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5296,7 +5380,7 @@
         <v>330</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>331</v>
@@ -5308,7 +5392,7 @@
         <v>-38.055529999999997</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5334,7 +5418,7 @@
         <v>333</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>334</v>
@@ -5346,7 +5430,7 @@
         <v>-38.055660000000003</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5372,7 +5456,7 @@
         <v>336</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>263</v>
@@ -5384,7 +5468,7 @@
         <v>-38.055929999999996</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5406,7 +5490,7 @@
         <v>338</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>8</v>
@@ -5418,7 +5502,7 @@
         <v>-38.055999999999997</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5444,7 +5528,7 @@
         <v>341</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>123</v>
@@ -5456,7 +5540,7 @@
         <v>-38.056220000000003</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5482,7 +5566,7 @@
         <v>343</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>219</v>
@@ -5494,7 +5578,7 @@
         <v>-38.056489999999997</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5520,7 +5604,7 @@
         <v>346</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>347</v>
@@ -5532,7 +5616,7 @@
         <v>-38.056080000000001</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5558,7 +5642,7 @@
         <v>350</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>351</v>
@@ -5570,7 +5654,7 @@
         <v>-38.056100000000001</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5596,7 +5680,7 @@
         <v>353</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>323</v>
@@ -5608,7 +5692,7 @@
         <v>-38.05547</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5634,7 +5718,7 @@
         <v>355</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>356</v>
@@ -5646,7 +5730,7 @@
         <v>-38.05527</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5668,7 +5752,7 @@
         <v>358</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>236</v>
@@ -5680,7 +5764,7 @@
         <v>-38.054609999999997</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5706,7 +5790,7 @@
         <v>360</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>361</v>
@@ -5718,7 +5802,7 @@
         <v>-38.05491</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5744,7 +5828,7 @@
         <v>364</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>236</v>
@@ -5756,7 +5840,7 @@
         <v>-38.054940000000002</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5782,7 +5866,7 @@
         <v>366</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>236</v>
@@ -5794,7 +5878,7 @@
         <v>-38.055030000000002</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5820,7 +5904,7 @@
         <v>368</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>116</v>
@@ -5832,7 +5916,7 @@
         <v>-38.055059999999997</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5858,7 +5942,7 @@
         <v>370</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>116</v>
@@ -5870,7 +5954,7 @@
         <v>-38.055280000000003</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5896,7 +5980,7 @@
         <v>372</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>219</v>
@@ -5908,7 +5992,7 @@
         <v>-38.055250000000001</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -5934,7 +6018,7 @@
         <v>374</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>375</v>
@@ -5972,7 +6056,7 @@
         <v>377</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>378</v>
@@ -5984,7 +6068,7 @@
         <v>-38.055100000000003</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6062,7 +6146,7 @@
         <v>388</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>65</v>
@@ -6098,10 +6182,10 @@
       </c>
       <c r="L2" s="8"/>
       <c r="M2" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -6134,10 +6218,10 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6160,10 +6244,10 @@
       <c r="K4" s="5"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6186,10 +6270,10 @@
       <c r="K5" s="5"/>
       <c r="L5" s="8"/>
       <c r="M5" s="8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6218,10 +6302,10 @@
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N6" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6246,10 +6330,10 @@
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6278,10 +6362,10 @@
       <c r="K8" s="5"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N8" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6304,10 +6388,10 @@
       <c r="K9" s="5"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>629</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6338,10 +6422,10 @@
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N10" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6372,10 +6456,10 @@
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N11" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6398,10 +6482,10 @@
       <c r="K12" s="5"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N12" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6424,10 +6508,10 @@
       <c r="K13" s="5"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="N13" s="8" t="s">
         <v>631</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6450,10 +6534,10 @@
       <c r="K14" s="5"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="N14" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6476,10 +6560,10 @@
       <c r="K15" s="5"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N15" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6502,10 +6586,10 @@
       <c r="K16" s="5"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N16" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6528,10 +6612,10 @@
       <c r="K17" s="5"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6562,10 +6646,10 @@
       </c>
       <c r="L18" s="8"/>
       <c r="M18" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6588,10 +6672,10 @@
       <c r="K19" s="5"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N19" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6614,10 +6698,10 @@
       <c r="K20" s="5"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="N20" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6640,10 +6724,10 @@
       <c r="K21" s="5"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="N21" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6674,10 +6758,10 @@
       </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N22" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6700,10 +6784,10 @@
       <c r="K23" s="5"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6726,10 +6810,10 @@
       <c r="K24" s="5"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N24" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6760,10 +6844,10 @@
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N25" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6786,10 +6870,10 @@
       <c r="K26" s="5"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -6820,10 +6904,10 @@
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N27" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6846,10 +6930,10 @@
       <c r="K28" s="5"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N28" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6872,10 +6956,10 @@
       <c r="K29" s="5"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N29" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6898,10 +6982,10 @@
       <c r="K30" s="5"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N30" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6924,10 +7008,10 @@
       <c r="K31" s="5"/>
       <c r="L31" s="8"/>
       <c r="M31" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N31" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6958,10 +7042,10 @@
       </c>
       <c r="L32" s="8"/>
       <c r="M32" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N32" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6984,10 +7068,10 @@
       <c r="K33" s="5"/>
       <c r="L33" s="8"/>
       <c r="M33" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="N33" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7012,10 +7096,10 @@
       </c>
       <c r="L34" s="8"/>
       <c r="M34" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N34" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7038,10 +7122,10 @@
       <c r="K35" s="5"/>
       <c r="L35" s="8"/>
       <c r="M35" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N35" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7072,10 +7156,10 @@
       </c>
       <c r="L36" s="8"/>
       <c r="M36" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N36" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7098,10 +7182,10 @@
       <c r="K37" s="5"/>
       <c r="L37" s="8"/>
       <c r="M37" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N37" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7132,10 +7216,10 @@
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="N38" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7158,10 +7242,10 @@
       <c r="K39" s="5"/>
       <c r="L39" s="8"/>
       <c r="M39" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N39" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7184,10 +7268,10 @@
       <c r="K40" s="5"/>
       <c r="L40" s="8"/>
       <c r="M40" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N40" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7218,10 +7302,10 @@
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N41" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7252,10 +7336,10 @@
       </c>
       <c r="L42" s="8"/>
       <c r="M42" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="N42" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7278,10 +7362,10 @@
       <c r="K43" s="5"/>
       <c r="L43" s="8"/>
       <c r="M43" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N43" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7306,10 +7390,10 @@
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N44" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N44" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7332,10 +7416,10 @@
       <c r="K45" s="5"/>
       <c r="L45" s="8"/>
       <c r="M45" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N45" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N45" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -7366,10 +7450,10 @@
       </c>
       <c r="L46" s="8"/>
       <c r="M46" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="N46" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="N46" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7392,10 +7476,10 @@
       <c r="K47" s="5"/>
       <c r="L47" s="8"/>
       <c r="M47" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="N47" s="8" t="s">
         <v>637</v>
-      </c>
-      <c r="N47" s="8" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -7833,18 +7917,18 @@
         <v>-38.055428999999997</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="D8" s="6">
         <v>-57.679726000000002</v>
@@ -7853,7 +7937,7 @@
         <v>-38.055993000000001</v>
       </c>
       <c r="F8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>662</v>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jzurita\Documents\Personal\ArboretumMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61229F68-AB47-41DF-A990-55E8E03BDBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6469A971-6561-4277-8113-870C616E33E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -7469,7 +7469,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>PechoAmarillo.JPG</t>
+          <t>Pechoamarillo.JPG</t>
         </is>
       </c>
       <c r="L32" s="8" t="n"/>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>TyrannusSavana.jpg</t>
+          <t>Tyrannussavana.jpg</t>
         </is>
       </c>
       <c r="L42" s="8" t="n"/>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Tordorenegrido.JPG</t>
+          <t>TordoRenegrido.JPG</t>
         </is>
       </c>
       <c r="L46" s="8" t="n"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -7469,7 +7469,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Pechoamarillo.JPG</t>
+          <t>pecho_amarillo.jpg</t>
         </is>
       </c>
       <c r="L32" s="8" t="n"/>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Tyrannussavana.jpg</t>
+          <t>tyrannus_savana.jpg</t>
         </is>
       </c>
       <c r="L42" s="8" t="n"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:Z92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="19.81640625" customWidth="1" min="2" max="2"/>
@@ -666,6 +666,16 @@
           <t>caduco_perenne</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>autor</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>forma_vida</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -680,7 +690,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Sabina virginiana (L.) Antoine</t>
+          <t>Sabina virginiana</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
@@ -742,6 +752,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>(L.) Antoine</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="29" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -804,6 +824,12 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -818,7 +844,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Quercus robur L.</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -874,6 +900,16 @@
         </is>
       </c>
       <c r="V4" s="16" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="43.5" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -888,7 +924,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Ilex aquifolium L.</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -932,6 +968,16 @@
         </is>
       </c>
       <c r="V5" s="16" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="43.5" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -946,7 +992,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Cedrus deodara (Roxb. ex D. Don) G. Don</t>
+          <t>Cedrus deodara</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
@@ -1006,6 +1052,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>(Roxb. ex D. Don) G. Don</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1020,7 +1076,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Casuarina equisetifolia L.</t>
+          <t>Casuarina equisetifolia</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1064,6 +1120,16 @@
         </is>
       </c>
       <c r="V7" s="16" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="43.5" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1078,7 +1144,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Nerium oleander L.</t>
+          <t>Nerium oleander</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -1122,6 +1188,16 @@
         </is>
       </c>
       <c r="V8" s="16" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1136,7 +1212,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Calocedrus decurrens (Torr.) Florin</t>
+          <t>Calocedrus decurrens</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1184,6 +1260,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>(Torr.) Florin</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1198,7 +1284,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Cedrus atlantica (Endl.) Manetti ex Carrière</t>
+          <t>Cedrus atlantica</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -1258,6 +1344,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>(Endl.) Manetti ex Carrière</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1316,6 +1412,12 @@
         </is>
       </c>
       <c r="V11" s="16" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="43.5" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -1326,7 +1428,7 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Eucalyptus globulus Labill.</t>
+          <t>Eucalyptus globulus</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -1374,6 +1476,16 @@
         </is>
       </c>
       <c r="V12" s="16" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Labill.</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="29" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1436,6 +1548,12 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="43.5" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1450,7 +1568,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Quercus rubra L.</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -1506,6 +1624,16 @@
         </is>
       </c>
       <c r="V14" s="16" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1520,7 +1648,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Abies concolor (Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
+          <t>Abies concolor</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1580,6 +1708,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>(Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1638,6 +1776,12 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -1710,6 +1854,12 @@
         </is>
       </c>
       <c r="V17" s="16" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1724,7 +1874,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Abelia x grandiflora L.</t>
+          <t>Abelia ×grandiflora</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -1768,6 +1918,16 @@
         </is>
       </c>
       <c r="V18" s="16" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>(André) Rehder</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -1830,6 +1990,12 @@
         </is>
       </c>
       <c r="V19" s="16" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -1844,7 +2010,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Magnolia grandiflora L.</t>
+          <t>Magnolia grandiflora</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -1892,6 +2058,16 @@
         </is>
       </c>
       <c r="V20" s="16" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -1906,7 +2082,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Platanus x hispanica</t>
+          <t>Platanus ×hispanica</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -1954,6 +2130,16 @@
         </is>
       </c>
       <c r="V21" s="16" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Mill. ex Münchh.</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="29" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -2018,6 +2204,12 @@
         </is>
       </c>
       <c r="V22" s="16" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="29" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -2032,7 +2224,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Araucaria bidwillii Hook.</t>
+          <t>Araucaria bidwillii</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2092,6 +2284,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Hook.</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="29" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -2106,7 +2308,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Cupressus macrocarpa var. lutea topacio</t>
+          <t>Cupressus macrocarpa var. lutea</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -2154,6 +2356,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Hartw. ex Gordon</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="29" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -2216,6 +2428,12 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="29" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -2230,7 +2448,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Casuarina equisetifolia L.</t>
+          <t>Casuarina equisetifolia</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -2274,6 +2492,16 @@
         </is>
       </c>
       <c r="V26" s="16" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="43.5" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -2288,7 +2516,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Quercus baloot Griff.</t>
+          <t>Quercus baloot</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -2340,6 +2568,16 @@
         </is>
       </c>
       <c r="V27" s="16" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Griff.</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="43.5" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -2354,7 +2592,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Pinus patula Schltdl. &amp; Cham.</t>
+          <t>Pinus patula</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -2402,6 +2640,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Schltdl. &amp; Cham.</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="29" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -2416,7 +2664,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Araucaria bidwillii Hook.</t>
+          <t>Araucaria bidwillii</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -2473,6 +2721,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Hook.</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="29" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -2487,7 +2745,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Populu alba L.</t>
+          <t>Populus alba</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -2531,6 +2789,16 @@
         </is>
       </c>
       <c r="V30" s="16" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="43.5" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -2545,7 +2813,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Aesculus hippocastanum L.</t>
+          <t>Aesculus hippocastanum</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -2601,6 +2869,16 @@
         </is>
       </c>
       <c r="V31" s="16" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2615,7 +2893,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>?Cinnamomum camphora</t>
+          <t>Cinnamomum camphora</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -2659,6 +2937,16 @@
         </is>
       </c>
       <c r="V32" s="16" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>(L.) J.Presl</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="29" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -2673,7 +2961,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Cryptomeria japonica (Thunb. ex L. f.) D. Don</t>
+          <t>Cryptomeria japonica</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -2733,6 +3021,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>(Thunb. ex L. f.) D. Don</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="29" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -2791,6 +3089,12 @@
         </is>
       </c>
       <c r="V34" s="16" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="29" customHeight="1">
       <c r="A35" t="inlineStr">
@@ -2857,6 +3161,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>(Lindl.) J.Buchholz</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="43.5" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -2911,6 +3225,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Ten.</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="43.5" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -2965,6 +3289,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>(D.Don) Pic.Serm. &amp; Bizzarri</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -3019,6 +3353,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="29" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -3069,6 +3413,16 @@
         </is>
       </c>
       <c r="V39" s="16" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Eschsch.</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="43.5" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -3083,7 +3437,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Hypericum x moserianum</t>
+          <t>Hypericum ×moserianum</t>
         </is>
       </c>
       <c r="D40" s="5" t="n"/>
@@ -3119,6 +3473,16 @@
         </is>
       </c>
       <c r="V40" s="16" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="43.5" customHeight="1">
       <c r="A41" t="inlineStr">
@@ -3169,6 +3533,16 @@
         </is>
       </c>
       <c r="V41" s="16" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Gillies ex Planch.</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="29" customHeight="1">
       <c r="A42" t="inlineStr">
@@ -3235,6 +3609,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>(Lamb.) Rich. &amp; A.Rich.</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3293,6 +3677,16 @@
         </is>
       </c>
       <c r="V43" s="16" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="29" customHeight="1">
       <c r="A44" t="inlineStr">
@@ -3307,7 +3701,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Quercus rubra L.</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
@@ -3351,6 +3745,16 @@
         </is>
       </c>
       <c r="V44" s="16" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" t="inlineStr">
@@ -3365,7 +3769,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Abies concolor (Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
+          <t>Abies concolor</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -3413,6 +3817,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>(Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="29" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -3475,6 +3889,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>(A.Murray bis) Parl.</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="29" customHeight="1">
       <c r="A47" t="inlineStr">
@@ -3537,6 +3961,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>(Siebold &amp; Zucc.) Endl.</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="29" customHeight="1">
       <c r="A48" t="inlineStr">
@@ -3595,6 +4029,16 @@
         </is>
       </c>
       <c r="V48" s="16" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Lour.</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="29" customHeight="1">
       <c r="A49" t="inlineStr">
@@ -3653,6 +4097,16 @@
         </is>
       </c>
       <c r="V49" s="16" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Lour.</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="43.5" customHeight="1">
       <c r="A50" t="inlineStr">
@@ -3703,6 +4157,12 @@
         </is>
       </c>
       <c r="V50" s="16" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3771,6 +4231,16 @@
         </is>
       </c>
       <c r="V51" s="16" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Thunb.</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" t="inlineStr">
@@ -3829,6 +4299,12 @@
         </is>
       </c>
       <c r="V52" s="16" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="101.5" customHeight="1">
       <c r="A53" t="inlineStr">
@@ -3887,6 +4363,16 @@
         </is>
       </c>
       <c r="V53" s="16" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Jacq.</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="29" customHeight="1">
       <c r="A54" t="inlineStr">
@@ -3949,6 +4435,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>(A.Murray bis) Parl.</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="29" customHeight="1">
       <c r="A55" t="inlineStr">
@@ -4007,6 +4503,16 @@
         </is>
       </c>
       <c r="V55" s="16" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>W.T.Aiton</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="43.5" customHeight="1">
       <c r="A56" t="inlineStr">
@@ -4021,7 +4527,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Cedrus sp.`</t>
+          <t>Cedrus sp.</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -4057,6 +4563,12 @@
         </is>
       </c>
       <c r="V56" s="16" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="43.5" customHeight="1">
       <c r="A57" t="inlineStr">
@@ -4115,6 +4627,16 @@
         </is>
       </c>
       <c r="V57" s="16" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>(L.) J.Presl</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="43.5" customHeight="1">
       <c r="A58" t="inlineStr">
@@ -4165,6 +4687,12 @@
         </is>
       </c>
       <c r="V58" s="16" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="43.5" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -4223,6 +4751,16 @@
         </is>
       </c>
       <c r="V59" s="16" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="29" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -4237,7 +4775,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Quercus rubra L.</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
@@ -4281,6 +4819,16 @@
         </is>
       </c>
       <c r="V60" s="16" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4339,6 +4887,16 @@
         </is>
       </c>
       <c r="V61" s="16" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Jacq.</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="43.5" customHeight="1">
       <c r="A62" t="inlineStr">
@@ -4397,6 +4955,16 @@
         </is>
       </c>
       <c r="V62" s="16" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="29" customHeight="1">
       <c r="A63" t="inlineStr">
@@ -4459,6 +5027,16 @@
         </is>
       </c>
       <c r="V63" s="16" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Hance</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="29" customHeight="1">
       <c r="A64" t="inlineStr">
@@ -4517,6 +5095,16 @@
         </is>
       </c>
       <c r="V64" s="16" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Lour.</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="43.5" customHeight="1">
       <c r="A65" t="inlineStr">
@@ -4567,6 +5155,12 @@
         </is>
       </c>
       <c r="V65" s="16" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="29" customHeight="1">
       <c r="A66" t="inlineStr">
@@ -4625,6 +5219,16 @@
         </is>
       </c>
       <c r="V66" s="16" t="inlineStr"/>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>M.Roem.</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" t="inlineStr">
@@ -4683,6 +5287,16 @@
         </is>
       </c>
       <c r="V67" s="16" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Jacq.</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="29" customHeight="1">
       <c r="A68" t="inlineStr">
@@ -4741,6 +5355,16 @@
         </is>
       </c>
       <c r="V68" s="16" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>W.T.Aiton</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="43.5" customHeight="1">
       <c r="A69" t="inlineStr">
@@ -4791,6 +5415,12 @@
         </is>
       </c>
       <c r="V69" s="16" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="43.5" customHeight="1">
       <c r="A70" t="inlineStr">
@@ -4849,6 +5479,16 @@
         </is>
       </c>
       <c r="V70" s="16" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>F.Muell. ex Benth.</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="29" customHeight="1">
       <c r="A71" t="inlineStr">
@@ -4863,7 +5503,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Sequoia semprevirens</t>
+          <t>Sequoia sempervirens</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
@@ -4907,6 +5547,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>(D.Don) Endl.</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="29" customHeight="1">
       <c r="A72" t="inlineStr">
@@ -4973,6 +5623,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>D.Don</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="58" customHeight="1">
       <c r="A73" t="inlineStr">
@@ -5031,6 +5691,16 @@
         </is>
       </c>
       <c r="V73" s="16" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>(Mirb.) Oerst.</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="58" customHeight="1">
       <c r="A74" t="inlineStr">
@@ -5045,7 +5715,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Nothofagus obliqua 2</t>
+          <t>Nothofagus obliqua</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
@@ -5089,6 +5759,16 @@
         </is>
       </c>
       <c r="V74" s="16" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>(Mirb.) Oerst.</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="29" customHeight="1">
       <c r="A75" t="inlineStr">
@@ -5103,7 +5783,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Cryptomeria japónica</t>
+          <t>Cryptomeria japonica</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -5147,6 +5827,16 @@
         </is>
       </c>
       <c r="V75" s="16" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>(Thunb. ex L. f.) D. Don</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
         <is>
           <t>Conífera</t>
         </is>
@@ -5201,6 +5891,12 @@
         </is>
       </c>
       <c r="V76" s="16" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="29" customHeight="1">
       <c r="A77" t="inlineStr">
@@ -5259,6 +5955,16 @@
         </is>
       </c>
       <c r="V77" s="16" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="43.5" customHeight="1">
       <c r="A78" t="inlineStr">
@@ -5273,7 +5979,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Eucalyptus globulus Labill.</t>
+          <t>Eucalyptus globulus</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
@@ -5317,6 +6023,16 @@
         </is>
       </c>
       <c r="V78" s="16" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Labill.</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="43.5" customHeight="1">
       <c r="A79" t="inlineStr">
@@ -5379,6 +6095,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Ten.</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="87" customHeight="1">
       <c r="A80" t="inlineStr">
@@ -5437,6 +6163,16 @@
         </is>
       </c>
       <c r="V80" s="16" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Vahl</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="29" customHeight="1">
       <c r="A81" t="inlineStr">
@@ -5451,7 +6187,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Fraxinus exelsior</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -5495,6 +6231,16 @@
         </is>
       </c>
       <c r="V81" s="16" t="inlineStr"/>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="29" customHeight="1">
       <c r="A82" t="inlineStr">
@@ -5553,6 +6299,16 @@
         </is>
       </c>
       <c r="V82" s="16" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>D.Don</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
         <is>
           <t>Conífera</t>
         </is>
@@ -5607,6 +6363,12 @@
         </is>
       </c>
       <c r="V83" s="16" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="29" customHeight="1">
       <c r="A84" t="inlineStr">
@@ -5665,6 +6427,16 @@
         </is>
       </c>
       <c r="V84" s="16" t="inlineStr"/>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Gillies ex Planch.</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="29" customHeight="1">
       <c r="A85" t="inlineStr">
@@ -5679,7 +6451,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Brahea Armata Palmatum</t>
+          <t>Brahea armata</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -5727,6 +6499,16 @@
           <t>Palmera</t>
         </is>
       </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>S.Watson</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Palmera</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="29" customHeight="1">
       <c r="A86" t="inlineStr">
@@ -5785,6 +6567,16 @@
         </is>
       </c>
       <c r="V86" s="16" t="inlineStr"/>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Gillies ex Planch.</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="29" customHeight="1">
       <c r="A87" t="inlineStr">
@@ -5843,6 +6635,16 @@
         </is>
       </c>
       <c r="V87" s="16" t="inlineStr"/>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Gillies ex Planch.</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="29" customHeight="1">
       <c r="A88" t="inlineStr">
@@ -5857,7 +6659,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Cedrus atlantica (Endl.) Manetti ex Carrière</t>
+          <t>Cedrus atlantica</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -5905,6 +6707,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>(Endl.) Manetti ex Carrière</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="29" customHeight="1">
       <c r="A89" t="inlineStr">
@@ -5919,7 +6731,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Cedrus atlantica (Endl.) Manetti ex Carrière</t>
+          <t>Cedrus atlantica</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -5967,6 +6779,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>(Endl.) Manetti ex Carrière</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="29" customHeight="1">
       <c r="A90" t="inlineStr">
@@ -6029,6 +6851,16 @@
           <t>Conífera</t>
         </is>
       </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Ten.</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6087,6 +6919,16 @@
         </is>
       </c>
       <c r="V91" s="16" t="inlineStr"/>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="29" customHeight="1">
       <c r="A92" t="inlineStr">
@@ -6137,6 +6979,12 @@
         </is>
       </c>
       <c r="V92" s="16" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z92"/>
+  <dimension ref="A1:AA92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="19.81640625" customWidth="1" min="2" max="2"/>
@@ -676,6 +676,11 @@
           <t>forma_vida</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>padrino</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -824,7 +829,6 @@
           <t>Conífera</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -1412,7 +1416,6 @@
         </is>
       </c>
       <c r="V11" s="16" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
           <t>Otro</t>
@@ -1548,7 +1551,6 @@
           <t>Conífera</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -1776,7 +1778,6 @@
           <t>Conífera</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -1854,7 +1855,6 @@
         </is>
       </c>
       <c r="V17" s="16" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
           <t>Arbusto</t>
@@ -1990,7 +1990,6 @@
         </is>
       </c>
       <c r="V19" s="16" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
           <t>Arbusto</t>
@@ -2204,7 +2203,6 @@
         </is>
       </c>
       <c r="V22" s="16" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr">
         <is>
           <t>Árbol latifoliado</t>
@@ -2428,7 +2426,6 @@
           <t>Conífera</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -3089,7 +3086,6 @@
         </is>
       </c>
       <c r="V34" s="16" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr">
         <is>
           <t>Árbol latifoliado</t>
@@ -4157,7 +4153,6 @@
         </is>
       </c>
       <c r="V50" s="16" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -4299,7 +4294,6 @@
         </is>
       </c>
       <c r="V52" s="16" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr">
         <is>
           <t>Arbusto</t>
@@ -4563,7 +4557,6 @@
         </is>
       </c>
       <c r="V56" s="16" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -4687,7 +4680,6 @@
         </is>
       </c>
       <c r="V58" s="16" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr">
         <is>
           <t>Otro</t>
@@ -5155,7 +5147,6 @@
         </is>
       </c>
       <c r="V65" s="16" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -5415,7 +5406,6 @@
         </is>
       </c>
       <c r="V69" s="16" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr">
         <is>
           <t>Otro</t>
@@ -5891,7 +5881,6 @@
         </is>
       </c>
       <c r="V76" s="16" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr">
         <is>
           <t>Conífera</t>
@@ -6363,7 +6352,6 @@
         </is>
       </c>
       <c r="V83" s="16" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr">
         <is>
           <t>Árbol latifoliado</t>
@@ -6979,7 +6967,6 @@
         </is>
       </c>
       <c r="V92" s="16" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr">
         <is>
           <t>Árbol latifoliado</t>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -11,8 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Senderos" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Puntos de interés" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos fenológicos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisar_datos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -22,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,16 +66,8 @@
       <name val="Segoe UI"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -88,11 +78,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F9F6"/>
         <bgColor rgb="FFF5F9F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E4A38"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -181,11 +166,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA92"/>
+  <dimension ref="A1:T92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="19.81640625" customWidth="1" min="2" max="2"/>
@@ -539,10 +519,6 @@
     <col width="12.7265625" customWidth="1" min="7" max="7"/>
     <col width="14.54296875" customWidth="1" min="9" max="9"/>
     <col width="13.36328125" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="29" customHeight="1">
@@ -646,41 +622,6 @@
           <t>ficha</t>
         </is>
       </c>
-      <c r="U1" s="15" t="inlineStr">
-        <is>
-          <t>continente_norm</t>
-        </is>
-      </c>
-      <c r="V1" s="15" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="W1" s="15" t="inlineStr">
-        <is>
-          <t>nativo_exotico</t>
-        </is>
-      </c>
-      <c r="X1" s="15" t="inlineStr">
-        <is>
-          <t>caduco_perenne</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>autor</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>forma_vida</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>padrino</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -695,7 +636,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Sabina virginiana</t>
+          <t>Sabina virginiana (L.) Antoine</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
@@ -747,26 +688,6 @@
           <t>sabina</t>
         </is>
       </c>
-      <c r="U2" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V2" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>(L.) Antoine</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="29" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -819,21 +740,6 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="U3" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V3" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -848,7 +754,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus robur L.</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -898,22 +804,6 @@
           <t>roblecomun</t>
         </is>
       </c>
-      <c r="U4" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V4" s="16" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="43.5" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -928,7 +818,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Ilex aquifolium</t>
+          <t>Ilex aquifolium L.</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -966,22 +856,6 @@
           <t>A4</t>
         </is>
       </c>
-      <c r="U5" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V5" s="16" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="43.5" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -996,7 +870,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Cedrus deodara</t>
+          <t>Cedrus deodara (Roxb. ex D. Don) G. Don</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
@@ -1046,26 +920,6 @@
           <t>cedrodelhimalaya</t>
         </is>
       </c>
-      <c r="U6" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V6" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>(Roxb. ex D. Don) G. Don</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1080,7 +934,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Casuarina equisetifolia</t>
+          <t>Casuarina equisetifolia L.</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1118,22 +972,6 @@
           <t>A6</t>
         </is>
       </c>
-      <c r="U7" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V7" s="16" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="43.5" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1148,7 +986,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Nerium oleander</t>
+          <t>Nerium oleander L.</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -1186,22 +1024,6 @@
           <t>A7</t>
         </is>
       </c>
-      <c r="U8" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V8" s="16" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1216,7 +1038,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Calocedrus decurrens</t>
+          <t>Calocedrus decurrens (Torr.) Florin</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -1254,26 +1076,6 @@
           <t>A8</t>
         </is>
       </c>
-      <c r="U9" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V9" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>(Torr.) Florin</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1288,7 +1090,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Cedrus atlantica</t>
+          <t>Cedrus atlantica (Endl.) Manetti ex Carrière</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -1338,26 +1140,6 @@
           <t>cedroazul</t>
         </is>
       </c>
-      <c r="U10" s="16" t="inlineStr">
-        <is>
-          <t>África</t>
-        </is>
-      </c>
-      <c r="V10" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>(Endl.) Manetti ex Carrière</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1410,17 +1192,6 @@
           <t>A10</t>
         </is>
       </c>
-      <c r="U11" s="16" t="inlineStr">
-        <is>
-          <t>Sin dato</t>
-        </is>
-      </c>
-      <c r="V11" s="16" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="43.5" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -1431,7 +1202,7 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Eucalyptus globulus</t>
+          <t>Eucalyptus globulus Labill.</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -1473,22 +1244,6 @@
           <t>A11</t>
         </is>
       </c>
-      <c r="U12" s="16" t="inlineStr">
-        <is>
-          <t>Oceanía</t>
-        </is>
-      </c>
-      <c r="V12" s="16" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Labill.</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="29" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1541,21 +1296,6 @@
           <t>A12</t>
         </is>
       </c>
-      <c r="U13" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V13" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="43.5" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1570,7 +1310,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus rubra L.</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -1620,22 +1360,6 @@
           <t>roblerojo</t>
         </is>
       </c>
-      <c r="U14" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V14" s="16" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1650,7 +1374,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Abies concolor</t>
+          <t>Abies concolor (Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1700,26 +1424,6 @@
           <t>abeto</t>
         </is>
       </c>
-      <c r="U15" s="16" t="inlineStr">
-        <is>
-          <t>América</t>
-        </is>
-      </c>
-      <c r="V15" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>(Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1768,21 +1472,6 @@
           <t>A15</t>
         </is>
       </c>
-      <c r="U16" s="16" t="inlineStr">
-        <is>
-          <t>Sin dato</t>
-        </is>
-      </c>
-      <c r="V16" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -1849,17 +1538,6 @@
           <t>limpiatubos</t>
         </is>
       </c>
-      <c r="U17" s="16" t="inlineStr">
-        <is>
-          <t>América del Sur</t>
-        </is>
-      </c>
-      <c r="V17" s="16" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1874,7 +1552,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Abelia ×grandiflora</t>
+          <t>Abelia x grandiflora L.</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -1912,22 +1590,6 @@
           <t>A17</t>
         </is>
       </c>
-      <c r="U18" s="16" t="inlineStr">
-        <is>
-          <t>Origen hortícola/híbrido</t>
-        </is>
-      </c>
-      <c r="V18" s="16" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>(André) Rehder</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -1984,17 +1646,6 @@
           <t>A18</t>
         </is>
       </c>
-      <c r="U19" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V19" s="16" t="inlineStr"/>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -2009,7 +1660,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Magnolia grandiflora</t>
+          <t>Magnolia grandiflora L.</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -2051,22 +1702,6 @@
           <t>A19</t>
         </is>
       </c>
-      <c r="U20" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V20" s="16" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -2081,7 +1716,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Platanus ×hispanica</t>
+          <t>Platanus x hispanica</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2123,22 +1758,6 @@
           <t>A20</t>
         </is>
       </c>
-      <c r="U21" s="16" t="inlineStr">
-        <is>
-          <t>Origen hortícola/híbrido</t>
-        </is>
-      </c>
-      <c r="V21" s="16" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Mill. ex Münchh.</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="29" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -2197,17 +1816,6 @@
           <t>A21</t>
         </is>
       </c>
-      <c r="U22" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V22" s="16" t="inlineStr"/>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="29" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -2222,7 +1830,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Araucaria bidwillii</t>
+          <t>Araucaria bidwillii Hook.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -2272,26 +1880,6 @@
           <t>araucariaaustraliana</t>
         </is>
       </c>
-      <c r="U23" s="16" t="inlineStr">
-        <is>
-          <t>Oceanía</t>
-        </is>
-      </c>
-      <c r="V23" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Hook.</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="29" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -2306,7 +1894,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Cupressus macrocarpa var. lutea</t>
+          <t>Cupressus macrocarpa var. lutea topacio</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -2344,26 +1932,6 @@
           <t>A23</t>
         </is>
       </c>
-      <c r="U24" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V24" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Hartw. ex Gordon</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="29" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -2416,21 +1984,6 @@
           <t>A24</t>
         </is>
       </c>
-      <c r="U25" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V25" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="29" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -2445,7 +1998,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Casuarina equisetifolia</t>
+          <t>Casuarina equisetifolia L.</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -2483,22 +2036,6 @@
           <t>A25</t>
         </is>
       </c>
-      <c r="U26" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V26" s="16" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="27" ht="43.5" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -2513,7 +2050,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Quercus baloot</t>
+          <t>Quercus baloot Griff.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -2559,22 +2096,6 @@
           <t>encina</t>
         </is>
       </c>
-      <c r="U27" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V27" s="16" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Griff.</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="43.5" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -2589,7 +2110,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Pinus patula</t>
+          <t>Pinus patula Schltdl. &amp; Cham.</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -2627,26 +2148,6 @@
           <t>A27</t>
         </is>
       </c>
-      <c r="U28" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V28" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Schltdl. &amp; Cham.</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="29" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -2661,7 +2162,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Araucaria bidwillii</t>
+          <t>Araucaria bidwillii Hook.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -2708,26 +2209,6 @@
           <t>araucariaaustraliana</t>
         </is>
       </c>
-      <c r="U29" s="16" t="inlineStr">
-        <is>
-          <t>Oceanía</t>
-        </is>
-      </c>
-      <c r="V29" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Hook.</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="29" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -2742,7 +2223,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Populus alba</t>
+          <t>Populu alba L.</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -2780,22 +2261,6 @@
           <t>A29</t>
         </is>
       </c>
-      <c r="U30" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V30" s="16" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="43.5" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -2810,7 +2275,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Aesculus hippocastanum</t>
+          <t>Aesculus hippocastanum L.</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -2860,22 +2325,6 @@
           <t>castanodeindias</t>
         </is>
       </c>
-      <c r="U31" s="16" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="V31" s="16" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2890,7 +2339,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Cinnamomum camphora</t>
+          <t>?Cinnamomum camphora</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -2928,22 +2377,6 @@
           <t>A31</t>
         </is>
       </c>
-      <c r="U32" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V32" s="16" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>(L.) J.Presl</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="29" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -2958,7 +2391,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Cryptomeria japonica</t>
+          <t>Cryptomeria japonica (Thunb. ex L. f.) D. Don</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -3008,26 +2441,6 @@
           <t>cedrojapones</t>
         </is>
       </c>
-      <c r="U33" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V33" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>(Thunb. ex L. f.) D. Don</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="29" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -3078,17 +2491,6 @@
       <c r="R34" s="5" t="inlineStr">
         <is>
           <t>A33</t>
-        </is>
-      </c>
-      <c r="U34" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V34" s="16" t="inlineStr"/>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
         </is>
       </c>
     </row>
@@ -3147,26 +2549,6 @@
           <t>secuoiaroja</t>
         </is>
       </c>
-      <c r="U35" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V35" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>(Lindl.) J.Buchholz</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="43.5" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -3211,26 +2593,6 @@
           <t>A35</t>
         </is>
       </c>
-      <c r="U36" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V36" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Ten.</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="43.5" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -3275,26 +2637,6 @@
           <t>A36</t>
         </is>
       </c>
-      <c r="U37" s="16" t="inlineStr">
-        <is>
-          <t>América del Sur</t>
-        </is>
-      </c>
-      <c r="V37" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>(D.Don) Pic.Serm. &amp; Bizzarri</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -3339,26 +2681,6 @@
           <t>A37</t>
         </is>
       </c>
-      <c r="U38" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V38" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="39" ht="29" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -3403,22 +2725,6 @@
           <t>A38</t>
         </is>
       </c>
-      <c r="U39" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V39" s="16" t="inlineStr"/>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Eschsch.</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="43.5" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -3433,7 +2739,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Hypericum ×moserianum</t>
+          <t>Hypericum x moserianum</t>
         </is>
       </c>
       <c r="D40" s="5" t="n"/>
@@ -3463,22 +2769,6 @@
           <t>A39</t>
         </is>
       </c>
-      <c r="U40" s="16" t="inlineStr">
-        <is>
-          <t>África</t>
-        </is>
-      </c>
-      <c r="V40" s="16" t="inlineStr"/>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>André</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="41" ht="43.5" customHeight="1">
       <c r="A41" t="inlineStr">
@@ -3523,22 +2813,6 @@
           <t>A40</t>
         </is>
       </c>
-      <c r="U41" s="16" t="inlineStr">
-        <is>
-          <t>Cosmopolita</t>
-        </is>
-      </c>
-      <c r="V41" s="16" t="inlineStr"/>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Gillies ex Planch.</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="29" customHeight="1">
       <c r="A42" t="inlineStr">
@@ -3595,26 +2869,6 @@
           <t>damara</t>
         </is>
       </c>
-      <c r="U42" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V42" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>(Lamb.) Rich. &amp; A.Rich.</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3667,22 +2921,6 @@
           <t>arboldelostulipanes</t>
         </is>
       </c>
-      <c r="U43" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V43" s="16" t="inlineStr"/>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="44" ht="29" customHeight="1">
       <c r="A44" t="inlineStr">
@@ -3697,7 +2935,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus rubra L.</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
@@ -3712,7 +2950,11 @@
         </is>
       </c>
       <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Roblerojoamericano.jpg</t>
+        </is>
+      </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>Fagaceae</t>
@@ -3735,22 +2977,6 @@
           <t>Jb1</t>
         </is>
       </c>
-      <c r="U44" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V44" s="16" t="inlineStr"/>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" t="inlineStr">
@@ -3765,7 +2991,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Abies concolor</t>
+          <t>Abies concolor (Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -3780,7 +3006,11 @@
         </is>
       </c>
       <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Abeto.jpg</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Pinaceae</t>
@@ -3803,26 +3033,6 @@
           <t>Jb2</t>
         </is>
       </c>
-      <c r="U45" s="16" t="inlineStr">
-        <is>
-          <t>América</t>
-        </is>
-      </c>
-      <c r="V45" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>(Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="29" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -3875,26 +3085,6 @@
           <t>Jb3</t>
         </is>
       </c>
-      <c r="U46" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V46" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>(A.Murray bis) Parl.</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="47" ht="29" customHeight="1">
       <c r="A47" t="inlineStr">
@@ -3947,26 +3137,6 @@
           <t>Jb4</t>
         </is>
       </c>
-      <c r="U47" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V47" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>(Siebold &amp; Zucc.) Endl.</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="48" ht="29" customHeight="1">
       <c r="A48" t="inlineStr">
@@ -4019,22 +3189,6 @@
           <t>Jb5</t>
         </is>
       </c>
-      <c r="U48" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V48" s="16" t="inlineStr"/>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Lour.</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="49" ht="29" customHeight="1">
       <c r="A49" t="inlineStr">
@@ -4085,22 +3239,6 @@
       <c r="R49" s="5" t="inlineStr">
         <is>
           <t>Jb6</t>
-        </is>
-      </c>
-      <c r="U49" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V49" s="16" t="inlineStr"/>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Lour.</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
         </is>
       </c>
     </row>
@@ -4147,17 +3285,6 @@
           <t>Jb7</t>
         </is>
       </c>
-      <c r="U50" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V50" s="16" t="inlineStr"/>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4220,22 +3347,6 @@
           <t>gingko</t>
         </is>
       </c>
-      <c r="U51" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V51" s="16" t="inlineStr"/>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Thunb.</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" t="inlineStr">
@@ -4265,7 +3376,11 @@
         </is>
       </c>
       <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Crataegus.jpg</t>
+        </is>
+      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Rosaceae</t>
@@ -4288,17 +3403,6 @@
           <t>Jb9</t>
         </is>
       </c>
-      <c r="U52" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V52" s="16" t="inlineStr"/>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="53" ht="101.5" customHeight="1">
       <c r="A53" t="inlineStr">
@@ -4351,22 +3455,6 @@
           <t>Jb10</t>
         </is>
       </c>
-      <c r="U53" s="16" t="inlineStr">
-        <is>
-          <t>Cosmopolita</t>
-        </is>
-      </c>
-      <c r="V53" s="16" t="inlineStr"/>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Jacq.</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="54" ht="29" customHeight="1">
       <c r="A54" t="inlineStr">
@@ -4419,26 +3507,6 @@
           <t>Jb11</t>
         </is>
       </c>
-      <c r="U54" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V54" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>(A.Murray bis) Parl.</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="55" ht="29" customHeight="1">
       <c r="A55" t="inlineStr">
@@ -4491,22 +3559,6 @@
           <t>Jb12</t>
         </is>
       </c>
-      <c r="U55" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V55" s="16" t="inlineStr"/>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>W.T.Aiton</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="56" ht="43.5" customHeight="1">
       <c r="A56" t="inlineStr">
@@ -4521,7 +3573,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Cedrus sp.</t>
+          <t>Cedrus sp.`</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -4551,17 +3603,6 @@
           <t>Jb13</t>
         </is>
       </c>
-      <c r="U56" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V56" s="16" t="inlineStr"/>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="57" ht="43.5" customHeight="1">
       <c r="A57" t="inlineStr">
@@ -4612,22 +3653,6 @@
       <c r="R57" s="5" t="inlineStr">
         <is>
           <t>Jb14</t>
-        </is>
-      </c>
-      <c r="U57" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V57" s="16" t="inlineStr"/>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>(L.) J.Presl</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
         </is>
       </c>
     </row>
@@ -4674,17 +3699,6 @@
           <t>Jb15</t>
         </is>
       </c>
-      <c r="U58" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V58" s="16" t="inlineStr"/>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
     </row>
     <row r="59" ht="43.5" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -4737,22 +3751,6 @@
           <t>Jb16</t>
         </is>
       </c>
-      <c r="U59" s="16" t="inlineStr">
-        <is>
-          <t>Oceanía</t>
-        </is>
-      </c>
-      <c r="V59" s="16" t="inlineStr"/>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="60" ht="29" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -4767,7 +3765,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus rubra L.</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
@@ -4782,7 +3780,11 @@
         </is>
       </c>
       <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Roblerojoamericano.jpg</t>
+        </is>
+      </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
           <t>Fagaceae</t>
@@ -4805,22 +3807,6 @@
           <t>Jb17</t>
         </is>
       </c>
-      <c r="U60" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V60" s="16" t="inlineStr"/>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4873,22 +3859,6 @@
           <t>Jb18</t>
         </is>
       </c>
-      <c r="U61" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V61" s="16" t="inlineStr"/>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Jacq.</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="62" ht="43.5" customHeight="1">
       <c r="A62" t="inlineStr">
@@ -4941,22 +3911,6 @@
           <t>Jb19</t>
         </is>
       </c>
-      <c r="U62" s="16" t="inlineStr">
-        <is>
-          <t>Oceanía</t>
-        </is>
-      </c>
-      <c r="V62" s="16" t="inlineStr"/>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="63" ht="29" customHeight="1">
       <c r="A63" t="inlineStr">
@@ -5013,22 +3967,6 @@
           <t>Jb20</t>
         </is>
       </c>
-      <c r="U63" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V63" s="16" t="inlineStr"/>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Hance</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="64" ht="29" customHeight="1">
       <c r="A64" t="inlineStr">
@@ -5079,22 +4017,6 @@
       <c r="R64" s="5" t="inlineStr">
         <is>
           <t>Jb21</t>
-        </is>
-      </c>
-      <c r="U64" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V64" s="16" t="inlineStr"/>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Lour.</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
         </is>
       </c>
     </row>
@@ -5141,17 +4063,6 @@
           <t>Jb22</t>
         </is>
       </c>
-      <c r="U65" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V65" s="16" t="inlineStr"/>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="66" ht="29" customHeight="1">
       <c r="A66" t="inlineStr">
@@ -5204,22 +4115,6 @@
           <t>Jb23</t>
         </is>
       </c>
-      <c r="U66" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V66" s="16" t="inlineStr"/>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>M.Roem.</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" t="inlineStr">
@@ -5272,22 +4167,6 @@
           <t>Jb24</t>
         </is>
       </c>
-      <c r="U67" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V67" s="16" t="inlineStr"/>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>Jacq.</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>Arbusto</t>
-        </is>
-      </c>
     </row>
     <row r="68" ht="29" customHeight="1">
       <c r="A68" t="inlineStr">
@@ -5338,22 +4217,6 @@
       <c r="R68" s="5" t="inlineStr">
         <is>
           <t>Jb25</t>
-        </is>
-      </c>
-      <c r="U68" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V68" s="16" t="inlineStr"/>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>W.T.Aiton</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
         </is>
       </c>
     </row>
@@ -5400,17 +4263,6 @@
           <t>Jb26</t>
         </is>
       </c>
-      <c r="U69" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V69" s="16" t="inlineStr"/>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
     </row>
     <row r="70" ht="43.5" customHeight="1">
       <c r="A70" t="inlineStr">
@@ -5463,22 +4315,6 @@
           <t>Jb27</t>
         </is>
       </c>
-      <c r="U70" s="16" t="inlineStr">
-        <is>
-          <t>Oceanía</t>
-        </is>
-      </c>
-      <c r="V70" s="16" t="inlineStr"/>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>F.Muell. ex Benth.</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="71" ht="29" customHeight="1">
       <c r="A71" t="inlineStr">
@@ -5493,7 +4329,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Sequoia sempervirens</t>
+          <t>Sequoia semprevirens</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
@@ -5527,26 +4363,6 @@
           <t>Jb28</t>
         </is>
       </c>
-      <c r="U71" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V71" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>(D.Don) Endl.</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="72" ht="29" customHeight="1">
       <c r="A72" t="inlineStr">
@@ -5603,26 +4419,6 @@
           <t>Jb29</t>
         </is>
       </c>
-      <c r="U72" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V72" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>D.Don</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="73" ht="58" customHeight="1">
       <c r="A73" t="inlineStr">
@@ -5675,22 +4471,6 @@
           <t>Jb30</t>
         </is>
       </c>
-      <c r="U73" s="16" t="inlineStr">
-        <is>
-          <t>América del Sur</t>
-        </is>
-      </c>
-      <c r="V73" s="16" t="inlineStr"/>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>(Mirb.) Oerst.</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="74" ht="58" customHeight="1">
       <c r="A74" t="inlineStr">
@@ -5705,7 +4485,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Nothofagus obliqua</t>
+          <t>Nothofagus obliqua 2</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
@@ -5743,22 +4523,6 @@
           <t>Jb31</t>
         </is>
       </c>
-      <c r="U74" s="16" t="inlineStr">
-        <is>
-          <t>América del Sur</t>
-        </is>
-      </c>
-      <c r="V74" s="16" t="inlineStr"/>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>(Mirb.) Oerst.</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="75" ht="29" customHeight="1">
       <c r="A75" t="inlineStr">
@@ -5773,7 +4537,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Cryptomeria japonica</t>
+          <t>Cryptomeria japónica</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -5788,7 +4552,11 @@
         </is>
       </c>
       <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Cedrojapones.jpg</t>
+        </is>
+      </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>Cupressaceae</t>
@@ -5809,26 +4577,6 @@
       <c r="R75" s="5" t="inlineStr">
         <is>
           <t>Jb32</t>
-        </is>
-      </c>
-      <c r="U75" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V75" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>(Thunb. ex L. f.) D. Don</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>Conífera</t>
         </is>
       </c>
     </row>
@@ -5875,17 +4623,6 @@
           <t>Jb33</t>
         </is>
       </c>
-      <c r="U76" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V76" s="16" t="inlineStr"/>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="77" ht="29" customHeight="1">
       <c r="A77" t="inlineStr">
@@ -5938,22 +4675,6 @@
           <t>Jb34</t>
         </is>
       </c>
-      <c r="U77" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V77" s="16" t="inlineStr"/>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
     </row>
     <row r="78" ht="43.5" customHeight="1">
       <c r="A78" t="inlineStr">
@@ -5968,7 +4689,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Eucalyptus globulus</t>
+          <t>Eucalyptus globulus Labill.</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
@@ -5983,7 +4704,11 @@
         </is>
       </c>
       <c r="G78" s="5" t="n"/>
-      <c r="H78" s="5" t="n"/>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Eucaliptoaustraliano.jpg</t>
+        </is>
+      </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Myrtaceae</t>
@@ -6006,22 +4731,6 @@
           <t>Jb35</t>
         </is>
       </c>
-      <c r="U78" s="16" t="inlineStr">
-        <is>
-          <t>Oceanía</t>
-        </is>
-      </c>
-      <c r="V78" s="16" t="inlineStr"/>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>Labill.</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="79" ht="43.5" customHeight="1">
       <c r="A79" t="inlineStr">
@@ -6074,26 +4783,6 @@
           <t>Jb36</t>
         </is>
       </c>
-      <c r="U79" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V79" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Ten.</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="80" ht="87" customHeight="1">
       <c r="A80" t="inlineStr">
@@ -6146,22 +4835,6 @@
           <t>Jb37</t>
         </is>
       </c>
-      <c r="U80" s="16" t="inlineStr">
-        <is>
-          <t>Varias regiones</t>
-        </is>
-      </c>
-      <c r="V80" s="16" t="inlineStr"/>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Vahl</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="81" ht="29" customHeight="1">
       <c r="A81" t="inlineStr">
@@ -6176,7 +4849,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fraxinus exelsior</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -6214,22 +4887,6 @@
           <t>Jb38</t>
         </is>
       </c>
-      <c r="U81" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V81" s="16" t="inlineStr"/>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="82" ht="29" customHeight="1">
       <c r="A82" t="inlineStr">
@@ -6259,7 +4916,11 @@
         </is>
       </c>
       <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="n"/>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Pinoinsignia.jpg</t>
+        </is>
+      </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pinaceae</t>
@@ -6280,26 +4941,6 @@
       <c r="R82" s="5" t="inlineStr">
         <is>
           <t>Jb39</t>
-        </is>
-      </c>
-      <c r="U82" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V82" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>D.Don</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>Conífera</t>
         </is>
       </c>
     </row>
@@ -6346,17 +4987,6 @@
           <t>Jb40</t>
         </is>
       </c>
-      <c r="U83" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V83" s="16" t="inlineStr"/>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="84" ht="29" customHeight="1">
       <c r="A84" t="inlineStr">
@@ -6409,22 +5039,6 @@
           <t>Jb41</t>
         </is>
       </c>
-      <c r="U84" s="16" t="inlineStr">
-        <is>
-          <t>Cosmopolita</t>
-        </is>
-      </c>
-      <c r="V84" s="16" t="inlineStr"/>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Gillies ex Planch.</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="85" ht="29" customHeight="1">
       <c r="A85" t="inlineStr">
@@ -6439,7 +5053,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Brahea armata</t>
+          <t>Brahea Armata Palmatum</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -6477,26 +5091,6 @@
           <t>Jb42</t>
         </is>
       </c>
-      <c r="U85" s="16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="V85" s="16" t="inlineStr">
-        <is>
-          <t>Palmera</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>S.Watson</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>Palmera</t>
-        </is>
-      </c>
     </row>
     <row r="86" ht="29" customHeight="1">
       <c r="A86" t="inlineStr">
@@ -6549,22 +5143,6 @@
           <t>Jb43</t>
         </is>
       </c>
-      <c r="U86" s="16" t="inlineStr">
-        <is>
-          <t>Cosmopolita</t>
-        </is>
-      </c>
-      <c r="V86" s="16" t="inlineStr"/>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Gillies ex Planch.</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="87" ht="29" customHeight="1">
       <c r="A87" t="inlineStr">
@@ -6617,22 +5195,6 @@
           <t>Jb44</t>
         </is>
       </c>
-      <c r="U87" s="16" t="inlineStr">
-        <is>
-          <t>Cosmopolita</t>
-        </is>
-      </c>
-      <c r="V87" s="16" t="inlineStr"/>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>Gillies ex Planch.</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
-        </is>
-      </c>
     </row>
     <row r="88" ht="29" customHeight="1">
       <c r="A88" t="inlineStr">
@@ -6647,7 +5209,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Cedrus atlantica</t>
+          <t>Cedrus atlantica (Endl.) Manetti ex Carrière</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -6662,7 +5224,11 @@
         </is>
       </c>
       <c r="G88" s="5" t="n"/>
-      <c r="H88" s="5" t="n"/>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Cedroazul.jpg</t>
+        </is>
+      </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
           <t>Pinaceae</t>
@@ -6685,26 +5251,6 @@
           <t>Jb45</t>
         </is>
       </c>
-      <c r="U88" s="16" t="inlineStr">
-        <is>
-          <t>África</t>
-        </is>
-      </c>
-      <c r="V88" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>(Endl.) Manetti ex Carrière</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="89" ht="29" customHeight="1">
       <c r="A89" t="inlineStr">
@@ -6719,7 +5265,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Cedrus atlantica</t>
+          <t>Cedrus atlantica (Endl.) Manetti ex Carrière</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -6734,7 +5280,11 @@
         </is>
       </c>
       <c r="G89" s="5" t="n"/>
-      <c r="H89" s="5" t="n"/>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Cedroazul.jpg</t>
+        </is>
+      </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Pinaceae</t>
@@ -6757,26 +5307,6 @@
           <t>Jb46</t>
         </is>
       </c>
-      <c r="U89" s="16" t="inlineStr">
-        <is>
-          <t>África</t>
-        </is>
-      </c>
-      <c r="V89" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>(Endl.) Manetti ex Carrière</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="90" ht="29" customHeight="1">
       <c r="A90" t="inlineStr">
@@ -6829,26 +5359,6 @@
           <t>Jb47</t>
         </is>
       </c>
-      <c r="U90" s="16" t="inlineStr">
-        <is>
-          <t>América del Norte</t>
-        </is>
-      </c>
-      <c r="V90" s="16" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Ten.</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Conífera</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6899,22 +5409,6 @@
       <c r="R91" s="5" t="inlineStr">
         <is>
           <t>Jb48</t>
-        </is>
-      </c>
-      <c r="U91" s="16" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="V91" s="16" t="inlineStr"/>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
         </is>
       </c>
     </row>
@@ -6959,17 +5453,6 @@
       <c r="R92" s="5" t="inlineStr">
         <is>
           <t>Jb49</t>
-        </is>
-      </c>
-      <c r="U92" s="16" t="inlineStr">
-        <is>
-          <t>Hemisferio Norte</t>
-        </is>
-      </c>
-      <c r="V92" s="16" t="inlineStr"/>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>Árbol latifoliado</t>
         </is>
       </c>
     </row>
@@ -8304,7 +6787,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>pecho_amarillo.jpg</t>
+          <t>PechoAmarillo.JPG</t>
         </is>
       </c>
       <c r="L32" s="8" t="n"/>
@@ -8716,7 +7199,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>tyrannus_savana.jpg</t>
+          <t>TyrannusSavana.jpg</t>
         </is>
       </c>
       <c r="L42" s="8" t="n"/>
@@ -8876,7 +7359,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>TordoRenegrido.JPG</t>
+          <t>Tordorenegrido.JPG</t>
         </is>
       </c>
       <c r="L46" s="8" t="n"/>
@@ -9631,1984 +8114,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Hoja</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="E1" s="15" t="inlineStr">
-        <is>
-          <t>Valores / ejemplo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>Identificador único del ejemplar</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>ARB001, ARB002…</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>nombre_comun</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>Nombre común en español</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>Sabina de Virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>nombre_cientifico</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>Nombre científico (género especie autor)</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>Ginkgo biloba L.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>longitud</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>número</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Longitud geográfica (decimal)</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>-57.6802</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>latitud</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>número</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>Latitud geográfica (decimal)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>-38.0568</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>continente</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Origen geográfico (texto libre, detallado)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>Asia (China)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>año_plantacion</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>entero</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Año de plantación</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>foto</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Nombre del archivo de foto en /fotos</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Sabina.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>familia</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>Familia botánica</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>Cupressaceae</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>origen</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>Origen / país (texto libre)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>E.E.U.U</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>altura_m</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>número</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>Altura estimada en metros</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>diametro_cm</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>número</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>Diámetro de tronco en cm</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>estado_sanitario</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Estado sanitario del ejemplar</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>Bueno / Regular / Malo</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>floracion</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>Época o notas de floración</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>fructificacion</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>Época o notas de fructificación</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>Otoño</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>observaciones</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Notas libres</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Sector del arboretum</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>A1, Parque Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>id_relev</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>Identificador de relevamiento</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>destacado</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>1 = aparece en "Especies destacadas"</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>ficha</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>Slug base para la ficha (opcional)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>sabina</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>continente_norm</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>texto (controlado)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>NUEVO. Continente normalizado para estadísticas</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>América del Norte, América del Sur, América, Europa, Asia, África, Oceanía, Hemisferio Norte, Varias regiones, Cosmopolita, Origen hortícola/híbrido, Sin dato</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>texto (controlado)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>NUEVO. Grupo morfológico. Autocompletado para coníferas y palmeras</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>Conífera, Palmera, (vacío = a completar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>nativo_exotico</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>texto (controlado)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>NUEVO. A completar por el equipo</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>Nativo / Exótico</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>caduco_perenne</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Árboles</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>texto (controlado)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>NUEVO. A completar por el equipo</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>Caduco / Perenne</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>id / especie / nombre_cientifico</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Aves</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>Identificación de la observación de ave</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>AVE001</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>fecha / observador / residencia</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Aves</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>varios</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>Datos de la observación</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>id_sendero / nombre / longitud_m</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Senderos</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>varios</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>Datos de senderos</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>id / nombre / tipo</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Puntos de interés</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>varios</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>Puntos de interés del predio</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>arbol_id / fecha / evento</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Eventos fenológicos</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>varios</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Registro fenológico ligado a un árbol</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Floración</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>nombre_comun</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>nombre_cientifico</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>familia</t>
-        </is>
-      </c>
-      <c r="E1" s="15" t="inlineStr">
-        <is>
-          <t>Problema detectado</t>
-        </is>
-      </c>
-      <c r="F1" s="15" t="inlineStr">
-        <is>
-          <t>Sugerencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>ARB031</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>?Alcanforero</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>?Cinnamomum camphora</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>Lauraceae</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>Carácter “?” en nombre científico</t>
-        </is>
-      </c>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>Quitar el “?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>ARB031</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>?Alcanforero</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>?Cinnamomum camphora</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>Lauraceae</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>Carácter “?” en nombre común</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>Quitar el “?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>ARB038</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>Abeto de Douglas</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>Ceanothus thyrsiflorus</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>Rhamnaceae</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>“Abeto de Douglas” vs Ceanothus thyrsiflorus (Rhamnaceae) — no coinciden</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>Corregir nombre común o científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>ARB040</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Carex</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Celtis tala</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Cannabaceae</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>“Carex” vs Celtis tala — no coinciden</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>Corregir nombre común o científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>ARB044</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Aliso andino</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Abies concolor (Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>Pinaceae</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>“Aliso andino” vs Abies concolor (Pinaceae) — no coinciden</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>Corregir nombre común o científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>ARB050</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Ginkgo</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Acer palmatum</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Sapindaceae</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>“Ginkgo” vs Acer palmatum (Sapindaceae) — no coinciden (hay otro Ginkgo correcto en ARB076)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>Corregir nombre común o científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>ARB054</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Ligustro</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Ligustrum lucidum</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Olives</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>Familia “Olives” no es válida</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>¿Oleaceae?</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>ARB057</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Boj</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Nombre científico = “Revisar” (placeholder)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>Completar nombre científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>ARB067</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Ligustro</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Ligustrum lucidum</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>Olives</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>Familia “Olives” no es válida</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>¿Oleaceae?</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>ARB068</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Boj</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Nombre científico = “Revisar” (placeholder)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>Completar nombre científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>ARB083</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Carex</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Celtis tala</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>Cannabaceae</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>“Carex” vs Celtis tala — no coinciden</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>Corregir nombre común o científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>ARB085</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Carex</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Celtis tala</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>Cannabaceae</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>“Carex” vs Celtis tala — no coinciden</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>Corregir nombre común o científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>ARB086</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Carex</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Celtis tala</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Cannabaceae</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>“Carex” vs Celtis tala — no coinciden</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>Corregir nombre común o científico</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>ARB004</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Falso muérdago</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Ilex aquifolium L.</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>ARB010</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>Myrtaceae</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>Falta nombre científico</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>ARB010</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Myrtaceae</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>Falta nombre común</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>ARB011</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>Eucalyptus globulus Labill.</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Myrtaceae</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>Falta nombre común</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>ARB015</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Picea sp.</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>Pinaceae</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>Falta nombre común</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>ARB034</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Secuoya roja</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Sequoiadendron giganteum</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>Cupressaceae</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>ARB035</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Ahuehuete</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Taxodium mucronatum</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>Cupressaceae</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>ARB036</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Ciprés de las Guaitecas</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Austrocedrus chilensis</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>Cupressaceae</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>ARB037</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Tejo común</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Larix decidua</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>Pinaceae</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>ARB038</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Abeto de Douglas</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Ceanothus thyrsiflorus</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>Rhamnaceae</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>ARB039</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Hipericón canario</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>Hypericum x moserianum</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>Hypericaceae</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>ARB040</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>Carex</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>Celtis tala</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>Cannabaceae</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>ARB041</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Damara</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>Agathis dammara</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>Araucariaceae</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>ARB042</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Árbol de los tulipanes</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>Liriodendron tulipifera</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>Magnoliaceae</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>Faltan coordenadas (no aparece en el mapa)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>Cargar lat/long</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>ARB049</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Cedro</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>Cedrus sp.</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>ARB055</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Cedro</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>Cedrus sp.`</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>ARB057</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Boj</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>ARB064</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>Cedro</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Cedrus sp.</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>ARB068</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Boj</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>ARB075</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Cedro</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Cedrus sp.</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>ARB082</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Espino</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>Eucalyptus sp.</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>ARB091</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Olmo</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>Quercus sp.</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>Falta familia</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>Completar</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T92"/>
+  <dimension ref="A1:AA92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="19.81640625" customWidth="1" min="2" max="2"/>
@@ -622,6 +622,41 @@
           <t>ficha</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>forma_vida</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>continente_norm</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>nativo_exotico</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>caduco_perenne</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>padrino</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>autor</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -688,6 +723,21 @@
           <t>sabina</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="29" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -740,6 +790,21 @@
           <t>A2</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -804,6 +869,16 @@
           <t>roblecomun</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="43.5" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -856,6 +931,16 @@
           <t>A4</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="43.5" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -920,6 +1005,21 @@
           <t>cedrodelhimalaya</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -972,6 +1072,16 @@
           <t>A6</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="43.5" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1024,6 +1134,16 @@
           <t>A7</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1076,6 +1196,21 @@
           <t>A8</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1140,6 +1275,21 @@
           <t>cedroazul</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1192,6 +1342,16 @@
           <t>A10</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="43.5" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -1244,6 +1404,16 @@
           <t>A11</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Oceanía</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="29" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1296,6 +1466,21 @@
           <t>A12</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="43.5" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1360,6 +1545,16 @@
           <t>roblerojo</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1424,6 +1619,21 @@
           <t>abeto</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1472,6 +1682,21 @@
           <t>A15</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -1538,6 +1763,16 @@
           <t>limpiatubos</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>América del Sur</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1590,6 +1825,16 @@
           <t>A17</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Origen hortícola/híbrido</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -1646,6 +1891,16 @@
           <t>A18</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -1702,6 +1957,16 @@
           <t>A19</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -1758,6 +2023,16 @@
           <t>A20</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Origen hortícola/híbrido</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="29" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -1816,6 +2091,16 @@
           <t>A21</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="29" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -1880,6 +2165,21 @@
           <t>araucariaaustraliana</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Oceanía</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="29" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -1932,6 +2232,21 @@
           <t>A23</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="29" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -1984,6 +2299,21 @@
           <t>A24</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="29" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -2036,6 +2366,16 @@
           <t>A25</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="43.5" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -2096,6 +2436,16 @@
           <t>encina</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="43.5" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -2148,6 +2498,21 @@
           <t>A27</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="29" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -2209,6 +2574,21 @@
           <t>araucariaaustraliana</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Oceanía</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="29" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -2261,6 +2641,16 @@
           <t>A29</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="43.5" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -2325,6 +2715,16 @@
           <t>castanodeindias</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2377,6 +2777,16 @@
           <t>A31</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="29" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -2441,6 +2851,21 @@
           <t>cedrojapones</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="29" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -2491,6 +2916,16 @@
       <c r="R34" s="5" t="inlineStr">
         <is>
           <t>A33</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
         </is>
       </c>
     </row>
@@ -2549,6 +2984,21 @@
           <t>secuoiaroja</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="43.5" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -2593,6 +3043,21 @@
           <t>A35</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="43.5" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -2637,6 +3102,21 @@
           <t>A36</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>América del Sur</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -2681,6 +3161,21 @@
           <t>A37</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="29" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -2725,6 +3220,16 @@
           <t>A38</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="43.5" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -2769,6 +3274,16 @@
           <t>A39</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="43.5" customHeight="1">
       <c r="A41" t="inlineStr">
@@ -2813,6 +3328,16 @@
           <t>A40</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Cosmopolita</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="29" customHeight="1">
       <c r="A42" t="inlineStr">
@@ -2869,6 +3394,21 @@
           <t>damara</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2921,6 +3461,16 @@
           <t>arboldelostulipanes</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="29" customHeight="1">
       <c r="A44" t="inlineStr">
@@ -2977,6 +3527,16 @@
           <t>Jb1</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" t="inlineStr">
@@ -3033,6 +3593,21 @@
           <t>Jb2</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="29" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -3085,6 +3660,21 @@
           <t>Jb3</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="29" customHeight="1">
       <c r="A47" t="inlineStr">
@@ -3137,6 +3727,21 @@
           <t>Jb4</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="29" customHeight="1">
       <c r="A48" t="inlineStr">
@@ -3189,6 +3794,16 @@
           <t>Jb5</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="29" customHeight="1">
       <c r="A49" t="inlineStr">
@@ -3239,6 +3854,16 @@
       <c r="R49" s="5" t="inlineStr">
         <is>
           <t>Jb6</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -3285,6 +3910,16 @@
           <t>Jb7</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3347,6 +3982,16 @@
           <t>gingko</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" t="inlineStr">
@@ -3403,6 +4048,16 @@
           <t>Jb9</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="101.5" customHeight="1">
       <c r="A53" t="inlineStr">
@@ -3455,6 +4110,16 @@
           <t>Jb10</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Cosmopolita</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="29" customHeight="1">
       <c r="A54" t="inlineStr">
@@ -3507,6 +4172,21 @@
           <t>Jb11</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="29" customHeight="1">
       <c r="A55" t="inlineStr">
@@ -3557,6 +4237,16 @@
       <c r="R55" s="5" t="inlineStr">
         <is>
           <t>Jb12</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -3603,6 +4293,16 @@
           <t>Jb13</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="43.5" customHeight="1">
       <c r="A57" t="inlineStr">
@@ -3653,6 +4353,16 @@
       <c r="R57" s="5" t="inlineStr">
         <is>
           <t>Jb14</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -3699,6 +4409,16 @@
           <t>Jb15</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="43.5" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -3751,6 +4471,16 @@
           <t>Jb16</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Oceanía</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="29" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -3807,6 +4537,16 @@
           <t>Jb17</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3859,6 +4599,16 @@
           <t>Jb18</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="43.5" customHeight="1">
       <c r="A62" t="inlineStr">
@@ -3911,6 +4661,16 @@
           <t>Jb19</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Oceanía</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="29" customHeight="1">
       <c r="A63" t="inlineStr">
@@ -3967,6 +4727,16 @@
           <t>Jb20</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="29" customHeight="1">
       <c r="A64" t="inlineStr">
@@ -4017,6 +4787,16 @@
       <c r="R64" s="5" t="inlineStr">
         <is>
           <t>Jb21</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -4063,6 +4843,16 @@
           <t>Jb22</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="29" customHeight="1">
       <c r="A66" t="inlineStr">
@@ -4115,6 +4905,16 @@
           <t>Jb23</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" t="inlineStr">
@@ -4167,6 +4967,16 @@
           <t>Jb24</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="29" customHeight="1">
       <c r="A68" t="inlineStr">
@@ -4217,6 +5027,16 @@
       <c r="R68" s="5" t="inlineStr">
         <is>
           <t>Jb25</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -4263,6 +5083,16 @@
           <t>Jb26</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="43.5" customHeight="1">
       <c r="A70" t="inlineStr">
@@ -4313,6 +5143,16 @@
       <c r="R70" s="5" t="inlineStr">
         <is>
           <t>Jb27</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Oceanía</t>
         </is>
       </c>
     </row>
@@ -4363,6 +5203,21 @@
           <t>Jb28</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="29" customHeight="1">
       <c r="A72" t="inlineStr">
@@ -4419,6 +5274,21 @@
           <t>Jb29</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="58" customHeight="1">
       <c r="A73" t="inlineStr">
@@ -4471,6 +5341,16 @@
           <t>Jb30</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>América del Sur</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="58" customHeight="1">
       <c r="A74" t="inlineStr">
@@ -4523,6 +5403,16 @@
           <t>Jb31</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>América del Sur</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="29" customHeight="1">
       <c r="A75" t="inlineStr">
@@ -4577,6 +5467,21 @@
       <c r="R75" s="5" t="inlineStr">
         <is>
           <t>Jb32</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Conífera</t>
         </is>
       </c>
     </row>
@@ -4623,6 +5528,16 @@
           <t>Jb33</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="29" customHeight="1">
       <c r="A77" t="inlineStr">
@@ -4675,6 +5590,16 @@
           <t>Jb34</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="43.5" customHeight="1">
       <c r="A78" t="inlineStr">
@@ -4731,6 +5656,16 @@
           <t>Jb35</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Oceanía</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="43.5" customHeight="1">
       <c r="A79" t="inlineStr">
@@ -4783,6 +5718,21 @@
           <t>Jb36</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="87" customHeight="1">
       <c r="A80" t="inlineStr">
@@ -4835,6 +5785,16 @@
           <t>Jb37</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Varias regiones</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="29" customHeight="1">
       <c r="A81" t="inlineStr">
@@ -4887,6 +5847,16 @@
           <t>Jb38</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="29" customHeight="1">
       <c r="A82" t="inlineStr">
@@ -4941,6 +5911,21 @@
       <c r="R82" s="5" t="inlineStr">
         <is>
           <t>Jb39</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Conífera</t>
         </is>
       </c>
     </row>
@@ -4987,6 +5972,16 @@
           <t>Jb40</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="29" customHeight="1">
       <c r="A84" t="inlineStr">
@@ -5039,6 +6034,16 @@
           <t>Jb41</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Cosmopolita</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="29" customHeight="1">
       <c r="A85" t="inlineStr">
@@ -5091,6 +6096,21 @@
           <t>Jb42</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Palmera</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Palmera</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="29" customHeight="1">
       <c r="A86" t="inlineStr">
@@ -5143,6 +6163,16 @@
           <t>Jb43</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Cosmopolita</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="29" customHeight="1">
       <c r="A87" t="inlineStr">
@@ -5195,6 +6225,16 @@
           <t>Jb44</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Cosmopolita</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="29" customHeight="1">
       <c r="A88" t="inlineStr">
@@ -5251,6 +6291,21 @@
           <t>Jb45</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="29" customHeight="1">
       <c r="A89" t="inlineStr">
@@ -5307,6 +6362,21 @@
           <t>Jb46</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>África</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="29" customHeight="1">
       <c r="A90" t="inlineStr">
@@ -5359,6 +6429,21 @@
           <t>Jb47</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>América del Norte</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5409,6 +6494,16 @@
       <c r="R91" s="5" t="inlineStr">
         <is>
           <t>Jb48</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Europa</t>
         </is>
       </c>
     </row>
@@ -5453,6 +6548,16 @@
       <c r="R92" s="5" t="inlineStr">
         <is>
           <t>Jb49</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Hemisferio Norte</t>
         </is>
       </c>
     </row>

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -2603,7 +2603,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Populu alba L.</t>
+          <t>Populus alba L.</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>?Alcanforero</t>
+          <t>Alcanforero</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>?Cinnamomum camphora</t>
+          <t>Cinnamomum camphora</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Cedrus sp.`</t>
+          <t>Cedrus sp.</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Sequoia semprevirens</t>
+          <t>Sequoia sempervirens</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Nothofagus obliqua 2</t>
+          <t>Nothofagus obliqua</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Cryptomeria japónica</t>
+          <t>Cryptomeria japonica</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">

--- a/data/Arboretum_Master.xlsx
+++ b/data/Arboretum_Master.xlsx
@@ -7892,7 +7892,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>PechoAmarillo.JPG</t>
+          <t>Pechoamarillo.JPG</t>
         </is>
       </c>
       <c r="L32" s="8" t="n"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>TyrannusSavana.jpg</t>
+          <t>Tyrannussavana.jpg</t>
         </is>
       </c>
       <c r="L42" s="8" t="n"/>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Tordorenegrido.JPG</t>
+          <t>TordoRenegrido.JPG</t>
         </is>
       </c>
       <c r="L46" s="8" t="n"/>
